--- a/products_categories_descriptions_documents_working.xlsx
+++ b/products_categories_descriptions_documents_working.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Products" sheetId="1" r:id="Ree96f10bc97749b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Products" sheetId="1" r:id="R5084499dcd0f40dc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -104,7 +104,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="15">
+  <x:cellXfs count="16">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -124,6 +124,9 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -332,6 +335,7 @@
     <x:col min="25" max="25" width="28" hidden="0" customWidth="1"/>
     <x:col min="26" max="26" width="28" hidden="0" customWidth="1"/>
     <x:col min="27" max="27" width="28" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="42" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -359,7 +363,7 @@
       <x:c r="H1" t="str">
         <x:v>Categories</x:v>
       </x:c>
-      <x:c r="I1" t="str">
+      <x:c r="I1" s="15" t="str">
         <x:v>Tags</x:v>
       </x:c>
       <x:c r="J1" t="str">
@@ -440,8 +444,8 @@
       <x:c r="H2" t="str">
         <x:v>Paints &gt; Interior</x:v>
       </x:c>
-      <x:c r="I2" t="str">
-        <x:v>benjamin moore, bm paints, colour sample, paint sample, sample, tester, wall colour test</x:v>
+      <x:c r="I2" s="15" t="str">
+        <x:v>paint sample, colour sample, liquid paint sample, interior paint sample</x:v>
       </x:c>
       <x:c r="J2" t="str">
         <x:v>Benjamin Moore</x:v>
@@ -498,8 +502,8 @@
       <x:c r="H3" t="str">
         <x:v>Paints &gt; Stains &amp; Varnishes</x:v>
       </x:c>
-      <x:c r="I3" t="str">
-        <x:v>benjamin moore, bm paints, exterior paint, exterior stain, sample, stain sample, tester, wood sample, wood stain</x:v>
+      <x:c r="I3" s="15" t="str">
+        <x:v>stain sample, wood stain sample, exterior stain sample, liquid stain sample</x:v>
       </x:c>
       <x:c r="J3" t="str">
         <x:v>Benjamin Moore</x:v>
@@ -559,8 +563,8 @@
       <x:c r="H4" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I4" t="str">
-        <x:v>benjamin moore, bm paints, paint swatch, peel &amp; stick, peel and stick, removable sample, sample, tester</x:v>
+      <x:c r="I4" s="15" t="str">
+        <x:v>paint sample, colour sample, peel and stick sample, repositionable paint sample</x:v>
       </x:c>
       <x:c r="J4" t="str">
         <x:v>Benjamin Moore</x:v>
@@ -614,8 +618,8 @@
       <x:c r="H5" t="str">
         <x:v>Paints &gt; Interior</x:v>
       </x:c>
-      <x:c r="I5" t="str">
-        <x:v>aura, aura interior, interior paint, benjamin moore, bm paints, indoor, interior,premium paint, washable walls, colour lock, premium</x:v>
+      <x:c r="I5" s="15" t="str">
+        <x:v>interior paint, architectural paint, wall paint, interior coating</x:v>
       </x:c>
       <x:c r="J5" t="str">
         <x:v>Benjamin Moore</x:v>
@@ -681,8 +685,8 @@
       <x:c r="H6" t="str">
         <x:v>Paints &gt; Interior</x:v>
       </x:c>
-      <x:c r="I6" t="str">
-        <x:v>aura, aura interior, interior paint, benjamin moore, bath &amp; spa, bathroom paint, bm paints, high humidity, indoor, interior, mildew resistant, colour lock, premium</x:v>
+      <x:c r="I6" s="15" t="str">
+        <x:v>interior paint, architectural paint, wall paint, interior coating, bathroom paint, moisture-resistant interior paint</x:v>
       </x:c>
       <x:c r="J6" t="str">
         <x:v>Benjamin Moore</x:v>
@@ -748,8 +752,8 @@
       <x:c r="H7" t="str">
         <x:v>Paints &gt; Interior</x:v>
       </x:c>
-      <x:c r="I7" t="str">
-        <x:v>regal, regal interior, interior paint, benjamin moore, bm paints, everyday paint, indoor, interior,  regal select, scrubbable</x:v>
+      <x:c r="I7" s="15" t="str">
+        <x:v>interior paint, architectural paint, wall paint, interior coating</x:v>
       </x:c>
       <x:c r="J7" t="str">
         <x:v>Benjamin Moore</x:v>
@@ -815,8 +819,8 @@
       <x:c r="H8" t="str">
         <x:v>Paints &gt; Interior</x:v>
       </x:c>
-      <x:c r="I8" t="str">
-        <x:v>ben, BEN, ben interior, interior paint, benjamin moore, bm paints, indoor, interior, zero voc, value, budget </x:v>
+      <x:c r="I8" s="15" t="str">
+        <x:v>interior paint, architectural paint, wall paint, interior coating</x:v>
       </x:c>
       <x:c r="J8" t="str">
         <x:v>Benjamin Moore</x:v>
@@ -882,8 +886,8 @@
       <x:c r="H9" t="str">
         <x:v>Paints &gt; Interior</x:v>
       </x:c>
-      <x:c r="I9" t="str">
-        <x:v>kitchen and bath, bathroom paint, benjamin moore, bm paints, indoor, interior, kitchen paint, mildew resistant, moisture resistant</x:v>
+      <x:c r="I9" s="15" t="str">
+        <x:v>interior paint, architectural paint, wall paint, interior coating, bathroom paint, moisture-resistant interior paint</x:v>
       </x:c>
       <x:c r="J9" t="str">
         <x:v>Benjamin Moore</x:v>
@@ -949,8 +953,8 @@
       <x:c r="H10" t="str">
         <x:v>Paints &gt; Interior</x:v>
       </x:c>
-      <x:c r="I10" t="str">
-        <x:v>benjamin moore, bm paints, ceiling, ceiling paint, indoor, interior, ultra flat, zero voc</x:v>
+      <x:c r="I10" s="15" t="str">
+        <x:v>ceiling paint, interior paint, flat paint, architectural coating</x:v>
       </x:c>
       <x:c r="J10" t="str">
         <x:v>Benjamin Moore</x:v>
@@ -1016,8 +1020,8 @@
       <x:c r="H11" t="str">
         <x:v>Paints &gt; Interior</x:v>
       </x:c>
-      <x:c r="I11" t="str">
-        <x:v>benjamin moore, bm paints, ceiling, ceiling paint, flat finish, indoor, interior, muresco</x:v>
+      <x:c r="I11" s="15" t="str">
+        <x:v>ceiling paint, interior paint, flat paint, architectural coating</x:v>
       </x:c>
       <x:c r="J11" t="str">
         <x:v>Benjamin Moore</x:v>
@@ -1083,8 +1087,8 @@
       <x:c r="H12" t="str">
         <x:v>Paints &gt; Exterior</x:v>
       </x:c>
-      <x:c r="I12" t="str">
-        <x:v>aura, aura exterior, exterior paint, benjamin moore, bm paints, colour lock, exterior, exterior paint, fade resistant, outdoor, premium</x:v>
+      <x:c r="I12" s="15" t="str">
+        <x:v>exterior paint, architectural paint, weather-resistant coating, exterior coating</x:v>
       </x:c>
       <x:c r="J12" t="str">
         <x:v>Benjamin Moore</x:v>
@@ -1150,8 +1154,8 @@
       <x:c r="H13" t="str">
         <x:v>Paints &gt; Exterior</x:v>
       </x:c>
-      <x:c r="I13" t="str">
-        <x:v>regal, regal exterior, exterior paint, benjamin moore, bm paints, exterior, high build, outdoor, regal select, everyday paint</x:v>
+      <x:c r="I13" s="15" t="str">
+        <x:v>exterior paint, architectural paint, weather-resistant coating, exterior coating</x:v>
       </x:c>
       <x:c r="J13" t="str">
         <x:v>Benjamin Moore</x:v>
@@ -1217,8 +1221,8 @@
       <x:c r="H14" t="str">
         <x:v>Paints &gt; Exterior</x:v>
       </x:c>
-      <x:c r="I14" t="str">
-        <x:v>benjamin moore, bm paints, element guard, exterior, exterior paint, harsh weather, moisture protection, outdoor</x:v>
+      <x:c r="I14" s="15" t="str">
+        <x:v>exterior paint, architectural paint, weather-resistant coating, exterior coating</x:v>
       </x:c>
       <x:c r="J14" t="str">
         <x:v>Benjamin Moore</x:v>
@@ -1284,8 +1288,8 @@
       <x:c r="H15" t="str">
         <x:v>Paints &gt; Exterior</x:v>
       </x:c>
-      <x:c r="I15" t="str">
-        <x:v>benjamin moore, bm paints, contractor grade, exterior, exterior paint, outdoor, ultra spec</x:v>
+      <x:c r="I15" s="15" t="str">
+        <x:v>exterior paint, architectural paint, weather-resistant coating, exterior coating</x:v>
       </x:c>
       <x:c r="J15" t="str">
         <x:v>Benjamin Moore</x:v>
@@ -1351,8 +1355,8 @@
       <x:c r="H16" t="str">
         <x:v>Paints &gt; Stains &amp; Varnishes</x:v>
       </x:c>
-      <x:c r="I16" t="str">
-        <x:v>benjamin moore, bm paints, deck stain, exterior, exterior wood, outdoor, stain, uv resistant, water-based stain, waterproofing stain, wood stain, woodluxe</x:v>
+      <x:c r="I16" s="15" t="str">
+        <x:v>exterior wood stain, penetrating wood finish, wood stain, exterior wood finish, wood sealer, waterproofing stain, water-based wood finish</x:v>
       </x:c>
       <x:c r="J16" t="str">
         <x:v>Benjamin Moore</x:v>
@@ -1418,8 +1422,8 @@
       <x:c r="H17" t="str">
         <x:v>Paints &gt; Stains &amp; Varnishes</x:v>
       </x:c>
-      <x:c r="I17" t="str">
-        <x:v>benjamin moore, bm paints, exterior, exterior wood, oil-based stain, outdoor, penetrating oil, stain, waterproofing stain, wood stain, woodluxe</x:v>
+      <x:c r="I17" s="15" t="str">
+        <x:v>exterior wood stain, penetrating wood finish, wood stain, exterior wood finish, wood sealer, waterproofing stain, oil-based wood finish</x:v>
       </x:c>
       <x:c r="J17" t="str">
         <x:v>Benjamin Moore</x:v>
@@ -1483,8 +1487,8 @@
       <x:c r="H18" t="str">
         <x:v>Paints &gt; Stains &amp; Varnishes</x:v>
       </x:c>
-      <x:c r="I18" t="str">
-        <x:v>benjamin moore, bm paints, deck stain, exterior, exterior paint, exterior stain, outdoor, siding stain, stain, wood stain, woodluxe</x:v>
+      <x:c r="I18" s="15" t="str">
+        <x:v>deck stain, exterior wood stain, wood stain, exterior wood finish, penetrating wood finish</x:v>
       </x:c>
       <x:c r="J18" t="str">
         <x:v>Benjamin Moore</x:v>
@@ -1550,8 +1554,8 @@
       <x:c r="H19" t="str">
         <x:v>Paints &gt; Primers</x:v>
       </x:c>
-      <x:c r="I19" t="str">
-        <x:v>benjamin moore, bm paints, fresh start, high hiding primer, primer, problem surface, stain blocking</x:v>
+      <x:c r="I19" s="15" t="str">
+        <x:v>primer, primer sealer, surface preparation coating, basecoat</x:v>
       </x:c>
       <x:c r="J19" t="str">
         <x:v>Benjamin Moore</x:v>
@@ -1615,8 +1619,8 @@
       <x:c r="H20" t="str">
         <x:v>Paints &gt; Primers</x:v>
       </x:c>
-      <x:c r="I20" t="str">
-        <x:v>adhesion, bonding primer, hard to coat, insl-x, primer, primer sealer, specialty coatings, stix</x:v>
+      <x:c r="I20" s="15" t="str">
+        <x:v>bonding primer, adhesion primer, primer, surface preparation coating, primer sealer, basecoat</x:v>
       </x:c>
       <x:c r="J20" t="str">
         <x:v>Insl-X</x:v>
@@ -1680,8 +1684,8 @@
       <x:c r="H21" t="str">
         <x:v>Paints &gt; Primers</x:v>
       </x:c>
-      <x:c r="I21" t="str">
-        <x:v>benjamin moore, bm paints, fast sanding, primer, primer sealer, sandable primer, smooth finish, wood primer</x:v>
+      <x:c r="I21" s="15" t="str">
+        <x:v>sanding primer, interior primer, primer sealer, surface preparation coating, primer, basecoat</x:v>
       </x:c>
       <x:c r="J21" t="str">
         <x:v>Benjamin Moore</x:v>
@@ -1745,8 +1749,8 @@
       <x:c r="H22" t="str">
         <x:v>Paints &gt; Primers</x:v>
       </x:c>
-      <x:c r="I22" t="str">
-        <x:v>benjamin moore, bm paints, drywall primer, new drywall, primer, primer sealer, sealer</x:v>
+      <x:c r="I22" s="15" t="str">
+        <x:v>drywall primer, interior primer, primer sealer, surface preparation coating, primer, basecoat</x:v>
       </x:c>
       <x:c r="J22" t="str">
         <x:v>Benjamin Moore</x:v>
@@ -1810,8 +1814,8 @@
       <x:c r="H23" t="str">
         <x:v>Paints &gt; Interior</x:v>
       </x:c>
-      <x:c r="I23" t="str">
-        <x:v>advance, benjamin moore, bm paints, cabinet paint, doors and trim, trim paint, waterborne alkyd</x:v>
+      <x:c r="I23" s="15" t="str">
+        <x:v>interior paint, architectural paint, wall paint, interior coating, cabinet paint, trim enamel, interior enamel, architectural coating</x:v>
       </x:c>
       <x:c r="J23" t="str">
         <x:v>Benjamin Moore</x:v>
@@ -1877,8 +1881,8 @@
       <x:c r="H24" t="str">
         <x:v>Paints &gt; Exterior</x:v>
       </x:c>
-      <x:c r="I24" t="str">
-        <x:v>benjamin moore, bm paints, concrete floor, floor, floor paint, patio paint, porch paint</x:v>
+      <x:c r="I24" s="15" t="str">
+        <x:v>floor paint, porch and patio paint, concrete floor coating, protective coating</x:v>
       </x:c>
       <x:c r="J24" t="str">
         <x:v>Benjamin Moore</x:v>
@@ -1944,8 +1948,8 @@
       <x:c r="H25" t="str">
         <x:v>Paints &gt; Interior</x:v>
       </x:c>
-      <x:c r="I25" t="str">
-        <x:v>cabinet coat, cabinet paint, furniture paint, insl-x, specialty coatings, urethane acrylic</x:v>
+      <x:c r="I25" s="15" t="str">
+        <x:v>cabinet paint, trim enamel, interior enamel, architectural coating</x:v>
       </x:c>
       <x:c r="J25" t="str">
         <x:v>Insl-X</x:v>
@@ -2011,8 +2015,8 @@
       <x:c r="H26" t="str">
         <x:v>Paints &gt; Interior</x:v>
       </x:c>
-      <x:c r="I26" t="str">
-        <x:v>benjamin moore, bm paints, commercial paint, indoor, interior, interior paint, ultra spec, zero voc</x:v>
+      <x:c r="I26" s="15" t="str">
+        <x:v>interior paint, architectural paint, wall paint, interior coating</x:v>
       </x:c>
       <x:c r="J26" t="str">
         <x:v>Benjamin Moore</x:v>
@@ -2078,8 +2082,8 @@
       <x:c r="H27" t="str">
         <x:v>Paints &gt; Interior</x:v>
       </x:c>
-      <x:c r="I27" t="str">
-        <x:v>benjamin moore, bm paints, commercial paint, high traffic, indoor, interior, scuff resistant, scuff-x, industrial </x:v>
+      <x:c r="I27" s="15" t="str">
+        <x:v>interior paint, architectural paint, wall paint, interior coating</x:v>
       </x:c>
       <x:c r="J27" t="str">
         <x:v>Benjamin Moore</x:v>
@@ -2145,8 +2149,8 @@
       <x:c r="H28" t="str">
         <x:v>Paints &gt; Interior</x:v>
       </x:c>
-      <x:c r="I28" t="str">
-        <x:v>benjamin moore, bm paints, eco friendly, eco spec, green paint, indoor, interior, zero voc</x:v>
+      <x:c r="I28" s="15" t="str">
+        <x:v>interior paint, architectural paint, wall paint, interior coating</x:v>
       </x:c>
       <x:c r="J28" t="str">
         <x:v>Benjamin Moore</x:v>
@@ -2212,8 +2216,8 @@
       <x:c r="H29" t="str">
         <x:v>Paints &gt; Primers</x:v>
       </x:c>
-      <x:c r="I29" t="str">
-        <x:v>primer, latex, multi-surface, sealer, drywall, masonry, quick drying</x:v>
+      <x:c r="I29" s="15" t="str">
+        <x:v>primer, primer sealer, surface preparation coating, basecoat</x:v>
       </x:c>
       <x:c r="J29" t="str">
         <x:v>Insl-X</x:v>
@@ -2277,8 +2281,8 @@
       <x:c r="H30" t="str">
         <x:v>Paints &gt; Primers</x:v>
       </x:c>
-      <x:c r="I30" t="str">
-        <x:v>primer, acrylic, sealer, stain blocker, water stains, adhesion, interior exterior</x:v>
+      <x:c r="I30" s="15" t="str">
+        <x:v>primer, primer sealer, surface preparation coating, basecoat</x:v>
       </x:c>
       <x:c r="J30" t="str">
         <x:v>Insl-X</x:v>
@@ -2342,8 +2346,8 @@
       <x:c r="H31" t="str">
         <x:v>Paints &gt; Interior</x:v>
       </x:c>
-      <x:c r="I31" t="str">
-        <x:v>alkyd primer, oil-based, stain sealer, enamel holdout, wood, trim, cabinets</x:v>
+      <x:c r="I31" s="15" t="str">
+        <x:v>primer, primer sealer, surface preparation coating, basecoat</x:v>
       </x:c>
       <x:c r="J31" t="str">
         <x:v>Insl-X</x:v>
@@ -2407,8 +2411,8 @@
       <x:c r="H32" t="str">
         <x:v>Paints &gt; Primers</x:v>
       </x:c>
-      <x:c r="I32" t="str">
-        <x:v>bonding primer, high adhesion, waterborne, multi-surface, tile, pvc, vinyl</x:v>
+      <x:c r="I32" s="15" t="str">
+        <x:v>bonding primer, adhesion primer, primer, surface preparation coating, primer sealer, basecoat</x:v>
       </x:c>
       <x:c r="J32" t="str">
         <x:v>Insl-X</x:v>
@@ -2472,8 +2476,8 @@
       <x:c r="H33" t="str">
         <x:v>Paints &gt; Primers</x:v>
       </x:c>
-      <x:c r="I33" t="str">
-        <x:v>stain blocker, water-based, severe stains, smoke damage, interior, low odour</x:v>
+      <x:c r="I33" s="15" t="str">
+        <x:v>stain-blocking primer, water-based primer, primer sealer, interior and exterior primer</x:v>
       </x:c>
       <x:c r="J33" t="str">
         <x:v>Insl-X</x:v>
@@ -2537,8 +2541,8 @@
       <x:c r="H34" t="str">
         <x:v>Paints &gt; Primers</x:v>
       </x:c>
-      <x:c r="I34" t="str">
-        <x:v>high build, latex primer, leveling, drywall repair, uneven walls</x:v>
+      <x:c r="I34" s="15" t="str">
+        <x:v>high-build primer, latex primer, interior primer, surface preparation coating, primer, primer sealer, basecoat</x:v>
       </x:c>
       <x:c r="J34" t="str">
         <x:v>Insl-X</x:v>
@@ -2602,8 +2606,8 @@
       <x:c r="H35" t="str">
         <x:v>Paints &gt; Primers</x:v>
       </x:c>
-      <x:c r="I35" t="str">
-        <x:v>oil-based primer, reduced odour, stain blocking, adhesion, sealer</x:v>
+      <x:c r="I35" s="15" t="str">
+        <x:v>primer, primer sealer, surface preparation coating, basecoat</x:v>
       </x:c>
       <x:c r="J35" t="str">
         <x:v>Insl-X</x:v>
@@ -2667,8 +2671,8 @@
       <x:c r="H36" t="str">
         <x:v>Paints &gt; Interior</x:v>
       </x:c>
-      <x:c r="I36" t="str">
-        <x:v>vapour barrier, sealer, moisture control, interior walls, specialty primer</x:v>
+      <x:c r="I36" s="15" t="str">
+        <x:v>vapour-barrier primer, primer sealer, interior coating, moisture-control coating, primer, surface preparation coating, basecoat</x:v>
       </x:c>
       <x:c r="J36" t="str">
         <x:v>Insl-X</x:v>
@@ -2732,8 +2736,8 @@
       <x:c r="H37" t="str">
         <x:v>Commercial &amp; Industrial &gt; Paints</x:v>
       </x:c>
-      <x:c r="I37" t="str">
-        <x:v>spray, acrylic, dtm, metal, quick dry, corrosion resistant</x:v>
+      <x:c r="I37" s="15" t="str">
+        <x:v>direct-to-metal paint, acrylic enamel, industrial coating, anti-corrosion coating</x:v>
       </x:c>
       <x:c r="J37" t="str">
         <x:v>Benjamin Moore</x:v>
@@ -2799,8 +2803,8 @@
       <x:c r="H38" t="str">
         <x:v>Commercial &amp; Industrial &gt; Paints</x:v>
       </x:c>
-      <x:c r="I38" t="str">
-        <x:v>dtm, acrylic enamel, gloss, metal coating, corrosion resistant, interior exterior</x:v>
+      <x:c r="I38" s="15" t="str">
+        <x:v>direct-to-metal paint, acrylic enamel, industrial coating, anti-corrosion coating</x:v>
       </x:c>
       <x:c r="J38" t="str">
         <x:v>Benjamin Moore</x:v>
@@ -2862,8 +2866,8 @@
       <x:c r="H39" t="str">
         <x:v>Commercial &amp; Industrial &gt; Epoxy</x:v>
       </x:c>
-      <x:c r="I39" t="str">
-        <x:v>epoxy, waterborne, semi-gloss, commercial, durable, chemical resistant</x:v>
+      <x:c r="I39" s="15" t="str">
+        <x:v>epoxy coating, two-part epoxy, protective coating, industrial coating</x:v>
       </x:c>
       <x:c r="J39" t="str">
         <x:v>Benjamin Moore</x:v>
@@ -2929,8 +2933,8 @@
       <x:c r="H40" t="str">
         <x:v>Commercial &amp; Industrial &gt; Paints</x:v>
       </x:c>
-      <x:c r="I40" t="str">
-        <x:v>urethane, acrylic, command, gloss, commercial, quick dry, high durability</x:v>
+      <x:c r="I40" s="15" t="str">
+        <x:v>acrylic urethane coating, water-based industrial coating, protective enamel, industrial coating</x:v>
       </x:c>
       <x:c r="J40" t="str">
         <x:v>Benjamin Moore</x:v>
@@ -2992,8 +2996,8 @@
       <x:c r="H41" t="str">
         <x:v>Commercial &amp; Industrial &gt; Epoxy</x:v>
       </x:c>
-      <x:c r="I41" t="str">
-        <x:v>aliphatic urethane, 2k, gloss, industrial, uv resistant, chemical resistant</x:v>
+      <x:c r="I41" s="15" t="str">
+        <x:v>aliphatic urethane coating, two-component coating, protective coating, industrial coating</x:v>
       </x:c>
       <x:c r="J41" t="str">
         <x:v>Benjamin Moore</x:v>
@@ -3055,8 +3059,8 @@
       <x:c r="H42" t="str">
         <x:v>Commercial &amp; Industrial &gt; Epoxy</x:v>
       </x:c>
-      <x:c r="I42" t="str">
-        <x:v>urethane mastic, dtm, gloss, corrosion resistant, industrial, high build</x:v>
+      <x:c r="I42" s="15" t="str">
+        <x:v>urethane mastic, direct-to-metal coating, protective coating, industrial coating</x:v>
       </x:c>
       <x:c r="J42" t="str">
         <x:v>Benjamin Moore</x:v>
@@ -3118,8 +3122,8 @@
       <x:c r="H43" t="str">
         <x:v>Commercial &amp; Industrial &gt; Primers</x:v>
       </x:c>
-      <x:c r="I43" t="str">
-        <x:v>acrylic, metal primer, corrosion resistant, adhesion, interior exterior</x:v>
+      <x:c r="I43" s="15" t="str">
+        <x:v>metal primer, anti-corrosion primer, industrial primer, surface preparation coating, primer, primer sealer, basecoat</x:v>
       </x:c>
       <x:c r="J43" t="str">
         <x:v>Benjamin Moore</x:v>
@@ -3183,8 +3187,8 @@
       <x:c r="H44" t="str">
         <x:v>Commercial &amp; Industrial &gt; Epoxy</x:v>
       </x:c>
-      <x:c r="I44" t="str">
-        <x:v>acrylic sealer, clear coat, protective finish, waterborne</x:v>
+      <x:c r="I44" s="15" t="str">
+        <x:v>acrylic sealer, clear protective coating, industrial coating, surface sealer</x:v>
       </x:c>
       <x:c r="J44" t="str">
         <x:v>Benjamin Moore</x:v>
@@ -3248,8 +3252,8 @@
       <x:c r="H45" t="str">
         <x:v>Commercial &amp; Industrial &gt; Primers</x:v>
       </x:c>
-      <x:c r="I45" t="str">
-        <x:v>metal primer, universal, rust inhibiting, adhesion, steel, machinery</x:v>
+      <x:c r="I45" s="15" t="str">
+        <x:v>metal primer, anti-corrosion primer, industrial primer, surface preparation coating, primer, primer sealer, basecoat</x:v>
       </x:c>
       <x:c r="J45" t="str">
         <x:v>Benjamin Moore</x:v>
@@ -3313,8 +3317,8 @@
       <x:c r="H46" t="str">
         <x:v>Commercial &amp; Industrial &gt; Primers</x:v>
       </x:c>
-      <x:c r="I46" t="str">
-        <x:v>shop primer, steel, fabrication, corrosion protection, industrial</x:v>
+      <x:c r="I46" s="15" t="str">
+        <x:v>metal primer, anti-corrosion primer, industrial primer, surface preparation coating, primer, primer sealer, basecoat</x:v>
       </x:c>
       <x:c r="J46" t="str">
         <x:v>Benjamin Moore</x:v>
@@ -3378,8 +3382,8 @@
       <x:c r="H47" t="str">
         <x:v>Commercial &amp; Industrial &gt; Epoxy</x:v>
       </x:c>
-      <x:c r="I47" t="str">
-        <x:v>epoxy primer, concrete, metal, chemical resistant, industrial</x:v>
+      <x:c r="I47" s="15" t="str">
+        <x:v>epoxy primer, concrete primer, metal primer, two-part industrial primer</x:v>
       </x:c>
       <x:c r="J47" t="str">
         <x:v>Benjamin Moore</x:v>
@@ -3443,8 +3447,8 @@
       <x:c r="H48" t="str">
         <x:v>Commercial &amp; Industrial &gt; Primers</x:v>
       </x:c>
-      <x:c r="I48" t="str">
-        <x:v>bonding primer, waterborne, adhesion, smooth surfaces</x:v>
+      <x:c r="I48" s="15" t="str">
+        <x:v>bonding primer, adhesion primer, primer, surface preparation coating, primer sealer, basecoat</x:v>
       </x:c>
       <x:c r="J48" t="str">
         <x:v>Benjamin Moore</x:v>
@@ -3508,8 +3512,8 @@
       <x:c r="H49" t="str">
         <x:v>Commercial &amp; Industrial &gt; Epoxy</x:v>
       </x:c>
-      <x:c r="I49" t="str">
-        <x:v>epoxy, polyamide, 2k, industrial, corrosion resistant, chemical resistant</x:v>
+      <x:c r="I49" s="15" t="str">
+        <x:v>epoxy coating, two-part epoxy, protective coating, industrial coating</x:v>
       </x:c>
       <x:c r="J49" t="str">
         <x:v>Benjamin Moore</x:v>
@@ -3575,8 +3579,8 @@
       <x:c r="H50" t="str">
         <x:v>Commercial &amp; Industrial &gt; Epoxy</x:v>
       </x:c>
-      <x:c r="I50" t="str">
-        <x:v>epoxy, polyamide, fast cure, industrial, corrosion resistant</x:v>
+      <x:c r="I50" s="15" t="str">
+        <x:v>epoxy coating, two-part epoxy, protective coating, industrial coating</x:v>
       </x:c>
       <x:c r="J50" t="str">
         <x:v>Benjamin Moore</x:v>
@@ -3642,8 +3646,8 @@
       <x:c r="H51" t="str">
         <x:v>Commercial &amp; Industrial &gt; Epoxy</x:v>
       </x:c>
-      <x:c r="I51" t="str">
-        <x:v>epoxy, 100% solids, industrial flooring, high build, chemical resistant</x:v>
+      <x:c r="I51" s="15" t="str">
+        <x:v>epoxy coating, two-part epoxy, protective coating, industrial coating</x:v>
       </x:c>
       <x:c r="J51" t="str">
         <x:v>Benjamin Moore</x:v>
@@ -3709,8 +3713,8 @@
       <x:c r="H52" t="str">
         <x:v>Paints &gt; Exterior</x:v>
       </x:c>
-      <x:c r="I52" t="str">
-        <x:v>concrete stain, tuffcrete, acrylic, waterborne, interior exterior</x:v>
+      <x:c r="I52" s="15" t="str">
+        <x:v>concrete stain, masonry coating, water-based coating, decorative concrete finish</x:v>
       </x:c>
       <x:c r="J52" t="str">
         <x:v>Insl-X</x:v>
@@ -3776,8 +3780,8 @@
       <x:c r="H53" t="str">
         <x:v>Paints &gt; Epoxy</x:v>
       </x:c>
-      <x:c r="I53" t="str">
-        <x:v>garageguard, epoxy, 2-part, concrete floor, chemical resistant, durable</x:v>
+      <x:c r="I53" s="15" t="str">
+        <x:v>epoxy coating, two-part epoxy, protective coating, industrial coating</x:v>
       </x:c>
       <x:c r="J53" t="str">
         <x:v>Insl-X</x:v>
@@ -3843,8 +3847,8 @@
       <x:c r="H54" t="str">
         <x:v>Paints &gt; Exterior</x:v>
       </x:c>
-      <x:c r="I54" t="str">
-        <x:v>garage floor paint, 1-part, concrete floor, acrylic, durable, quick dry</x:v>
+      <x:c r="I54" s="15" t="str">
+        <x:v>floor paint, porch and patio paint, concrete floor coating, protective coating</x:v>
       </x:c>
       <x:c r="J54" t="str">
         <x:v>Insl-X</x:v>
@@ -3910,8 +3914,8 @@
       <x:c r="H55" t="str">
         <x:v>Paints &gt; Exterior</x:v>
       </x:c>
-      <x:c r="I55" t="str">
-        <x:v>waterproofer, masonry, concrete, penetrating sealer, clear, exterior</x:v>
+      <x:c r="I55" s="15" t="str">
+        <x:v>waterproofing sealer, masonry waterproofer, clear protective coating, penetrating sealer</x:v>
       </x:c>
       <x:c r="J55" t="str">
         <x:v>Insl-X</x:v>
@@ -3977,8 +3981,8 @@
       <x:c r="H56" t="str">
         <x:v>Paints &gt; Specialty Paints</x:v>
       </x:c>
-      <x:c r="I56" t="str">
-        <x:v>pool paint, waterborne, acrylic, semi-gloss, concrete pool</x:v>
+      <x:c r="I56" s="15" t="str">
+        <x:v>pool paint, swimming pool coating, immersed-service coating, specialty coating</x:v>
       </x:c>
       <x:c r="J56" t="str">
         <x:v>Insl-X</x:v>
@@ -4044,8 +4048,8 @@
       <x:c r="H57" t="str">
         <x:v>Paints &gt; Specialty Paints</x:v>
       </x:c>
-      <x:c r="I57" t="str">
-        <x:v>pool paint, rubber-based, satin, concrete pool, durable</x:v>
+      <x:c r="I57" s="15" t="str">
+        <x:v>pool paint, swimming pool coating, immersed-service coating, specialty coating</x:v>
       </x:c>
       <x:c r="J57" t="str">
         <x:v>Insl-X</x:v>
@@ -4111,8 +4115,8 @@
       <x:c r="H58" t="str">
         <x:v>Paints &gt; Specialty Paints</x:v>
       </x:c>
-      <x:c r="I58" t="str">
-        <x:v>pool paint, epoxy, 2-part, high build, chemical resistant, durable</x:v>
+      <x:c r="I58" s="15" t="str">
+        <x:v>epoxy pool paint, swimming pool coating, two-part epoxy coating, immersed-service coating</x:v>
       </x:c>
       <x:c r="J58" t="str">
         <x:v>Insl-X</x:v>
@@ -4178,8 +4182,8 @@
       <x:c r="H59" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I59" t="str">
-        <x:v>painter’s tape, masking, prep</x:v>
+      <x:c r="I59" s="15" t="str">
+        <x:v>painter's tape applicator, masking tape applicator, hand masking tool, painting accessory</x:v>
       </x:c>
       <x:c r="J59" t="str">
         <x:v>3M</x:v>
@@ -4227,8 +4231,8 @@
       <x:c r="H60" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I60" t="str">
-        <x:v>masking system, paint prep, dispenser</x:v>
+      <x:c r="I60" s="15" t="str">
+        <x:v>masking dispenser, hand masking tool, film and paper applicator, painting accessory</x:v>
       </x:c>
       <x:c r="J60" t="str">
         <x:v>3M</x:v>
@@ -4276,8 +4280,8 @@
       <x:c r="H61" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I61" t="str">
-        <x:v>masking tool, paint prep, dispenser</x:v>
+      <x:c r="I61" s="15" t="str">
+        <x:v>masking dispenser, hand masking tool, film and paper applicator, painting accessory</x:v>
       </x:c>
       <x:c r="J61" t="str">
         <x:v>3M</x:v>
@@ -4325,8 +4329,8 @@
       <x:c r="H62" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I62" t="str">
-        <x:v>masking film, paint prep, surface protection</x:v>
+      <x:c r="I62" s="15" t="str">
+        <x:v>masking film, surface protection film, paint masking material, painting accessory</x:v>
       </x:c>
       <x:c r="J62" t="str">
         <x:v>3M</x:v>
@@ -4374,8 +4378,8 @@
       <x:c r="H63" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Clothing &amp; Safety</x:v>
       </x:c>
-      <x:c r="I63" t="str">
-        <x:v>respirator, dust protection, disposable</x:v>
+      <x:c r="I63" s="15" t="str">
+        <x:v>n95 respirator, particulate respirator, disposable mask, respiratory protection</x:v>
       </x:c>
       <x:c r="J63" t="str">
         <x:v>3M</x:v>
@@ -4423,8 +4427,8 @@
       <x:c r="H64" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Clothing &amp; Safety</x:v>
       </x:c>
-      <x:c r="I64" t="str">
-        <x:v>respirator, dust protection, disposable</x:v>
+      <x:c r="I64" s="15" t="str">
+        <x:v>n95 respirator, particulate respirator, disposable mask, respiratory protection</x:v>
       </x:c>
       <x:c r="J64" t="str">
         <x:v>3M</x:v>
@@ -4472,8 +4476,8 @@
       <x:c r="H65" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Clothing &amp; Safety</x:v>
       </x:c>
-      <x:c r="I65" t="str">
-        <x:v>respirator cartridge, organic vapor, replacement filter</x:v>
+      <x:c r="I65" s="15" t="str">
+        <x:v>organic vapour cartridge, respirator cartridge, chemical vapour filter, respiratory protection accessory</x:v>
       </x:c>
       <x:c r="J65" t="str">
         <x:v>3M</x:v>
@@ -4521,8 +4525,8 @@
       <x:c r="H66" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Clothing &amp; Safety</x:v>
       </x:c>
-      <x:c r="I66" t="str">
-        <x:v>respirator, paint fumes, reusable</x:v>
+      <x:c r="I66" s="15" t="str">
+        <x:v>reusable respirator, paint respirator, respiratory protection, half-mask respirator</x:v>
       </x:c>
       <x:c r="J66" t="str">
         <x:v>3M</x:v>
@@ -4570,8 +4574,8 @@
       <x:c r="H67" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I67" t="str">
-        <x:v>painter’s tape, masking, prep</x:v>
+      <x:c r="I67" s="15" t="str">
+        <x:v>masking tape, painter's tape, pressure-sensitive tape, painting accessory</x:v>
       </x:c>
       <x:c r="J67" t="str">
         <x:v>3M</x:v>
@@ -4619,8 +4623,8 @@
       <x:c r="H68" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I68" t="str">
-        <x:v>painter’s tape, masking, prep</x:v>
+      <x:c r="I68" s="15" t="str">
+        <x:v>masking tape, painter's tape, pressure-sensitive tape, painting accessory, delicate-surface masking tape</x:v>
       </x:c>
       <x:c r="J68" t="str">
         <x:v>3M</x:v>
@@ -4668,8 +4672,8 @@
       <x:c r="H69" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I69" t="str">
-        <x:v>painter’s tape, masking, prep</x:v>
+      <x:c r="I69" s="15" t="str">
+        <x:v>masking tape, painter's tape, pressure-sensitive tape, painting accessory</x:v>
       </x:c>
       <x:c r="J69" t="str">
         <x:v>3M</x:v>
@@ -4717,8 +4721,8 @@
       <x:c r="H70" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I70" t="str">
-        <x:v>painter’s tape, masking, prep</x:v>
+      <x:c r="I70" s="15" t="str">
+        <x:v>masking tape, painter's tape, pressure-sensitive tape, painting accessory, heavy-duty masking tape</x:v>
       </x:c>
       <x:c r="J70" t="str">
         <x:v>3M</x:v>
@@ -4766,8 +4770,8 @@
       <x:c r="H71" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I71" t="str">
-        <x:v>painter’s tape, masking, prep</x:v>
+      <x:c r="I71" s="15" t="str">
+        <x:v>masking tape, painter's tape, pressure-sensitive tape, painting accessory</x:v>
       </x:c>
       <x:c r="J71" t="str">
         <x:v>3M</x:v>
@@ -4815,8 +4819,8 @@
       <x:c r="H72" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I72" t="str">
-        <x:v>filler, repair, surface prep</x:v>
+      <x:c r="I72" s="15" t="str">
+        <x:v>glazing putty, spot putty, automotive filler, surface repair compound</x:v>
       </x:c>
       <x:c r="J72" t="str">
         <x:v>3M</x:v>
@@ -4864,8 +4868,8 @@
       <x:c r="H73" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I73" t="str">
-        <x:v>filler, repair, surface prep</x:v>
+      <x:c r="I73" s="15" t="str">
+        <x:v>automotive body filler, polyester filler, two-part repair compound, surface repair product</x:v>
       </x:c>
       <x:c r="J73" t="str">
         <x:v>3M</x:v>
@@ -4913,8 +4917,8 @@
       <x:c r="H74" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Clothing &amp; Safety</x:v>
       </x:c>
-      <x:c r="I74" t="str">
-        <x:v>full face respirator, fume protection, reusable</x:v>
+      <x:c r="I74" s="15" t="str">
+        <x:v>reusable respirator, paint respirator, respiratory protection, full-face respirator</x:v>
       </x:c>
       <x:c r="J74" t="str">
         <x:v>3M</x:v>
@@ -4962,8 +4966,8 @@
       <x:c r="H75" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I75" t="str">
-        <x:v>filler, repair, surface prep</x:v>
+      <x:c r="I75" s="15" t="str">
+        <x:v>wood filler, wood repair compound, grain filler, surface repair product</x:v>
       </x:c>
       <x:c r="J75" t="str">
         <x:v>Timbermate</x:v>
@@ -5011,8 +5015,8 @@
       <x:c r="H76" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I76" t="str">
-        <x:v>epoxy, repair, adhesive</x:v>
+      <x:c r="I76" s="15" t="str">
+        <x:v>epoxy adhesive, two-part epoxy, repair adhesive, epoxy repair compound</x:v>
       </x:c>
       <x:c r="J76" t="str">
         <x:v>PC Products</x:v>
@@ -5060,8 +5064,8 @@
       <x:c r="H77" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I77" t="str">
-        <x:v>filler, repair, surface prep</x:v>
+      <x:c r="I77" s="15" t="str">
+        <x:v>seam repair compound, laminate seam filler, wallcovering seam repair, repair filler</x:v>
       </x:c>
       <x:c r="J77" t="str">
         <x:v>Kampel</x:v>
@@ -5107,8 +5111,8 @@
       <x:c r="H78" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I78" t="str">
-        <x:v>detail brush, fine finish, touch-up</x:v>
+      <x:c r="I78" s="15" t="str">
+        <x:v>artist brush, fine-detail brush, paint brush, painting tool</x:v>
       </x:c>
       <x:c r="J78" t="str">
         <x:v>DFP</x:v>
@@ -5156,8 +5160,8 @@
       <x:c r="H79" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Cleaners &amp; Removers</x:v>
       </x:c>
-      <x:c r="I79" t="str">
-        <x:v>paint remover, stripping, surface prep</x:v>
+      <x:c r="I79" s="15" t="str">
+        <x:v>coating remover, paint remover, finish stripper, surface preparation chemical</x:v>
       </x:c>
       <x:c r="J79" t="str">
         <x:v>Dumond</x:v>
@@ -5205,8 +5209,8 @@
       <x:c r="H80" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Cleaners &amp; Removers</x:v>
       </x:c>
-      <x:c r="I80" t="str">
-        <x:v>paint remover, stripping, surface prep</x:v>
+      <x:c r="I80" s="15" t="str">
+        <x:v>coating remover, paint remover, finish stripper, surface preparation chemical</x:v>
       </x:c>
       <x:c r="J80" t="str">
         <x:v>Dumond</x:v>
@@ -5254,8 +5258,8 @@
       <x:c r="H81" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Cleaners &amp; Removers</x:v>
       </x:c>
-      <x:c r="I81" t="str">
-        <x:v>paint remover, stripping, surface prep</x:v>
+      <x:c r="I81" s="15" t="str">
+        <x:v>coating remover, paint remover, finish stripper, surface preparation chemical</x:v>
       </x:c>
       <x:c r="J81" t="str">
         <x:v>Dumond</x:v>
@@ -5303,8 +5307,8 @@
       <x:c r="H82" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I82" t="str">
-        <x:v>epoxy, repair, adhesive</x:v>
+      <x:c r="I82" s="15" t="str">
+        <x:v>concrete epoxy adhesive, two-part epoxy, masonry repair adhesive, structural adhesive</x:v>
       </x:c>
       <x:c r="J82" t="str">
         <x:v>PC Products</x:v>
@@ -5352,8 +5356,8 @@
       <x:c r="H83" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I83" t="str">
-        <x:v>ladder protection, non-marking, jobsite safety</x:v>
+      <x:c r="I83" s="15" t="str">
+        <x:v>ladder mitt, ladder protection pad, ladder accessory, surface protection product</x:v>
       </x:c>
       <x:c r="J83" t="str">
         <x:v>H.F. Staples</x:v>
@@ -5401,8 +5405,8 @@
       <x:c r="H84" t="str">
         <x:v>Lacquer and Millwork Coatings &gt; Dover</x:v>
       </x:c>
-      <x:c r="I84" t="str">
-        <x:v>touch-up marker, repair, wood finishing</x:v>
+      <x:c r="I84" s="15" t="str">
+        <x:v>touch-up marker, wood repair marker, colour repair pen, finishing tool</x:v>
       </x:c>
       <x:c r="J84" t="str">
         <x:v>Premier</x:v>
@@ -5450,8 +5454,8 @@
       <x:c r="H85" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I85" t="str">
-        <x:v>filler, repair, surface prep</x:v>
+      <x:c r="I85" s="15" t="str">
+        <x:v>wood filler, wood repair compound, grain filler, surface repair product</x:v>
       </x:c>
       <x:c r="J85" t="str">
         <x:v>GoodFilla</x:v>
@@ -5499,8 +5503,8 @@
       <x:c r="H86" t="str">
         <x:v>Lacquer and Millwork Coatings &gt; Dover</x:v>
       </x:c>
-      <x:c r="I86" t="str">
-        <x:v>touch-up marker, repair, wood finishing</x:v>
+      <x:c r="I86" s="15" t="str">
+        <x:v>touch-up marker, wood repair marker, colour repair pen, finishing tool</x:v>
       </x:c>
       <x:c r="J86" t="str">
         <x:v>DFP</x:v>
@@ -5548,8 +5552,8 @@
       <x:c r="H87" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I87" t="str">
-        <x:v>epoxy, repair, adhesive</x:v>
+      <x:c r="I87" s="15" t="str">
+        <x:v>wood repair epoxy, wood filler, two-part epoxy, repair compound, quick-cure epoxy</x:v>
       </x:c>
       <x:c r="J87" t="str">
         <x:v>DFP</x:v>
@@ -5597,8 +5601,8 @@
       <x:c r="H88" t="str">
         <x:v>Lacquer and Millwork Coatings &gt; Dover</x:v>
       </x:c>
-      <x:c r="I88" t="str">
-        <x:v>painting tool, accessory, application</x:v>
+      <x:c r="I88" s="15" t="str">
+        <x:v>fill stick, wax repair stick, wood repair filler, furniture touch-up product</x:v>
       </x:c>
       <x:c r="J88" t="str">
         <x:v>DFP</x:v>
@@ -5646,8 +5650,8 @@
       <x:c r="H89" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I89" t="str">
-        <x:v>caulking tool, finishing, application</x:v>
+      <x:c r="I89" s="15" t="str">
+        <x:v>caulk finishing tool, sealant smoothing tool, caulking applicator, hand tool</x:v>
       </x:c>
       <x:c r="J89" t="str">
         <x:v>Innovatco</x:v>
@@ -5695,8 +5699,8 @@
       <x:c r="H90" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I90" t="str">
-        <x:v>epoxy, repair, adhesive</x:v>
+      <x:c r="I90" s="15" t="str">
+        <x:v>wood repair epoxy, wood filler, two-part epoxy, repair compound</x:v>
       </x:c>
       <x:c r="J90" t="str">
         <x:v>PC Products</x:v>
@@ -5744,8 +5748,8 @@
       <x:c r="H91" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I91" t="str">
-        <x:v>epoxy, repair, adhesive</x:v>
+      <x:c r="I91" s="15" t="str">
+        <x:v>epoxy paste, two-part epoxy, repair adhesive, repair compound</x:v>
       </x:c>
       <x:c r="J91" t="str">
         <x:v>PC Products</x:v>
@@ -5793,8 +5797,8 @@
       <x:c r="H92" t="str">
         <x:v>Lacquer and Millwork Coatings &gt; Goudey</x:v>
       </x:c>
-      <x:c r="I92" t="str">
-        <x:v>solvent, thinner, cleanup</x:v>
+      <x:c r="I92" s="15" t="str">
+        <x:v>mineral spirits, paint thinner, finishing solvent, cleaning solvent</x:v>
       </x:c>
       <x:c r="J92" t="str">
         <x:v>Gotham</x:v>
@@ -5842,8 +5846,8 @@
       <x:c r="H93" t="str">
         <x:v>Lacquer and Millwork Coatings &gt; Goudey</x:v>
       </x:c>
-      <x:c r="I93" t="str">
-        <x:v>lacquer thinner, solvent, cleanup</x:v>
+      <x:c r="I93" s="15" t="str">
+        <x:v>lacquer thinner, lacquer solvent, coating reducer, finishing solvent</x:v>
       </x:c>
       <x:c r="J93" t="str">
         <x:v>Gotham</x:v>
@@ -5891,8 +5895,8 @@
       <x:c r="H94" t="str">
         <x:v>Lacquer and Millwork Coatings &gt; Goudey</x:v>
       </x:c>
-      <x:c r="I94" t="str">
-        <x:v>solvent, thinner, cleanup</x:v>
+      <x:c r="I94" s="15" t="str">
+        <x:v>acetone, finishing solvent, cleaning solvent, surface preparation solvent</x:v>
       </x:c>
       <x:c r="J94" t="str">
         <x:v>Gotham</x:v>
@@ -5940,8 +5944,8 @@
       <x:c r="H95" t="str">
         <x:v>Lacquer and Millwork Coatings &gt; Goudey</x:v>
       </x:c>
-      <x:c r="I95" t="str">
-        <x:v>stain, wood finish, wood projects</x:v>
+      <x:c r="I95" s="15" t="str">
+        <x:v>paint thinner, finishing solvent, coating reducer, cleaning solvent</x:v>
       </x:c>
       <x:c r="J95" t="str">
         <x:v>Gotham</x:v>
@@ -5989,8 +5993,8 @@
       <x:c r="H96" t="str">
         <x:v>Lacquer and Millwork Coatings &gt; Goudey</x:v>
       </x:c>
-      <x:c r="I96" t="str">
-        <x:v>shellac, wood finish, clear coat</x:v>
+      <x:c r="I96" s="15" t="str">
+        <x:v>methyl hydrate, finishing solvent, cleaning solvent, surface preparation solvent</x:v>
       </x:c>
       <x:c r="J96" t="str">
         <x:v>Gotham</x:v>
@@ -6038,8 +6042,8 @@
       <x:c r="H97" t="str">
         <x:v>Lacquer and Millwork Coatings &gt; Goudey</x:v>
       </x:c>
-      <x:c r="I97" t="str">
-        <x:v>solvent, thinner, cleanup</x:v>
+      <x:c r="I97" s="15" t="str">
+        <x:v>methyl hydrate, finishing solvent, cleaning solvent, surface preparation solvent</x:v>
       </x:c>
       <x:c r="J97" t="str">
         <x:v>Goudey</x:v>
@@ -6087,8 +6091,8 @@
       <x:c r="H98" t="str">
         <x:v>Lacquer and Millwork Coatings &gt; Goudey</x:v>
       </x:c>
-      <x:c r="I98" t="str">
-        <x:v>solvent, thinner, cleanup</x:v>
+      <x:c r="I98" s="15" t="str">
+        <x:v>toluene, finishing solvent, coating solvent, surface preparation solvent</x:v>
       </x:c>
       <x:c r="J98" t="str">
         <x:v>Goudey</x:v>
@@ -6136,8 +6140,8 @@
       <x:c r="H99" t="str">
         <x:v>Lacquer and Millwork Coatings &gt; Goudey</x:v>
       </x:c>
-      <x:c r="I99" t="str">
-        <x:v>solvent, thinner, cleanup</x:v>
+      <x:c r="I99" s="15" t="str">
+        <x:v>naphtha, finishing solvent, coating solvent, cleaning solvent</x:v>
       </x:c>
       <x:c r="J99" t="str">
         <x:v>Goudey</x:v>
@@ -6185,8 +6189,8 @@
       <x:c r="H100" t="str">
         <x:v>Lacquer and Millwork Coatings &gt; Goudey</x:v>
       </x:c>
-      <x:c r="I100" t="str">
-        <x:v>solvent, thinner, cleanup</x:v>
+      <x:c r="I100" s="15" t="str">
+        <x:v>mineral spirits, paint thinner, finishing solvent, cleaning solvent</x:v>
       </x:c>
       <x:c r="J100" t="str">
         <x:v>Goudey</x:v>
@@ -6234,8 +6238,8 @@
       <x:c r="H101" t="str">
         <x:v>Lacquer and Millwork Coatings &gt; Goudey</x:v>
       </x:c>
-      <x:c r="I101" t="str">
-        <x:v>blush retarder, lacquer additive, spray finishing</x:v>
+      <x:c r="I101" s="15" t="str">
+        <x:v>lacquer retarder, blush eliminator, finish additive, lacquer additive</x:v>
       </x:c>
       <x:c r="J101" t="str">
         <x:v>Goudey</x:v>
@@ -6283,8 +6287,8 @@
       <x:c r="H102" t="str">
         <x:v>Lacquer and Millwork Coatings &gt; Goudey</x:v>
       </x:c>
-      <x:c r="I102" t="str">
-        <x:v>wiping stain, wood stain, interior wood</x:v>
+      <x:c r="I102" s="15" t="str">
+        <x:v>stain reducer, wood finishing solvent, coating reducer, finishing solvent</x:v>
       </x:c>
       <x:c r="J102" t="str">
         <x:v>Goudey</x:v>
@@ -6332,8 +6336,8 @@
       <x:c r="H103" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Cleaners &amp; Removers</x:v>
       </x:c>
-      <x:c r="I103" t="str">
-        <x:v>paint remover, stripping, surface prep</x:v>
+      <x:c r="I103" s="15" t="str">
+        <x:v>coating remover, paint remover, finish stripper, surface preparation chemical</x:v>
       </x:c>
       <x:c r="J103" t="str">
         <x:v>Goudey</x:v>
@@ -6381,8 +6385,8 @@
       <x:c r="H104" t="str">
         <x:v>Lacquer and Millwork Coatings &gt; Goudey</x:v>
       </x:c>
-      <x:c r="I104" t="str">
-        <x:v>lacquer thinner, solvent, cleanup</x:v>
+      <x:c r="I104" s="15" t="str">
+        <x:v>lacquer thinner, lacquer solvent, coating reducer, finishing solvent</x:v>
       </x:c>
       <x:c r="J104" t="str">
         <x:v>Goudey</x:v>
@@ -6430,8 +6434,8 @@
       <x:c r="H105" t="str">
         <x:v>Lacquer and Millwork Coatings &gt; Goudey</x:v>
       </x:c>
-      <x:c r="I105" t="str">
-        <x:v>wood bleach, wood prep, stain projects</x:v>
+      <x:c r="I105" s="15" t="str">
+        <x:v>wood bleach, two-part wood bleach, wood treatment, wood restoration product</x:v>
       </x:c>
       <x:c r="J105" t="str">
         <x:v>Goudey</x:v>
@@ -6479,8 +6483,8 @@
       <x:c r="H106" t="str">
         <x:v>Lacquer and Millwork Coatings &gt; Goudey</x:v>
       </x:c>
-      <x:c r="I106" t="str">
-        <x:v>undercoat, wood primer, solvent-based</x:v>
+      <x:c r="I106" s="15" t="str">
+        <x:v>wood undercoat, white undercoat, high-solids undercoat, wood finishing basecoat</x:v>
       </x:c>
       <x:c r="J106" t="str">
         <x:v>Goudey</x:v>
@@ -6528,8 +6532,8 @@
       <x:c r="H107" t="str">
         <x:v>Lacquer and Millwork Coatings &gt; Goudey</x:v>
       </x:c>
-      <x:c r="I107" t="str">
-        <x:v>pre-cat lacquer, wood finish, professional</x:v>
+      <x:c r="I107" s="15" t="str">
+        <x:v>pre-catalyzed lacquer, wood lacquer, clear wood finish, solvent-based lacquer</x:v>
       </x:c>
       <x:c r="J107" t="str">
         <x:v>Goudey</x:v>
@@ -6577,8 +6581,8 @@
       <x:c r="H108" t="str">
         <x:v>Lacquer and Millwork Coatings &gt; Goudey</x:v>
       </x:c>
-      <x:c r="I108" t="str">
-        <x:v>wood conditioner, pre-stain prep, wood finishing</x:v>
+      <x:c r="I108" s="15" t="str">
+        <x:v>wood conditioner, stain glaze base, wood finishing basecoat, solvent-based wood finish</x:v>
       </x:c>
       <x:c r="J108" t="str">
         <x:v>Goudey</x:v>
@@ -6626,8 +6630,8 @@
       <x:c r="H109" t="str">
         <x:v>Lacquer and Millwork Coatings &gt; Goudey</x:v>
       </x:c>
-      <x:c r="I109" t="str">
-        <x:v>wiping stain, wood stain, interior wood</x:v>
+      <x:c r="I109" s="15" t="str">
+        <x:v>wiping stain, wood stain, wood finish, solvent-based wood stain</x:v>
       </x:c>
       <x:c r="J109" t="str">
         <x:v>Goudey</x:v>
@@ -6675,8 +6679,8 @@
       <x:c r="H110" t="str">
         <x:v>Lacquer and Millwork Coatings &gt; Goudey</x:v>
       </x:c>
-      <x:c r="I110" t="str">
-        <x:v>shellac, wood finish, clear coat</x:v>
+      <x:c r="I110" s="15" t="str">
+        <x:v>shellac finish, clear wood finish, natural resin finish, sealing finish</x:v>
       </x:c>
       <x:c r="J110" t="str">
         <x:v>Goudey</x:v>
@@ -6724,8 +6728,8 @@
       <x:c r="H111" t="str">
         <x:v>Lacquer and Millwork Coatings &gt; Goudey</x:v>
       </x:c>
-      <x:c r="I111" t="str">
-        <x:v>water-based stain, wood stain, low odor</x:v>
+      <x:c r="I111" s="15" t="str">
+        <x:v>wiping stain, wood stain, wood finish, water-based wood stain</x:v>
       </x:c>
       <x:c r="J111" t="str">
         <x:v>Goudey</x:v>
@@ -6773,8 +6777,8 @@
       <x:c r="H112" t="str">
         <x:v>Paints &gt; Exterior</x:v>
       </x:c>
-      <x:c r="I112" t="str">
-        <x:v>deck stain, exterior wood, oil finish</x:v>
+      <x:c r="I112" s="15" t="str">
+        <x:v>exterior wood finish, deck stain, siding stain, oil-based wood stain</x:v>
       </x:c>
       <x:c r="J112" t="str">
         <x:v>Messmer's</x:v>
@@ -6828,8 +6832,8 @@
       <x:c r="H113" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I113" t="str">
-        <x:v>paint brush, application, professional</x:v>
+      <x:c r="I113" s="15" t="str">
+        <x:v>deck stain brush, wide paint brush, wood finish applicator, painting tool</x:v>
       </x:c>
       <x:c r="J113" t="str">
         <x:v>Nour</x:v>
@@ -6877,8 +6881,8 @@
       <x:c r="H114" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I114" t="str">
-        <x:v>paint brush, application, professional</x:v>
+      <x:c r="I114" s="15" t="str">
+        <x:v>angled paint brush, sash brush, paint applicator, painting tool</x:v>
       </x:c>
       <x:c r="J114" t="str">
         <x:v>Nour</x:v>
@@ -6926,8 +6930,8 @@
       <x:c r="H115" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I115" t="str">
-        <x:v>paint brush, application, professional</x:v>
+      <x:c r="I115" s="15" t="str">
+        <x:v>paint brush, paint applicator, painting tool, bristle brush</x:v>
       </x:c>
       <x:c r="J115" t="str">
         <x:v>AllPro</x:v>
@@ -6975,8 +6979,8 @@
       <x:c r="H116" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I116" t="str">
-        <x:v>paint brush, application, professional</x:v>
+      <x:c r="I116" s="15" t="str">
+        <x:v>paint brush, paint applicator, painting tool, bristle brush</x:v>
       </x:c>
       <x:c r="J116" t="str">
         <x:v>AllPro</x:v>
@@ -7024,8 +7028,8 @@
       <x:c r="H117" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I117" t="str">
-        <x:v>paint brush, application, professional</x:v>
+      <x:c r="I117" s="15" t="str">
+        <x:v>paint brush, paint applicator, painting tool, bristle brush</x:v>
       </x:c>
       <x:c r="J117" t="str">
         <x:v>AllPro</x:v>
@@ -7073,8 +7077,8 @@
       <x:c r="H118" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I118" t="str">
-        <x:v>paint brush, application, professional</x:v>
+      <x:c r="I118" s="15" t="str">
+        <x:v>oval paint brush, paint applicator, paint brush, painting tool</x:v>
       </x:c>
       <x:c r="J118" t="str">
         <x:v>AllPro</x:v>
@@ -7122,8 +7126,8 @@
       <x:c r="H119" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I119" t="str">
-        <x:v>paint brush, application, professional</x:v>
+      <x:c r="I119" s="15" t="str">
+        <x:v>oval paint brush, paint applicator, paint brush, painting tool</x:v>
       </x:c>
       <x:c r="J119" t="str">
         <x:v>AllPro</x:v>
@@ -7171,8 +7175,8 @@
       <x:c r="H120" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I120" t="str">
-        <x:v>paint brush, application, professional</x:v>
+      <x:c r="I120" s="15" t="str">
+        <x:v>angled paint brush, sash brush, paint applicator, painting tool</x:v>
       </x:c>
       <x:c r="J120" t="str">
         <x:v>Nour</x:v>
@@ -7220,8 +7224,8 @@
       <x:c r="H121" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I121" t="str">
-        <x:v>paint brush, application, professional</x:v>
+      <x:c r="I121" s="15" t="str">
+        <x:v>angled paint brush, sash brush, paint applicator, painting tool</x:v>
       </x:c>
       <x:c r="J121" t="str">
         <x:v>Nour</x:v>
@@ -7269,8 +7273,8 @@
       <x:c r="H122" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I122" t="str">
-        <x:v>paint brush, application, professional</x:v>
+      <x:c r="I122" s="15" t="str">
+        <x:v>angled paint brush, sash brush, paint applicator, painting tool</x:v>
       </x:c>
       <x:c r="J122" t="str">
         <x:v>Nour</x:v>
@@ -7318,8 +7322,8 @@
       <x:c r="H123" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I123" t="str">
-        <x:v>paint brush, application, professional</x:v>
+      <x:c r="I123" s="15" t="str">
+        <x:v>angled paint brush, sash brush, paint applicator, painting tool</x:v>
       </x:c>
       <x:c r="J123" t="str">
         <x:v>Nour</x:v>
@@ -7367,8 +7371,8 @@
       <x:c r="H124" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I124" t="str">
-        <x:v>paint brush, application, professional</x:v>
+      <x:c r="I124" s="15" t="str">
+        <x:v>angled paint brush, sash brush, paint applicator, painting tool</x:v>
       </x:c>
       <x:c r="J124" t="str">
         <x:v>Nour</x:v>
@@ -7416,8 +7420,8 @@
       <x:c r="H125" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I125" t="str">
-        <x:v>paint brush, application, professional</x:v>
+      <x:c r="I125" s="15" t="str">
+        <x:v>angled paint brush, sash brush, paint applicator, painting tool</x:v>
       </x:c>
       <x:c r="J125" t="str">
         <x:v>Nour</x:v>
@@ -7465,8 +7469,8 @@
       <x:c r="H126" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I126" t="str">
-        <x:v>paint brush, application, professional</x:v>
+      <x:c r="I126" s="15" t="str">
+        <x:v>paint brush, paint applicator, painting tool, bristle brush</x:v>
       </x:c>
       <x:c r="J126" t="str">
         <x:v>AllPro</x:v>
@@ -7514,8 +7518,8 @@
       <x:c r="H127" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I127" t="str">
-        <x:v>roller cover, paint application, refill</x:v>
+      <x:c r="I127" s="15" t="str">
+        <x:v>paint roller cover, paint roller refill, paint applicator, painting tool, microfiber roller cover</x:v>
       </x:c>
       <x:c r="J127" t="str">
         <x:v>AllPro</x:v>
@@ -7563,8 +7567,8 @@
       <x:c r="H128" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I128" t="str">
-        <x:v>roller cover, paint application, refill</x:v>
+      <x:c r="I128" s="15" t="str">
+        <x:v>paint roller cover, paint roller refill, paint applicator, painting tool, microfiber roller cover</x:v>
       </x:c>
       <x:c r="J128" t="str">
         <x:v>AllPro</x:v>
@@ -7612,8 +7616,8 @@
       <x:c r="H129" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I129" t="str">
-        <x:v>roller cover, paint application, refill</x:v>
+      <x:c r="I129" s="15" t="str">
+        <x:v>paint roller cover, paint roller refill, paint applicator, painting tool, microfiber roller cover</x:v>
       </x:c>
       <x:c r="J129" t="str">
         <x:v>AllPro</x:v>
@@ -7661,8 +7665,8 @@
       <x:c r="H130" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I130" t="str">
-        <x:v>roller cover, paint application, refill</x:v>
+      <x:c r="I130" s="15" t="str">
+        <x:v>paint roller cover, paint roller refill, paint applicator, painting tool, microfiber roller cover</x:v>
       </x:c>
       <x:c r="J130" t="str">
         <x:v>AllPro</x:v>
@@ -7710,8 +7714,8 @@
       <x:c r="H131" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I131" t="str">
-        <x:v>roller cover, paint application, refill</x:v>
+      <x:c r="I131" s="15" t="str">
+        <x:v>paint roller cover, paint roller refill, paint applicator, painting tool</x:v>
       </x:c>
       <x:c r="J131" t="str">
         <x:v>Nour</x:v>
@@ -7759,8 +7763,8 @@
       <x:c r="H132" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I132" t="str">
-        <x:v>roller cover, paint application, refill</x:v>
+      <x:c r="I132" s="15" t="str">
+        <x:v>paint roller cover, paint roller refill, paint applicator, painting tool, microfiber roller cover</x:v>
       </x:c>
       <x:c r="J132" t="str">
         <x:v>Nour</x:v>
@@ -7808,8 +7812,8 @@
       <x:c r="H133" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I133" t="str">
-        <x:v>roller cover, paint application, refill</x:v>
+      <x:c r="I133" s="15" t="str">
+        <x:v>paint roller cover, paint roller refill, paint applicator, painting tool, microfiber roller cover</x:v>
       </x:c>
       <x:c r="J133" t="str">
         <x:v>Nour</x:v>
@@ -7857,8 +7861,8 @@
       <x:c r="H134" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I134" t="str">
-        <x:v>roller cover, paint application, refill</x:v>
+      <x:c r="I134" s="15" t="str">
+        <x:v>paint roller cover, paint roller refill, paint applicator, painting tool, microfiber roller cover</x:v>
       </x:c>
       <x:c r="J134" t="str">
         <x:v>Nour</x:v>
@@ -7906,8 +7910,8 @@
       <x:c r="H135" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I135" t="str">
-        <x:v>roller cover, paint application, refill</x:v>
+      <x:c r="I135" s="15" t="str">
+        <x:v>paint roller cover, paint roller refill, paint applicator, painting tool, loop roller cover, textured coating roller</x:v>
       </x:c>
       <x:c r="J135" t="str">
         <x:v>AllPro</x:v>
@@ -7955,8 +7959,8 @@
       <x:c r="H136" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I136" t="str">
-        <x:v>roller cover, paint application, refill</x:v>
+      <x:c r="I136" s="15" t="str">
+        <x:v>paint roller frame, wide roller frame, roller handle, paint applicator</x:v>
       </x:c>
       <x:c r="J136" t="str">
         <x:v>Nour</x:v>
@@ -8004,8 +8008,8 @@
       <x:c r="H137" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I137" t="str">
-        <x:v>roller frame, paint application, tool</x:v>
+      <x:c r="I137" s="15" t="str">
+        <x:v>paint roller frame, roller handle, paint applicator, painting tool</x:v>
       </x:c>
       <x:c r="J137" t="str">
         <x:v>AllPro</x:v>
@@ -8053,8 +8057,8 @@
       <x:c r="H138" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I138" t="str">
-        <x:v>squeegee, floor coating, application</x:v>
+      <x:c r="I138" s="15" t="str">
+        <x:v>coating squeegee, floor coating applicator, rubber blade, painting tool</x:v>
       </x:c>
       <x:c r="J138" t="str">
         <x:v>Nour</x:v>
@@ -8102,8 +8106,8 @@
       <x:c r="H139" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I139" t="str">
-        <x:v>roller frame, paint application, tool</x:v>
+      <x:c r="I139" s="15" t="str">
+        <x:v>spiked roller, floor coating tool, bubble-removal roller, coating applicator</x:v>
       </x:c>
       <x:c r="J139" t="str">
         <x:v>Nour</x:v>
@@ -8151,8 +8155,8 @@
       <x:c r="H140" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I140" t="str">
-        <x:v>squeegee, floor coating, application</x:v>
+      <x:c r="I140" s="15" t="str">
+        <x:v>coating squeegee, floor coating applicator, rubber blade, painting tool</x:v>
       </x:c>
       <x:c r="J140" t="str">
         <x:v>Nour</x:v>
@@ -8200,8 +8204,8 @@
       <x:c r="H141" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I141" t="str">
-        <x:v>squeegee, floor coating, application</x:v>
+      <x:c r="I141" s="15" t="str">
+        <x:v>coating squeegee, floor coating applicator, rubber blade, painting tool</x:v>
       </x:c>
       <x:c r="J141" t="str">
         <x:v>Nour</x:v>
@@ -8249,8 +8253,8 @@
       <x:c r="H142" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Clothing &amp; Safety</x:v>
       </x:c>
-      <x:c r="I142" t="str">
-        <x:v>spiked shoes, epoxy flooring, self-leveling</x:v>
+      <x:c r="I142" s="15" t="str">
+        <x:v>spiked shoes, floor coating footwear, epoxy application shoes, painting tool</x:v>
       </x:c>
       <x:c r="J142" t="str">
         <x:v>AllPro</x:v>
@@ -8298,8 +8302,8 @@
       <x:c r="H143" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I143" t="str">
-        <x:v>roller frame, paint application, tool</x:v>
+      <x:c r="I143" s="15" t="str">
+        <x:v>spiked roller, floor coating tool, bubble-removal roller, coating applicator</x:v>
       </x:c>
       <x:c r="J143" t="str">
         <x:v>Nour</x:v>
@@ -8347,8 +8351,8 @@
       <x:c r="H144" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I144" t="str">
-        <x:v>paint tray, paint application, tool</x:v>
+      <x:c r="I144" s="15" t="str">
+        <x:v>paint tray, paint container, painting accessory, paint roller tray</x:v>
       </x:c>
       <x:c r="J144" t="str">
         <x:v>AllPro</x:v>
@@ -8396,8 +8400,8 @@
       <x:c r="H145" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I145" t="str">
-        <x:v>paint brush, application, professional</x:v>
+      <x:c r="I145" s="15" t="str">
+        <x:v>deck stain brush, wide paint brush, wood finish applicator, painting tool</x:v>
       </x:c>
       <x:c r="J145" t="str">
         <x:v>Nour</x:v>
@@ -8445,8 +8449,8 @@
       <x:c r="H146" t="str">
         <x:v>Paints &gt; Stains &amp; Varnishes</x:v>
       </x:c>
-      <x:c r="I146" t="str">
-        <x:v>wiping stain, wood stain, interior wood</x:v>
+      <x:c r="I146" s="15" t="str">
+        <x:v>wiping stain, wood stain, wood finish, solvent-based wood stain</x:v>
       </x:c>
       <x:c r="J146" t="str">
         <x:v>Old Masters</x:v>
@@ -8500,8 +8504,8 @@
       <x:c r="H147" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I147" t="str">
-        <x:v>wood graining, decorative tool, faux finish</x:v>
+      <x:c r="I147" s="15" t="str">
+        <x:v>wood graining tool, decorative painting tool, texture applicator, painting tool</x:v>
       </x:c>
       <x:c r="J147" t="str">
         <x:v>Old Masters</x:v>
@@ -8549,8 +8553,8 @@
       <x:c r="H148" t="str">
         <x:v>Paints &gt; Stains &amp; Varnishes</x:v>
       </x:c>
-      <x:c r="I148" t="str">
-        <x:v>wood conditioner, pre-stain prep, wood finishing</x:v>
+      <x:c r="I148" s="15" t="str">
+        <x:v>wood conditioner, pre-stain treatment, wood preparation product, wood finishing basecoat</x:v>
       </x:c>
       <x:c r="J148" t="str">
         <x:v>Old Masters</x:v>
@@ -8604,8 +8608,8 @@
       <x:c r="H149" t="str">
         <x:v>Paints &gt; Stains &amp; Varnishes</x:v>
       </x:c>
-      <x:c r="I149" t="str">
-        <x:v>clear finish, interior exterior, wood protection</x:v>
+      <x:c r="I149" s="15" t="str">
+        <x:v>clear protective finish, water-based clear coat, interior and exterior finish, wood finish</x:v>
       </x:c>
       <x:c r="J149" t="str">
         <x:v>Old Masters</x:v>
@@ -8659,8 +8663,8 @@
       <x:c r="H150" t="str">
         <x:v>Paints &gt; Stains &amp; Varnishes</x:v>
       </x:c>
-      <x:c r="I150" t="str">
-        <x:v>water-based stain, wood stain, low odor</x:v>
+      <x:c r="I150" s="15" t="str">
+        <x:v>water-based wood stain, wood stain, interior wood finish, water-based finish</x:v>
       </x:c>
       <x:c r="J150" t="str">
         <x:v>Old Masters</x:v>
@@ -8714,8 +8718,8 @@
       <x:c r="H151" t="str">
         <x:v>Paints &gt; Stains &amp; Varnishes</x:v>
       </x:c>
-      <x:c r="I151" t="str">
-        <x:v>gel stain, wood stain, interior wood</x:v>
+      <x:c r="I151" s="15" t="str">
+        <x:v>gel stain, wood stain, thick-bodied stain, wood finish</x:v>
       </x:c>
       <x:c r="J151" t="str">
         <x:v>Old Masters</x:v>
@@ -8769,8 +8773,8 @@
       <x:c r="H152" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I152" t="str">
-        <x:v>paint brush, application, professional</x:v>
+      <x:c r="I152" s="15" t="str">
+        <x:v>paint pail, paint container, mixing container, painting accessory</x:v>
       </x:c>
       <x:c r="J152" t="str">
         <x:v>Wooster</x:v>
@@ -8818,8 +8822,8 @@
       <x:c r="H153" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I153" t="str">
-        <x:v>paint pail, hand-held, tool</x:v>
+      <x:c r="I153" s="15" t="str">
+        <x:v>paint pail liner, disposable pail liner, paint container accessory, painting accessory</x:v>
       </x:c>
       <x:c r="J153" t="str">
         <x:v>Wooster</x:v>
@@ -8867,8 +8871,8 @@
       <x:c r="H154" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I154" t="str">
-        <x:v>roller frame, paint application, tool</x:v>
+      <x:c r="I154" s="15" t="str">
+        <x:v>paint roller frame, roller handle, paint applicator, painting tool</x:v>
       </x:c>
       <x:c r="J154" t="str">
         <x:v>Wooster</x:v>
@@ -8916,8 +8920,8 @@
       <x:c r="H155" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I155" t="str">
-        <x:v>extension pole, painting tool, reach</x:v>
+      <x:c r="I155" s="15" t="str">
+        <x:v>paint roller extension pole, telescoping pole, paint applicator accessory, painting tool</x:v>
       </x:c>
       <x:c r="J155" t="str">
         <x:v>Wooster</x:v>
@@ -8965,8 +8969,8 @@
       <x:c r="H156" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I156" t="str">
-        <x:v>extension pole, painting tool, reach</x:v>
+      <x:c r="I156" s="15" t="str">
+        <x:v>paint roller extension pole, telescoping pole, paint applicator accessory, painting tool</x:v>
       </x:c>
       <x:c r="J156" t="str">
         <x:v>Wooster</x:v>
@@ -9014,8 +9018,8 @@
       <x:c r="H157" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I157" t="str">
-        <x:v>roller frame, paint application, tool</x:v>
+      <x:c r="I157" s="15" t="str">
+        <x:v>paint roller frame, roller handle, paint applicator, painting tool</x:v>
       </x:c>
       <x:c r="J157" t="str">
         <x:v>Wooster</x:v>
@@ -9063,8 +9067,8 @@
       <x:c r="H158" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I158" t="str">
-        <x:v>painting tool, accessory, application</x:v>
+      <x:c r="I158" s="15" t="str">
+        <x:v>extension pole maintenance kit, roller pole repair kit, painting tool accessory, replacement hardware</x:v>
       </x:c>
       <x:c r="J158" t="str">
         <x:v>Wooster</x:v>
@@ -9112,8 +9116,8 @@
       <x:c r="H159" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I159" t="str">
-        <x:v>paint tray, paint application, tool</x:v>
+      <x:c r="I159" s="15" t="str">
+        <x:v>paint tray, paint container, painting accessory, paint roller tray</x:v>
       </x:c>
       <x:c r="J159" t="str">
         <x:v>Wooster</x:v>
@@ -9161,8 +9165,8 @@
       <x:c r="H160" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I160" t="str">
-        <x:v>paint tray, paint application, tool</x:v>
+      <x:c r="I160" s="15" t="str">
+        <x:v>paint roller tray, wide paint tray, paint container, painting accessory</x:v>
       </x:c>
       <x:c r="J160" t="str">
         <x:v>Wooster</x:v>
@@ -9210,8 +9214,8 @@
       <x:c r="H161" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I161" t="str">
-        <x:v>paint tray, paint application, tool</x:v>
+      <x:c r="I161" s="15" t="str">
+        <x:v>paint tray, paint container, painting accessory, paint tray liner</x:v>
       </x:c>
       <x:c r="J161" t="str">
         <x:v>Wooster</x:v>
@@ -9259,8 +9263,8 @@
       <x:c r="H162" t="str">
         <x:v>Paints &gt; Aerosols</x:v>
       </x:c>
-      <x:c r="I162" t="str">
-        <x:v>primer, spray, sealer</x:v>
+      <x:c r="I162" s="15" t="str">
+        <x:v>spray primer, aerosol primer, primer, surface preparation coating, stain-blocking primer, odour-blocking primer, primer sealer</x:v>
       </x:c>
       <x:c r="J162" t="str">
         <x:v>Zinsser</x:v>
@@ -9314,8 +9318,8 @@
       <x:c r="H163" t="str">
         <x:v>Paints &gt; Primers</x:v>
       </x:c>
-      <x:c r="I163" t="str">
-        <x:v>primer, oil-based, stain blocking</x:v>
+      <x:c r="I163" s="15" t="str">
+        <x:v>primer, primer sealer, surface preparation coating, basecoat</x:v>
       </x:c>
       <x:c r="J163" t="str">
         <x:v>Zinsser</x:v>
@@ -9369,8 +9373,8 @@
       <x:c r="H164" t="str">
         <x:v>Paints &gt; Aerosols</x:v>
       </x:c>
-      <x:c r="I164" t="str">
-        <x:v>primer, spray, sealer</x:v>
+      <x:c r="I164" s="15" t="str">
+        <x:v>spray primer, aerosol primer, primer, surface preparation coating, primer sealer, basecoat</x:v>
       </x:c>
       <x:c r="J164" t="str">
         <x:v>Zinsser</x:v>
@@ -9424,8 +9428,8 @@
       <x:c r="H165" t="str">
         <x:v>Paints &gt; Primers</x:v>
       </x:c>
-      <x:c r="I165" t="str">
-        <x:v>primer, shellac, stain blocking</x:v>
+      <x:c r="I165" s="15" t="str">
+        <x:v>shellac primer, stain-blocking primer, primer sealer, interior primer, primer, surface preparation coating, basecoat</x:v>
       </x:c>
       <x:c r="J165" t="str">
         <x:v>Zinsser</x:v>
@@ -9479,8 +9483,8 @@
       <x:c r="H166" t="str">
         <x:v>Paints &gt; Aerosols</x:v>
       </x:c>
-      <x:c r="I166" t="str">
-        <x:v>primer, spray, sealer</x:v>
+      <x:c r="I166" s="15" t="str">
+        <x:v>spray primer, aerosol primer, primer, surface preparation coating, shellac primer, stain-blocking primer, primer sealer, interior primer</x:v>
       </x:c>
       <x:c r="J166" t="str">
         <x:v>Zinsser</x:v>
@@ -9534,8 +9538,8 @@
       <x:c r="H167" t="str">
         <x:v>Paints &gt; Primers</x:v>
       </x:c>
-      <x:c r="I167" t="str">
-        <x:v>primer, water-based, multi-surface</x:v>
+      <x:c r="I167" s="15" t="str">
+        <x:v>primer, primer sealer, surface preparation coating, basecoat</x:v>
       </x:c>
       <x:c r="J167" t="str">
         <x:v>Zinsser</x:v>
@@ -9589,8 +9593,8 @@
       <x:c r="H168" t="str">
         <x:v>Paints &gt; Aerosols</x:v>
       </x:c>
-      <x:c r="I168" t="str">
-        <x:v>rust paint, metal protection, oil-based</x:v>
+      <x:c r="I168" s="15" t="str">
+        <x:v>rust-preventive paint, metal paint, protective enamel, anti-corrosion coating</x:v>
       </x:c>
       <x:c r="J168" t="str">
         <x:v>Tremclad</x:v>
@@ -9644,8 +9648,8 @@
       <x:c r="H169" t="str">
         <x:v>Paints &gt; Specialty Paints</x:v>
       </x:c>
-      <x:c r="I169" t="str">
-        <x:v>high heat paint, metal protection, heat resistant</x:v>
+      <x:c r="I169" s="15" t="str">
+        <x:v>heat-resistant paint, high-temperature coating, metal paint, protective coating</x:v>
       </x:c>
       <x:c r="J169" t="str">
         <x:v>Tremclad</x:v>
@@ -9696,8 +9700,8 @@
       <x:c r="H170" t="str">
         <x:v>Paints &gt; Specialty Paints</x:v>
       </x:c>
-      <x:c r="I170" t="str">
-        <x:v>rust paint, metal protection, oil-based</x:v>
+      <x:c r="I170" s="15" t="str">
+        <x:v>rust-preventive paint, metal paint, protective enamel, anti-corrosion coating</x:v>
       </x:c>
       <x:c r="J170" t="str">
         <x:v>Tremclad</x:v>
@@ -9748,8 +9752,8 @@
       <x:c r="H171" t="str">
         <x:v>Paints &gt; Specialty Paints</x:v>
       </x:c>
-      <x:c r="I171" t="str">
-        <x:v>rust paint, metal protection, oil-based</x:v>
+      <x:c r="I171" s="15" t="str">
+        <x:v>rust-preventive paint, metal paint, protective enamel, anti-corrosion coating</x:v>
       </x:c>
       <x:c r="J171" t="str">
         <x:v>Tremclad</x:v>
@@ -9800,8 +9804,8 @@
       <x:c r="H172" t="str">
         <x:v>Paints &gt; Specialty Paints</x:v>
       </x:c>
-      <x:c r="I172" t="str">
-        <x:v>rust paint, metal protection, oil-based</x:v>
+      <x:c r="I172" s="15" t="str">
+        <x:v>rust-preventive paint, metal paint, protective enamel, anti-corrosion coating</x:v>
       </x:c>
       <x:c r="J172" t="str">
         <x:v>Tremclad</x:v>
@@ -9852,8 +9856,8 @@
       <x:c r="H173" t="str">
         <x:v>Paints &gt; Specialty Paints</x:v>
       </x:c>
-      <x:c r="I173" t="str">
-        <x:v>rust paint, metal protection, oil-based</x:v>
+      <x:c r="I173" s="15" t="str">
+        <x:v>rust-preventive paint, metal paint, protective enamel, anti-corrosion coating</x:v>
       </x:c>
       <x:c r="J173" t="str">
         <x:v>Tremclad</x:v>
@@ -9904,8 +9908,8 @@
       <x:c r="H174" t="str">
         <x:v>Paints &gt; Specialty Paints</x:v>
       </x:c>
-      <x:c r="I174" t="str">
-        <x:v>rust paint, metal protection, oil-based</x:v>
+      <x:c r="I174" s="15" t="str">
+        <x:v>rust-preventive paint, metal paint, protective enamel, anti-corrosion coating</x:v>
       </x:c>
       <x:c r="J174" t="str">
         <x:v>Tremclad</x:v>
@@ -9956,8 +9960,8 @@
       <x:c r="H175" t="str">
         <x:v>Paints &gt; Specialty Paints</x:v>
       </x:c>
-      <x:c r="I175" t="str">
-        <x:v>rust paint, metal protection, oil-based</x:v>
+      <x:c r="I175" s="15" t="str">
+        <x:v>rust-preventive paint, metal paint, protective enamel, anti-corrosion coating</x:v>
       </x:c>
       <x:c r="J175" t="str">
         <x:v>Tremclad</x:v>
@@ -10008,8 +10012,8 @@
       <x:c r="H176" t="str">
         <x:v>Paints &gt; Specialty Paints</x:v>
       </x:c>
-      <x:c r="I176" t="str">
-        <x:v>rust paint, metal protection, oil-based</x:v>
+      <x:c r="I176" s="15" t="str">
+        <x:v>rust-preventive paint, metal paint, protective enamel, anti-corrosion coating</x:v>
       </x:c>
       <x:c r="J176" t="str">
         <x:v>Tremclad</x:v>
@@ -10060,8 +10064,8 @@
       <x:c r="H177" t="str">
         <x:v>Paints &gt; Specialty Paints</x:v>
       </x:c>
-      <x:c r="I177" t="str">
-        <x:v>rust paint, metal protection, oil-based</x:v>
+      <x:c r="I177" s="15" t="str">
+        <x:v>rust-preventive paint, metal paint, protective enamel, anti-corrosion coating</x:v>
       </x:c>
       <x:c r="J177" t="str">
         <x:v>Tremclad</x:v>
@@ -10112,8 +10116,8 @@
       <x:c r="H178" t="str">
         <x:v>Paints &gt; Specialty Paints</x:v>
       </x:c>
-      <x:c r="I178" t="str">
-        <x:v>rust paint, metal protection, oil-based</x:v>
+      <x:c r="I178" s="15" t="str">
+        <x:v>rust-preventive paint, metal paint, protective enamel, anti-corrosion coating</x:v>
       </x:c>
       <x:c r="J178" t="str">
         <x:v>Tremclad</x:v>
@@ -10164,8 +10168,8 @@
       <x:c r="H179" t="str">
         <x:v>Paints &gt; Specialty Paints</x:v>
       </x:c>
-      <x:c r="I179" t="str">
-        <x:v>rust paint, metal protection, oil-based</x:v>
+      <x:c r="I179" s="15" t="str">
+        <x:v>rust-preventive paint, metal paint, protective enamel, anti-corrosion coating</x:v>
       </x:c>
       <x:c r="J179" t="str">
         <x:v>Tremclad</x:v>
@@ -10216,8 +10220,8 @@
       <x:c r="H180" t="str">
         <x:v>Paints &gt; Specialty Paints</x:v>
       </x:c>
-      <x:c r="I180" t="str">
-        <x:v>rust paint, metal protection, oil-based</x:v>
+      <x:c r="I180" s="15" t="str">
+        <x:v>rust-preventive paint, metal paint, protective enamel, anti-corrosion coating</x:v>
       </x:c>
       <x:c r="J180" t="str">
         <x:v>Tremclad</x:v>
@@ -10268,8 +10272,8 @@
       <x:c r="H181" t="str">
         <x:v>Paints &gt; Specialty Paints</x:v>
       </x:c>
-      <x:c r="I181" t="str">
-        <x:v>rust paint, metal protection, oil-based</x:v>
+      <x:c r="I181" s="15" t="str">
+        <x:v>rust-preventive paint, metal paint, protective enamel, anti-corrosion coating</x:v>
       </x:c>
       <x:c r="J181" t="str">
         <x:v>Tremclad</x:v>
@@ -10320,8 +10324,8 @@
       <x:c r="H182" t="str">
         <x:v>Paints &gt; Specialty Paints</x:v>
       </x:c>
-      <x:c r="I182" t="str">
-        <x:v>rust paint, metal protection, oil-based</x:v>
+      <x:c r="I182" s="15" t="str">
+        <x:v>rust-preventive paint, metal paint, protective enamel, anti-corrosion coating</x:v>
       </x:c>
       <x:c r="J182" t="str">
         <x:v>Tremclad</x:v>
@@ -10372,8 +10376,8 @@
       <x:c r="H183" t="str">
         <x:v>Paints &gt; Specialty Paints</x:v>
       </x:c>
-      <x:c r="I183" t="str">
-        <x:v>rust paint, metal protection, oil-based</x:v>
+      <x:c r="I183" s="15" t="str">
+        <x:v>rust-preventive paint, metal paint, protective enamel, anti-corrosion coating</x:v>
       </x:c>
       <x:c r="J183" t="str">
         <x:v>Tremclad</x:v>
@@ -10424,8 +10428,8 @@
       <x:c r="H184" t="str">
         <x:v>Paints &gt; Specialty Paints</x:v>
       </x:c>
-      <x:c r="I184" t="str">
-        <x:v>rust paint, metal protection, oil-based</x:v>
+      <x:c r="I184" s="15" t="str">
+        <x:v>rust-preventive paint, metal paint, protective enamel, anti-corrosion coating</x:v>
       </x:c>
       <x:c r="J184" t="str">
         <x:v>Tremclad</x:v>
@@ -10476,8 +10480,8 @@
       <x:c r="H185" t="str">
         <x:v>Paints &gt; Specialty Paints</x:v>
       </x:c>
-      <x:c r="I185" t="str">
-        <x:v>rust paint, metal protection, oil-based</x:v>
+      <x:c r="I185" s="15" t="str">
+        <x:v>rust-preventive paint, metal paint, protective enamel, anti-corrosion coating</x:v>
       </x:c>
       <x:c r="J185" t="str">
         <x:v>Tremclad</x:v>
@@ -10528,8 +10532,8 @@
       <x:c r="H186" t="str">
         <x:v>Paints &gt; Specialty Paints</x:v>
       </x:c>
-      <x:c r="I186" t="str">
-        <x:v>rust paint, metal protection, oil-based</x:v>
+      <x:c r="I186" s="15" t="str">
+        <x:v>rust-preventive paint, metal paint, protective enamel, anti-corrosion coating</x:v>
       </x:c>
       <x:c r="J186" t="str">
         <x:v>Tremclad</x:v>
@@ -10580,8 +10584,8 @@
       <x:c r="H187" t="str">
         <x:v>Paints &gt; Primers</x:v>
       </x:c>
-      <x:c r="I187" t="str">
-        <x:v>primer, water-based, multi-surface</x:v>
+      <x:c r="I187" s="15" t="str">
+        <x:v>mould-resistant primer, stain-blocking primer, interior primer, primer sealer, primer, surface preparation coating, basecoat</x:v>
       </x:c>
       <x:c r="J187" t="str">
         <x:v>Zinsser</x:v>
@@ -10635,8 +10639,8 @@
       <x:c r="H188" t="str">
         <x:v>Paints &gt; Aerosols</x:v>
       </x:c>
-      <x:c r="I188" t="str">
-        <x:v>primer, spray, sealer</x:v>
+      <x:c r="I188" s="15" t="str">
+        <x:v>spray primer, aerosol primer, primer, surface preparation coating, primer sealer, basecoat</x:v>
       </x:c>
       <x:c r="J188" t="str">
         <x:v>Zinsser</x:v>
@@ -10690,8 +10694,8 @@
       <x:c r="H189" t="str">
         <x:v>Paints &gt; Specialty Paints</x:v>
       </x:c>
-      <x:c r="I189" t="str">
-        <x:v>rust paint, metal protection, oil-based</x:v>
+      <x:c r="I189" s="15" t="str">
+        <x:v>rust-preventive paint, metal paint, protective enamel, anti-corrosion coating</x:v>
       </x:c>
       <x:c r="J189" t="str">
         <x:v>Tremclad</x:v>
@@ -10742,8 +10746,8 @@
       <x:c r="H190" t="str">
         <x:v>Paints &gt; Specialty Paints</x:v>
       </x:c>
-      <x:c r="I190" t="str">
-        <x:v>rust paint, metal protection, oil-based</x:v>
+      <x:c r="I190" s="15" t="str">
+        <x:v>rust-preventive paint, metal paint, protective enamel, anti-corrosion coating</x:v>
       </x:c>
       <x:c r="J190" t="str">
         <x:v>Tremclad</x:v>
@@ -10794,8 +10798,8 @@
       <x:c r="H191" t="str">
         <x:v>Paints &gt; Primers</x:v>
       </x:c>
-      <x:c r="I191" t="str">
-        <x:v>primer, oil-based, stain blocking</x:v>
+      <x:c r="I191" s="15" t="str">
+        <x:v>stain-blocking primer, odour-blocking primer, primer sealer, surface preparation coating</x:v>
       </x:c>
       <x:c r="J191" t="str">
         <x:v>Zinsser</x:v>
@@ -10849,8 +10853,8 @@
       <x:c r="H192" t="str">
         <x:v>Paints &gt; Primers</x:v>
       </x:c>
-      <x:c r="I192" t="str">
-        <x:v>primer, water-based, multi-surface</x:v>
+      <x:c r="I192" s="15" t="str">
+        <x:v>primer, primer sealer, surface preparation coating, basecoat</x:v>
       </x:c>
       <x:c r="J192" t="str">
         <x:v>Zinsser</x:v>
@@ -10904,8 +10908,8 @@
       <x:c r="H193" t="str">
         <x:v>Paints &gt; Specialty Paints</x:v>
       </x:c>
-      <x:c r="I193" t="str">
-        <x:v>rust paint, metal protection, oil-based</x:v>
+      <x:c r="I193" s="15" t="str">
+        <x:v>rust-preventive paint, metal paint, protective enamel, anti-corrosion coating</x:v>
       </x:c>
       <x:c r="J193" t="str">
         <x:v>Tremclad</x:v>
@@ -10956,8 +10960,8 @@
       <x:c r="H194" t="str">
         <x:v>Paints &gt; Specialty Paints</x:v>
       </x:c>
-      <x:c r="I194" t="str">
-        <x:v>rust paint, metal protection, oil-based</x:v>
+      <x:c r="I194" s="15" t="str">
+        <x:v>rust-preventive paint, metal paint, protective enamel, anti-corrosion coating</x:v>
       </x:c>
       <x:c r="J194" t="str">
         <x:v>Tremclad</x:v>
@@ -11008,8 +11012,8 @@
       <x:c r="H195" t="str">
         <x:v>Paints &gt; Specialty Paints</x:v>
       </x:c>
-      <x:c r="I195" t="str">
-        <x:v>rust paint, metal protection, oil-based</x:v>
+      <x:c r="I195" s="15" t="str">
+        <x:v>rust-preventive paint, metal paint, protective enamel, anti-corrosion coating</x:v>
       </x:c>
       <x:c r="J195" t="str">
         <x:v>Tremclad</x:v>
@@ -11060,8 +11064,8 @@
       <x:c r="H196" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I196" t="str">
-        <x:v>painters tape, masking tape, washi tape, blue dolphin, axis apt</x:v>
+      <x:c r="I196" s="15" t="str">
+        <x:v>masking tape, painter's tape, pressure-sensitive tape, painting accessory</x:v>
       </x:c>
       <x:c r="J196" t="str">
         <x:v>Blue Dolphin</x:v>
@@ -11109,8 +11113,8 @@
       <x:c r="H197" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I197" t="str">
-        <x:v>painters tape, masking tape, washi tape, blue dolphin, axis apt</x:v>
+      <x:c r="I197" s="15" t="str">
+        <x:v>masking tape, painter's tape, pressure-sensitive tape, painting accessory</x:v>
       </x:c>
       <x:c r="J197" t="str">
         <x:v>Blue Dolphin</x:v>
@@ -11158,8 +11162,8 @@
       <x:c r="H198" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I198" t="str">
-        <x:v>painters tape, masking tape, washi tape, blue dolphin, axis apt</x:v>
+      <x:c r="I198" s="15" t="str">
+        <x:v>masking tape, painter's tape, pressure-sensitive tape, painting accessory</x:v>
       </x:c>
       <x:c r="J198" t="str">
         <x:v>Blue Dolphin</x:v>
@@ -11207,8 +11211,8 @@
       <x:c r="H199" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I199" t="str">
-        <x:v>painters tape, masking tape, washi tape, blue dolphin, axis apt</x:v>
+      <x:c r="I199" s="15" t="str">
+        <x:v>masking tape, painter's tape, pressure-sensitive tape, painting accessory</x:v>
       </x:c>
       <x:c r="J199" t="str">
         <x:v>Blue Dolphin</x:v>
@@ -11256,8 +11260,8 @@
       <x:c r="H200" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I200" t="str">
-        <x:v>extension pole, paint pole, everlok, roller pole</x:v>
+      <x:c r="I200" s="15" t="str">
+        <x:v>paint roller extension pole, telescoping pole, paint applicator accessory, painting tool</x:v>
       </x:c>
       <x:c r="J200" t="str">
         <x:v>Everlok</x:v>
@@ -11305,8 +11309,8 @@
       <x:c r="H201" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I201" t="str">
-        <x:v>extension pole, paint pole, everlok, roller pole</x:v>
+      <x:c r="I201" s="15" t="str">
+        <x:v>paint roller extension pole, telescoping pole, paint applicator accessory, painting tool</x:v>
       </x:c>
       <x:c r="J201" t="str">
         <x:v>Everlok</x:v>
@@ -11354,8 +11358,8 @@
       <x:c r="H202" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I202" t="str">
-        <x:v>roller frame, mini roller frame, painting tools</x:v>
+      <x:c r="I202" s="15" t="str">
+        <x:v>paint roller frame, roller handle, paint applicator, painting tool</x:v>
       </x:c>
       <x:c r="J202" t="str">
         <x:v>Pintar</x:v>
@@ -11403,8 +11407,8 @@
       <x:c r="H203" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I203" t="str">
-        <x:v>extension pole, paint pole, everlok, roller pole</x:v>
+      <x:c r="I203" s="15" t="str">
+        <x:v>paint roller extension pole, telescoping pole, paint applicator accessory, painting tool</x:v>
       </x:c>
       <x:c r="J203" t="str">
         <x:v>Everlok</x:v>
@@ -11452,8 +11456,8 @@
       <x:c r="H204" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I204" t="str">
-        <x:v>extension pole, paint pole, everlok, roller pole</x:v>
+      <x:c r="I204" s="15" t="str">
+        <x:v>paint roller extension pole, telescoping pole, paint applicator accessory, painting tool</x:v>
       </x:c>
       <x:c r="J204" t="str">
         <x:v>Everlok</x:v>
@@ -11501,8 +11505,8 @@
       <x:c r="H205" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I205" t="str">
-        <x:v>roller frame, wire cage frame, painting tools</x:v>
+      <x:c r="I205" s="15" t="str">
+        <x:v>paint roller frame, roller handle, paint applicator, painting tool</x:v>
       </x:c>
       <x:c r="J205" t="str">
         <x:v>Pintar</x:v>
@@ -11550,8 +11554,8 @@
       <x:c r="H206" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I206" t="str">
-        <x:v>roller cover, mini roller, paint roller cover</x:v>
+      <x:c r="I206" s="15" t="str">
+        <x:v>paint roller cover, paint roller refill, paint applicator, painting tool</x:v>
       </x:c>
       <x:c r="J206" t="str">
         <x:v>Pintar</x:v>
@@ -11599,8 +11603,8 @@
       <x:c r="H207" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I207" t="str">
-        <x:v>wallpaper tools, vinyl trimmer, wallcovering trimmer, wallpaper installation, trimming tool</x:v>
+      <x:c r="I207" s="15" t="str">
+        <x:v>wallpaper trimmer, wallcovering cutting tool, installation tool, hand tool</x:v>
       </x:c>
       <x:c r="J207" t="str">
         <x:v>Advance Equipment</x:v>
@@ -11648,8 +11652,8 @@
       <x:c r="H208" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I208" t="str">
-        <x:v>wallpaper tools, pasting machine, qwikpaster, wallpaper adhesive, wallcovering installation</x:v>
+      <x:c r="I208" s="15" t="str">
+        <x:v>wallpaper pasting machine, wallcovering tool, adhesive applicator, installation equipment</x:v>
       </x:c>
       <x:c r="J208" t="str">
         <x:v>Advance Equipment</x:v>
@@ -11697,8 +11701,8 @@
       <x:c r="H209" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I209" t="str">
-        <x:v>pasting syringe, wallpaper repair, seam repair, wallpaper adhesive, wallcovering tools</x:v>
+      <x:c r="I209" s="15" t="str">
+        <x:v>adhesive syringe, wallpaper repair tool, wallcovering tool, adhesive applicator</x:v>
       </x:c>
       <x:c r="J209" t="str">
         <x:v>Advance Equipment</x:v>
@@ -11746,8 +11750,8 @@
       <x:c r="H210" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I210" t="str">
-        <x:v>corner roller, wallpaper roller, seam roller, wallcovering tools, wallpaper installation</x:v>
+      <x:c r="I210" s="15" t="str">
+        <x:v>corner roller, paint roller, paint applicator, painting tool</x:v>
       </x:c>
       <x:c r="J210" t="str">
         <x:v>Advance Equipment</x:v>
@@ -11795,8 +11799,8 @@
       <x:c r="H211" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I211" t="str">
-        <x:v>corner bead applicator, drywall tools, mud application, corner bead, finishing tools</x:v>
+      <x:c r="I211" s="15" t="str">
+        <x:v>corner bead applicator, drywall tool, adhesive applicator, installation tool</x:v>
       </x:c>
       <x:c r="J211" t="str">
         <x:v>Advance Equipment</x:v>
@@ -11844,8 +11848,8 @@
       <x:c r="H212" t="str">
         <x:v>Paints &gt; Stains &amp; Varnishes</x:v>
       </x:c>
-      <x:c r="I212" t="str">
-        <x:v>oil based varnish, hybrid varnish, floor varnish, semi-gloss finish</x:v>
+      <x:c r="I212" s="15" t="str">
+        <x:v>floor varnish, wood floor finish, clear wood finish, protective coating</x:v>
       </x:c>
       <x:c r="J212" t="str">
         <x:v>Saman</x:v>
@@ -11903,8 +11907,8 @@
       <x:c r="H213" t="str">
         <x:v>Paints &gt; Stains &amp; Varnishes</x:v>
       </x:c>
-      <x:c r="I213" t="str">
-        <x:v>wood stain, urban grey, 099, waterbased stain, interior wood finishing</x:v>
+      <x:c r="I213" s="15" t="str">
+        <x:v>water-based wood stain, wood stain, interior wood finish, water-based finish</x:v>
       </x:c>
       <x:c r="J213" t="str">
         <x:v>Saman</x:v>
@@ -11958,8 +11962,8 @@
       <x:c r="H214" t="str">
         <x:v>Paints &gt; Stains &amp; Varnishes</x:v>
       </x:c>
-      <x:c r="I214" t="str">
-        <x:v>dead flat varnish, clear finish, protective coating, waterbased varnish</x:v>
+      <x:c r="I214" s="15" t="str">
+        <x:v>flat varnish, water-based varnish, clear wood finish, protective coating</x:v>
       </x:c>
       <x:c r="J214" t="str">
         <x:v>Saman</x:v>
@@ -12013,8 +12017,8 @@
       <x:c r="H215" t="str">
         <x:v>Paints &gt; Stains &amp; Varnishes</x:v>
       </x:c>
-      <x:c r="I215" t="str">
-        <x:v>exterior clear coat, wood protection, uv protection, semi-gloss, waterbased finish</x:v>
+      <x:c r="I215" s="15" t="str">
+        <x:v>exterior varnish, water-based varnish, clear wood finish, uv-resistant finish, clear finish, protective coating, clear coat, wood finish</x:v>
       </x:c>
       <x:c r="J215" t="str">
         <x:v>Saman</x:v>
@@ -12072,8 +12076,8 @@
       <x:c r="H216" t="str">
         <x:v>Paints &gt; Stains &amp; Varnishes</x:v>
       </x:c>
-      <x:c r="I216" t="str">
-        <x:v>floor varnish, waterbased varnish, hardwood floors, semi-gloss finish</x:v>
+      <x:c r="I216" s="15" t="str">
+        <x:v>floor varnish, wood floor finish, clear wood finish, protective coating</x:v>
       </x:c>
       <x:c r="J216" t="str">
         <x:v>Saman</x:v>
@@ -12131,8 +12135,8 @@
       <x:c r="H217" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I217" t="str">
-        <x:v>tsp, surface cleaner, paint preparation, degreaser, heavy duty cleaner, biodegradable</x:v>
+      <x:c r="I217" s="15" t="str">
+        <x:v>tsp cleaner, surface preparation cleaner, degreaser, paint preparation chemical</x:v>
       </x:c>
       <x:c r="J217" t="str">
         <x:v>Swing</x:v>
@@ -12180,8 +12184,8 @@
       <x:c r="H218" t="str">
         <x:v>Paints &gt; Primers</x:v>
       </x:c>
-      <x:c r="I218" t="str">
-        <x:v>wallpaper primer, primer sealer, wallpaper pre-coat, universal primer, tintable primer</x:v>
+      <x:c r="I218" s="15" t="str">
+        <x:v>wallcovering primer, primer sealer, wall preparation coating, interior primer, primer, surface preparation coating, basecoat</x:v>
       </x:c>
       <x:c r="J218" t="str">
         <x:v>Swing</x:v>
@@ -12229,8 +12233,8 @@
       <x:c r="H219" t="str">
         <x:v>Paints &gt; Primers</x:v>
       </x:c>
-      <x:c r="I219" t="str">
-        <x:v>primer sealer, universal primer, prime plus, interior exterior primer, water based primer</x:v>
+      <x:c r="I219" s="15" t="str">
+        <x:v>primer, primer sealer, surface preparation coating, basecoat</x:v>
       </x:c>
       <x:c r="J219" t="str">
         <x:v>Swing</x:v>
@@ -12278,8 +12282,8 @@
       <x:c r="H220" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Cleaners &amp; Removers</x:v>
       </x:c>
-      <x:c r="I220" t="str">
-        <x:v>paint remover, varnish remover, stripper, heavy body gel, surface restoration</x:v>
+      <x:c r="I220" s="15" t="str">
+        <x:v>coating remover, paint remover, finish stripper, surface preparation chemical</x:v>
       </x:c>
       <x:c r="J220" t="str">
         <x:v>Circa 1850</x:v>
@@ -12327,8 +12331,8 @@
       <x:c r="H221" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Cleaners &amp; Removers</x:v>
       </x:c>
-      <x:c r="I221" t="str">
-        <x:v>furniture stripper, paint remover, varnish remover, wood restoration, furniture refinishing</x:v>
+      <x:c r="I221" s="15" t="str">
+        <x:v>coating remover, paint remover, finish stripper, surface preparation chemical</x:v>
       </x:c>
       <x:c r="J221" t="str">
         <x:v>Circa 1850</x:v>
@@ -12376,8 +12380,8 @@
       <x:c r="H222" t="str">
         <x:v>Commercial &amp; Industrial &gt; Epoxy</x:v>
       </x:c>
-      <x:c r="I222" t="str">
-        <x:v>polyaspartic coating, uv resistant coating, clear topcoat, epoxy flooring, garage floor coating, industrial coating</x:v>
+      <x:c r="I222" s="15" t="str">
+        <x:v>polyaspartic coating, clear floor coating, two-component coating, protective coating</x:v>
       </x:c>
       <x:c r="J222" t="str">
         <x:v>Zeraus</x:v>
@@ -12431,8 +12435,8 @@
       <x:c r="H223" t="str">
         <x:v>Commercial &amp; Industrial &gt; Epoxy</x:v>
       </x:c>
-      <x:c r="I223" t="str">
-        <x:v>epoxy adhesive, concrete repair, crack filler, structural epoxy, bonding gel, epoxy repair</x:v>
+      <x:c r="I223" s="15" t="str">
+        <x:v>epoxy adhesive, epoxy gel, two-part epoxy, structural adhesive</x:v>
       </x:c>
       <x:c r="J223" t="str">
         <x:v>Zeraus</x:v>
@@ -12480,8 +12484,8 @@
       <x:c r="H224" t="str">
         <x:v>Commercial &amp; Industrial &gt; Epoxy</x:v>
       </x:c>
-      <x:c r="I224" t="str">
-        <x:v>clear epoxy, epoxy coating, decorative flooring, flake floor coating, quartz flooring, countertop coating</x:v>
+      <x:c r="I224" s="15" t="str">
+        <x:v>clear epoxy coating, epoxy floor coating, two-part epoxy, protective coating</x:v>
       </x:c>
       <x:c r="J224" t="str">
         <x:v>Zeraus</x:v>
@@ -12529,8 +12533,8 @@
       <x:c r="H225" t="str">
         <x:v>Commercial &amp; Industrial &gt; Epoxy</x:v>
       </x:c>
-      <x:c r="I225" t="str">
-        <x:v>epoxy floor coating, industrial flooring, garage floor coating, commercial flooring, concrete coating, chemical resistant coating</x:v>
+      <x:c r="I225" s="15" t="str">
+        <x:v>epoxy floor coating, 100% solids epoxy, two-part epoxy, industrial floor coating</x:v>
       </x:c>
       <x:c r="J225" t="str">
         <x:v>Zeraus</x:v>
@@ -12582,8 +12586,8 @@
       <x:c r="H226" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I226" t="str">
-        <x:v>3m, 3m super77 spray adhesive, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I226" s="15" t="str">
+        <x:v>spray adhesive, aerosol adhesive, contact adhesive, multi-purpose glue</x:v>
       </x:c>
       <x:c r="J226" t="str">
         <x:v>3M</x:v>
@@ -12629,8 +12633,8 @@
       <x:c r="H227" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Clothing &amp; Safety</x:v>
       </x:c>
-      <x:c r="I227" t="str">
-        <x:v>3m, 3m multi-gas/vapour cartridge 6006, painting tools &amp; accessories, clothing &amp; safety</x:v>
+      <x:c r="I227" s="15" t="str">
+        <x:v>multi-gas cartridge, vapour cartridge, respirator cartridge, respiratory protection accessory</x:v>
       </x:c>
       <x:c r="J227" t="str">
         <x:v>3M</x:v>
@@ -12676,8 +12680,8 @@
       <x:c r="H228" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I228" t="str">
-        <x:v>3m, 3m scotch-brite general purpose hand pad 7447, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I228" s="15" t="str">
+        <x:v>abrasive hand pad, nonwoven abrasive, surface preparation pad, scuffing pad</x:v>
       </x:c>
       <x:c r="J228" t="str">
         <x:v>3M</x:v>
@@ -12731,8 +12735,8 @@
       <x:c r="H229" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Clothing &amp; Safety</x:v>
       </x:c>
-      <x:c r="I229" t="str">
-        <x:v>3m, 3m replacement lens covers, painting tools &amp; accessories, clothing &amp; safety</x:v>
+      <x:c r="I229" s="15" t="str">
+        <x:v>respirator lens cover, protective lens film, respirator accessory, face shield accessory</x:v>
       </x:c>
       <x:c r="J229" t="str">
         <x:v>3M</x:v>
@@ -12778,8 +12782,8 @@
       <x:c r="H230" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I230" t="str">
-        <x:v>3m, 3m new safe release blue 3m canad, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I230" s="15" t="str">
+        <x:v>masking tape, painter's tape, clean-release tape, painting accessory</x:v>
       </x:c>
       <x:c r="J230" t="str">
         <x:v>3M</x:v>
@@ -12825,8 +12829,8 @@
       <x:c r="H231" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I231" t="str">
-        <x:v>3m, 3m performance green masking tape, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I231" s="15" t="str">
+        <x:v>masking tape, painter's tape, pressure-sensitive tape, painting accessory</x:v>
       </x:c>
       <x:c r="J231" t="str">
         <x:v>3M</x:v>
@@ -12880,8 +12884,8 @@
       <x:c r="H232" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Clothing &amp; Safety</x:v>
       </x:c>
-      <x:c r="I232" t="str">
-        <x:v>3m, 3m filter p100, painting tools &amp; accessories, clothing &amp; safety</x:v>
+      <x:c r="I232" s="15" t="str">
+        <x:v>p100 filter, particulate filter, respirator filter, respiratory protection accessory</x:v>
       </x:c>
       <x:c r="J232" t="str">
         <x:v>3M</x:v>
@@ -12927,8 +12931,8 @@
       <x:c r="H233" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Clothing &amp; Safety</x:v>
       </x:c>
-      <x:c r="I233" t="str">
-        <x:v>3m, 3m blue long mask, painting tools &amp; accessories, clothing &amp; safety</x:v>
+      <x:c r="I233" s="15" t="str">
+        <x:v>masking tape, painter's tape, blue masking tape, painting accessory</x:v>
       </x:c>
       <x:c r="J233" t="str">
         <x:v>3M</x:v>
@@ -12974,8 +12978,8 @@
       <x:c r="H234" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I234" t="str">
-        <x:v>3m, 3m hand-masker 12" film blade, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I234" s="15" t="str">
+        <x:v>masking film blade, dispenser blade, masking tool accessory, replacement blade</x:v>
       </x:c>
       <x:c r="J234" t="str">
         <x:v>3M</x:v>
@@ -13021,8 +13025,8 @@
       <x:c r="H235" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I235" t="str">
-        <x:v>3m, 3m cutoff blade, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I235" s="15" t="str">
+        <x:v>replacement blade, scraper blade, cutting accessory, hand tool accessory</x:v>
       </x:c>
       <x:c r="J235" t="str">
         <x:v>3M</x:v>
@@ -13068,8 +13072,8 @@
       <x:c r="H236" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I236" t="str">
-        <x:v>richard, w-10 wood scraper, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I236" s="15" t="str">
+        <x:v>scraper, surface preparation tool, hand tool, painting tool</x:v>
       </x:c>
       <x:c r="J236" t="str">
         <x:v>Richard</x:v>
@@ -13115,8 +13119,8 @@
       <x:c r="H237" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I237" t="str">
-        <x:v>richard, w 1 3/4 blade, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I237" s="15" t="str">
+        <x:v>replacement blade, scraper blade, cutting accessory, hand tool accessory</x:v>
       </x:c>
       <x:c r="J237" t="str">
         <x:v>Richard</x:v>
@@ -13162,8 +13166,8 @@
       <x:c r="H238" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I238" t="str">
-        <x:v>richard, u-s-10 richard lever bar, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I238" s="15" t="str">
+        <x:v>pry bar, lever tool, hand tool, surface preparation tool</x:v>
       </x:c>
       <x:c r="J238" t="str">
         <x:v>Richard</x:v>
@@ -13209,8 +13213,8 @@
       <x:c r="H239" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I239" t="str">
-        <x:v>richard, sp2 sash painter, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I239" s="15" t="str">
+        <x:v>angled paint brush, sash brush, paint applicator, painting tool</x:v>
       </x:c>
       <x:c r="J239" t="str">
         <x:v>Richard</x:v>
@@ -13256,8 +13260,8 @@
       <x:c r="H240" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I240" t="str">
-        <x:v>richard, sp1 sash painter, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I240" s="15" t="str">
+        <x:v>angled paint brush, sash brush, paint applicator, painting tool</x:v>
       </x:c>
       <x:c r="J240" t="str">
         <x:v>Richard</x:v>
@@ -13303,8 +13307,8 @@
       <x:c r="H241" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I241" t="str">
-        <x:v>richard, rubber sanding block, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I241" s="15" t="str">
+        <x:v>sanding block, hand sander, surface preparation tool, abrasive tool</x:v>
       </x:c>
       <x:c r="J241" t="str">
         <x:v>Richard</x:v>
@@ -13350,8 +13354,8 @@
       <x:c r="H242" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I242" t="str">
-        <x:v>richard, richard wallpaper smoother, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I242" s="15" t="str">
+        <x:v>wallpaper smoother, wallcovering tool, smoothing tool, installation tool</x:v>
       </x:c>
       <x:c r="J242" t="str">
         <x:v>Richard</x:v>
@@ -13397,8 +13401,8 @@
       <x:c r="H243" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I243" t="str">
-        <x:v>richard, richard utility blades u-1-b, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I243" s="15" t="str">
+        <x:v>utility knife blade, replacement blade, cutting accessory, hand tool accessory</x:v>
       </x:c>
       <x:c r="J243" t="str">
         <x:v>Richard</x:v>
@@ -13444,8 +13448,8 @@
       <x:c r="H244" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I244" t="str">
-        <x:v>richard, richard stir whip mixer, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I244" s="15" t="str">
+        <x:v>paint mixer, drill mixing attachment, coating mixing tool, painting tool</x:v>
       </x:c>
       <x:c r="J244" t="str">
         <x:v>Richard</x:v>
@@ -13491,8 +13495,8 @@
       <x:c r="H245" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I245" t="str">
-        <x:v>richard, richard h.d. plastic tray liner, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I245" s="15" t="str">
+        <x:v>paint tray, paint container, painting accessory, paint tray liner</x:v>
       </x:c>
       <x:c r="J245" t="str">
         <x:v>Richard</x:v>
@@ -13538,8 +13542,8 @@
       <x:c r="H246" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I246" t="str">
-        <x:v>richard, richard h.d. jumbo plastic tray, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I246" s="15" t="str">
+        <x:v>paint tray, paint container, painting accessory, paint roller tray</x:v>
       </x:c>
       <x:c r="J246" t="str">
         <x:v>Richard</x:v>
@@ -13585,8 +13589,8 @@
       <x:c r="H247" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I247" t="str">
-        <x:v>richard, richard fat boy 2 1/2" oval angle brush, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I247" s="15" t="str">
+        <x:v>angled paint brush, sash brush, paint applicator, painting tool</x:v>
       </x:c>
       <x:c r="J247" t="str">
         <x:v>Richard</x:v>
@@ -13632,8 +13636,8 @@
       <x:c r="H248" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I248" t="str">
-        <x:v>richard, richard ergo-grip hand sander rub-18350, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I248" s="15" t="str">
+        <x:v>hand sander, surface preparation tool, abrasive tool, painting tool</x:v>
       </x:c>
       <x:c r="J248" t="str">
         <x:v>Richard</x:v>
@@ -13679,8 +13683,8 @@
       <x:c r="H249" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I249" t="str">
-        <x:v>richard, richard drywall saw ergo-grip, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I249" s="15" t="str">
+        <x:v>drywall saw, jab saw, cutting tool, hand tool</x:v>
       </x:c>
       <x:c r="J249" t="str">
         <x:v>Richard</x:v>
@@ -13726,8 +13730,8 @@
       <x:c r="H250" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I250" t="str">
-        <x:v>richard, richard drywall patch 18204, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I250" s="15" t="str">
+        <x:v>drywall patch, wall repair product, patching material, surface repair product</x:v>
       </x:c>
       <x:c r="J250" t="str">
         <x:v>Richard</x:v>
@@ -13773,8 +13777,8 @@
       <x:c r="H251" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I251" t="str">
-        <x:v>richard, richard aluminum pole sander, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I251" s="15" t="str">
+        <x:v>pole sander, drywall sander, surface preparation tool, hand sander</x:v>
       </x:c>
       <x:c r="J251" t="str">
         <x:v>Richard</x:v>
@@ -13820,8 +13824,8 @@
       <x:c r="H252" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I252" t="str">
-        <x:v>richard, richard aluminum round pole sander, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I252" s="15" t="str">
+        <x:v>pole sander, drywall sander, surface preparation tool, hand sander</x:v>
       </x:c>
       <x:c r="J252" t="str">
         <x:v>Richard</x:v>
@@ -13867,8 +13871,8 @@
       <x:c r="H253" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I253" t="str">
-        <x:v>richard, richard ergo-grip taping knife, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I253" s="15" t="str">
+        <x:v>drywall taping knife, drywall finishing tool, hand tool, surface repair tool</x:v>
       </x:c>
       <x:c r="J253" t="str">
         <x:v>Richard</x:v>
@@ -13914,8 +13918,8 @@
       <x:c r="H254" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I254" t="str">
-        <x:v>richard, richard heavy duty floor scraper, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I254" s="15" t="str">
+        <x:v>scraper, surface preparation tool, hand tool, painting tool</x:v>
       </x:c>
       <x:c r="J254" t="str">
         <x:v>Richard</x:v>
@@ -13961,8 +13965,8 @@
       <x:c r="H255" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I255" t="str">
-        <x:v>richard, richard floor scraper blade, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I255" s="15" t="str">
+        <x:v>scraper, surface preparation tool, hand tool, painting tool, replacement blade, scraper blade, cutting accessory, hand tool accessory</x:v>
       </x:c>
       <x:c r="J255" t="str">
         <x:v>Richard</x:v>
@@ -14008,8 +14012,8 @@
       <x:c r="H256" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I256" t="str">
-        <x:v>richard, richard scraper pro series rub-114, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I256" s="15" t="str">
+        <x:v>scraper, surface preparation tool, hand tool, painting tool</x:v>
       </x:c>
       <x:c r="J256" t="str">
         <x:v>Richard</x:v>
@@ -14055,8 +14059,8 @@
       <x:c r="H257" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I257" t="str">
-        <x:v>richard, richard stainless steel putty knife, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I257" s="15" t="str">
+        <x:v>putty knife, filling knife, surface repair tool, hand tool</x:v>
       </x:c>
       <x:c r="J257" t="str">
         <x:v>Richard</x:v>
@@ -14102,8 +14106,8 @@
       <x:c r="H258" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I258" t="str">
-        <x:v>richard, richard 2 1/2" goose neck flexible paint brush, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I258" s="15" t="str">
+        <x:v>angled paint brush, sash brush, paint applicator, painting tool, paint brush, bristle brush</x:v>
       </x:c>
       <x:c r="J258" t="str">
         <x:v>Richard</x:v>
@@ -14149,8 +14153,8 @@
       <x:c r="H259" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I259" t="str">
-        <x:v>richard, richard ergo-grip scraper, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I259" s="15" t="str">
+        <x:v>scraper, surface preparation tool, hand tool, painting tool</x:v>
       </x:c>
       <x:c r="J259" t="str">
         <x:v>Richard</x:v>
@@ -14196,8 +14200,8 @@
       <x:c r="H260" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I260" t="str">
-        <x:v>richard, richard new plastic pole sander, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I260" s="15" t="str">
+        <x:v>pole sander, drywall sander, surface preparation tool, hand sander</x:v>
       </x:c>
       <x:c r="J260" t="str">
         <x:v>Richard</x:v>
@@ -14243,8 +14247,8 @@
       <x:c r="H261" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I261" t="str">
-        <x:v>richard, richard mini wire brush, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I261" s="15" t="str">
+        <x:v>wire brush, surface preparation brush, rust-removal tool, hand tool</x:v>
       </x:c>
       <x:c r="J261" t="str">
         <x:v>Richard</x:v>
@@ -14290,8 +14294,8 @@
       <x:c r="H262" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I262" t="str">
-        <x:v>richard, paint pad sp2, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I262" s="15" t="str">
+        <x:v>paint pad, flat paint applicator, painting tool, coating applicator</x:v>
       </x:c>
       <x:c r="J262" t="str">
         <x:v>Richard</x:v>
@@ -14337,8 +14341,8 @@
       <x:c r="H263" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I263" t="str">
-        <x:v>richard, window scraper blades, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I263" s="15" t="str">
+        <x:v>scraper, surface preparation tool, hand tool, painting tool, replacement blade, scraper blade, cutting accessory, hand tool accessory</x:v>
       </x:c>
       <x:c r="J263" t="str">
         <x:v>Richard</x:v>
@@ -14384,8 +14388,8 @@
       <x:c r="H264" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I264" t="str">
-        <x:v>richard, drywall knife richard rub-rw-10-ab, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I264" s="15" t="str">
+        <x:v>drywall taping knife, drywall finishing tool, hand tool, surface repair tool</x:v>
       </x:c>
       <x:c r="J264" t="str">
         <x:v>Richard</x:v>
@@ -14431,8 +14435,8 @@
       <x:c r="H265" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I265" t="str">
-        <x:v>advance equipment, seam buster double cutter advance, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I265" s="15" t="str">
+        <x:v>wallpaper seam cutter, double-cut tool, wallcovering tool, cutting tool</x:v>
       </x:c>
       <x:c r="J265" t="str">
         <x:v>Advance Equipment</x:v>
@@ -14478,8 +14482,8 @@
       <x:c r="H266" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I266" t="str">
-        <x:v>advance equipment, advance quick truss door painting stands, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I266" s="15" t="str">
+        <x:v>door painting stand, work support, painting accessory, finishing stand</x:v>
       </x:c>
       <x:c r="J266" t="str">
         <x:v>Advance Equipment</x:v>
@@ -14525,8 +14529,8 @@
       <x:c r="H267" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I267" t="str">
-        <x:v>advance equipment, advance equipment 2" stainless steel seam roller, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I267" s="15" t="str">
+        <x:v>wallpaper seam roller, wallcovering tool, smoothing roller, installation tool</x:v>
       </x:c>
       <x:c r="J267" t="str">
         <x:v>Advance Equipment</x:v>
@@ -14572,8 +14576,8 @@
       <x:c r="H268" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I268" t="str">
-        <x:v>advance equipment, advance equipment 2" plastic oval seam roller, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I268" s="15" t="str">
+        <x:v>wallpaper seam roller, wallcovering tool, smoothing roller, installation tool</x:v>
       </x:c>
       <x:c r="J268" t="str">
         <x:v>Advance Equipment</x:v>
@@ -14619,8 +14623,8 @@
       <x:c r="H269" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I269" t="str">
-        <x:v>advance equipment, advance equipment plastic flat seam roller, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I269" s="15" t="str">
+        <x:v>wallpaper seam roller, wallcovering tool, smoothing roller, installation tool</x:v>
       </x:c>
       <x:c r="J269" t="str">
         <x:v>Advance Equipment</x:v>
@@ -14674,8 +14678,8 @@
       <x:c r="H270" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I270" t="str">
-        <x:v>anchor, floor guard 400 sq ft wide, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I270" s="15" t="str">
+        <x:v>floor protection, surface protection material, protective paper, painting accessory</x:v>
       </x:c>
       <x:c r="J270" t="str">
         <x:v>Anchor</x:v>
@@ -14721,8 +14725,8 @@
       <x:c r="H271" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I271" t="str">
-        <x:v>anchor, anchored rubber coated paper (86), painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I271" s="15" t="str">
+        <x:v>floor protection, surface protection material, protective paper, painting accessory</x:v>
       </x:c>
       <x:c r="J271" t="str">
         <x:v>Anchor</x:v>
@@ -14768,8 +14772,8 @@
       <x:c r="H272" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I272" t="str">
-        <x:v>anchor, anchored coated paper 700sq ft w(77), painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I272" s="15" t="str">
+        <x:v>floor protection, surface protection material, protective paper, painting accessory</x:v>
       </x:c>
       <x:c r="J272" t="str">
         <x:v>Anchor</x:v>
@@ -14815,8 +14819,8 @@
       <x:c r="H273" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I273" t="str">
-        <x:v>atrium, wonder wipes 100, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I273" s="15" t="str">
+        <x:v>cleaning wipes, multi-purpose wipes, surface cleaning product, pre-moistened wipes</x:v>
       </x:c>
       <x:c r="J273" t="str">
         <x:v>Atrium</x:v>
@@ -14862,8 +14866,8 @@
       <x:c r="H274" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I274" t="str">
-        <x:v>atrium, mitre bond adhesive, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I274" s="15" t="str">
+        <x:v>instant adhesive, cyanoacrylate adhesive, two-part adhesive system, woodworking adhesive</x:v>
       </x:c>
       <x:c r="J274" t="str">
         <x:v>Atrium</x:v>
@@ -14909,8 +14913,8 @@
       <x:c r="H275" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I275" t="str">
-        <x:v>atrium, mammoth double sided tape 2.5 meters, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I275" s="15" t="str">
+        <x:v>double-sided tape, mounting tape, pressure-sensitive adhesive, repair tape</x:v>
       </x:c>
       <x:c r="J275" t="str">
         <x:v>Atrium</x:v>
@@ -14956,8 +14960,8 @@
       <x:c r="H276" t="str">
         <x:v>Paints &gt; Interior</x:v>
       </x:c>
-      <x:c r="I276" t="str">
-        <x:v>insl-x, insl-x fire retardant latex - flat white, paints, interior</x:v>
+      <x:c r="I276" s="15" t="str">
+        <x:v>fire-retardant paint, protective coating, interior coating, architectural paint</x:v>
       </x:c>
       <x:c r="J276" t="str">
         <x:v>Insl-X</x:v>
@@ -15009,8 +15013,8 @@
       <x:c r="H277" t="str">
         <x:v>Commercial &amp; Industrial &gt; Epoxy</x:v>
       </x:c>
-      <x:c r="I277" t="str">
-        <x:v>benjamin moore, benjamin moore high performance epoxy floor sealer, commercial &amp; industrial, epoxy</x:v>
+      <x:c r="I277" s="15" t="str">
+        <x:v>epoxy floor sealer, concrete sealer, industrial floor coating, two-part epoxy</x:v>
       </x:c>
       <x:c r="J277" t="str">
         <x:v>Benjamin Moore</x:v>
@@ -15062,8 +15066,8 @@
       <x:c r="H278" t="str">
         <x:v>Commercial &amp; Industrial &gt; Paints</x:v>
       </x:c>
-      <x:c r="I278" t="str">
-        <x:v>benjamin moore, benjamin moore high performance alkyd urethane, commercial &amp; industrial, paints</x:v>
+      <x:c r="I278" s="15" t="str">
+        <x:v>alkyd urethane coating, industrial enamel, protective coating, industrial paint</x:v>
       </x:c>
       <x:c r="J278" t="str">
         <x:v>Benjamin Moore</x:v>
@@ -15123,8 +15127,8 @@
       <x:c r="H279" t="str">
         <x:v>Commercial &amp; Industrial &gt; Paints</x:v>
       </x:c>
-      <x:c r="I279" t="str">
-        <x:v>benjamin moore, benjamin moore high performance quick-dry alkyd enamel, commercial &amp; industrial, paints</x:v>
+      <x:c r="I279" s="15" t="str">
+        <x:v>alkyd enamel, industrial enamel, protective coating, industrial paint</x:v>
       </x:c>
       <x:c r="J279" t="str">
         <x:v>Benjamin Moore</x:v>
@@ -15176,8 +15180,8 @@
       <x:c r="H280" t="str">
         <x:v>Commercial &amp; Industrial &gt; Paints</x:v>
       </x:c>
-      <x:c r="I280" t="str">
-        <x:v>benjamin moore, benjamin moore high performance rapid-dry alkyd enamel, commercial &amp; industrial, paints</x:v>
+      <x:c r="I280" s="15" t="str">
+        <x:v>alkyd enamel, industrial enamel, protective coating, industrial paint</x:v>
       </x:c>
       <x:c r="J280" t="str">
         <x:v>Benjamin Moore</x:v>
@@ -15229,8 +15233,8 @@
       <x:c r="H281" t="str">
         <x:v>Commercial &amp; Industrial &gt; Epoxy</x:v>
       </x:c>
-      <x:c r="I281" t="str">
-        <x:v>benjamin moore, benjamin moore high performance waterborne epoxy, commercial &amp; industrial, epoxy</x:v>
+      <x:c r="I281" s="15" t="str">
+        <x:v>epoxy coating, two-part epoxy, protective coating, industrial coating</x:v>
       </x:c>
       <x:c r="J281" t="str">
         <x:v>Benjamin Moore</x:v>
@@ -15282,8 +15286,8 @@
       <x:c r="H282" t="str">
         <x:v>Paints &gt; Stains &amp; Varnishes</x:v>
       </x:c>
-      <x:c r="I282" t="str">
-        <x:v>benjamin moore, benjamin moore woodluxe stain remover, paints, stains &amp; varnishes</x:v>
+      <x:c r="I282" s="15" t="str">
+        <x:v>wood stain remover, exterior wood stripper, wood finish remover, surface preparation chemical</x:v>
       </x:c>
       <x:c r="J282" t="str">
         <x:v>Benjamin Moore</x:v>
@@ -15329,8 +15333,8 @@
       <x:c r="H283" t="str">
         <x:v>Paints &gt; Stains &amp; Varnishes</x:v>
       </x:c>
-      <x:c r="I283" t="str">
-        <x:v>benjamin moore, benjamin moore woodluxe wood restorer, paints, stains &amp; varnishes</x:v>
+      <x:c r="I283" s="15" t="str">
+        <x:v>wood restorer, wood treatment, wood restoration product, surface preparation chemical</x:v>
       </x:c>
       <x:c r="J283" t="str">
         <x:v>Benjamin Moore</x:v>
@@ -15376,8 +15380,8 @@
       <x:c r="H284" t="str">
         <x:v>Paints &gt; Stains &amp; Varnishes</x:v>
       </x:c>
-      <x:c r="I284" t="str">
-        <x:v>benjamin moore, benjamin moore woodluxe wood brightener/neutralizer, paints, stains &amp; varnishes</x:v>
+      <x:c r="I284" s="15" t="str">
+        <x:v>wood brightener, wood neutralizer, wood restoration product, surface preparation chemical</x:v>
       </x:c>
       <x:c r="J284" t="str">
         <x:v>Benjamin Moore</x:v>
@@ -15423,8 +15427,8 @@
       <x:c r="H285" t="str">
         <x:v>Paints &gt; Stains &amp; Varnishes</x:v>
       </x:c>
-      <x:c r="I285" t="str">
-        <x:v>benjamin moore, benjamin moore woodluxe wood cleaner, paints, stains &amp; varnishes</x:v>
+      <x:c r="I285" s="15" t="str">
+        <x:v>wood cleaner, wood preparation cleaner, wood restoration product, surface preparation chemical</x:v>
       </x:c>
       <x:c r="J285" t="str">
         <x:v>Benjamin Moore</x:v>
@@ -15470,8 +15474,8 @@
       <x:c r="H286" t="str">
         <x:v>Paints &gt; Exterior</x:v>
       </x:c>
-      <x:c r="I286" t="str">
-        <x:v>benjamin moore, benjamin moore ultra spec elastomeric coating, paints, exterior</x:v>
+      <x:c r="I286" s="15" t="str">
+        <x:v>elastomeric coating, masonry coating, exterior wall coating, waterproof coating</x:v>
       </x:c>
       <x:c r="J286" t="str">
         <x:v>Benjamin Moore</x:v>
@@ -15523,8 +15527,8 @@
       <x:c r="H287" t="str">
         <x:v>Paints &gt; Interior</x:v>
       </x:c>
-      <x:c r="I287" t="str">
-        <x:v>benjamin moore, benjamin moore latex dryfall, paints, interior</x:v>
+      <x:c r="I287" s="15" t="str">
+        <x:v>dryfall paint, interior coating, commercial paint, spray-applied coating</x:v>
       </x:c>
       <x:c r="J287" t="str">
         <x:v>Benjamin Moore</x:v>
@@ -15576,8 +15580,8 @@
       <x:c r="H288" t="str">
         <x:v>Paints &gt; Interior</x:v>
       </x:c>
-      <x:c r="I288" t="str">
-        <x:v>benjamin moore, benjamin moore paint extender, paints, interior</x:v>
+      <x:c r="I288" s="15" t="str">
+        <x:v>paint additive, paint conditioner, latex paint additive, flow and levelling additive</x:v>
       </x:c>
       <x:c r="J288" t="str">
         <x:v>Benjamin Moore</x:v>
@@ -15623,8 +15627,8 @@
       <x:c r="H289" t="str">
         <x:v>Paints &gt; Exterior</x:v>
       </x:c>
-      <x:c r="I289" t="str">
-        <x:v>insl-x, insl-x sure step anti-slip coating - knight gray, paints, exterior</x:v>
+      <x:c r="I289" s="15" t="str">
+        <x:v>floor paint, porch and patio paint, concrete floor coating, protective coating, anti-slip coating, floor coating, protective sealer, specialty coating</x:v>
       </x:c>
       <x:c r="J289" t="str">
         <x:v>Insl-X</x:v>
@@ -15676,8 +15680,8 @@
       <x:c r="H290" t="str">
         <x:v>Paints &gt; Exterior</x:v>
       </x:c>
-      <x:c r="I290" t="str">
-        <x:v>coronado, coronado rust-a-void - semi-gloss white, paints, exterior</x:v>
+      <x:c r="I290" s="15" t="str">
+        <x:v>exterior paint, architectural paint, weather-resistant coating, exterior coating, rust-preventive paint, metal paint, protective enamel, anti-corrosion coating</x:v>
       </x:c>
       <x:c r="J290" t="str">
         <x:v>Coronado</x:v>
@@ -15729,8 +15733,8 @@
       <x:c r="H291" t="str">
         <x:v>Commercial &amp; Industrial &gt; Traffic Paints</x:v>
       </x:c>
-      <x:c r="I291" t="str">
-        <x:v>insl-x, insl-x latex zone marking paint, commercial &amp; industrial, traffic paints</x:v>
+      <x:c r="I291" s="15" t="str">
+        <x:v>traffic marking paint, line marking paint, industrial coating, pavement marking paint</x:v>
       </x:c>
       <x:c r="J291" t="str">
         <x:v>Insl-X</x:v>
@@ -15782,8 +15786,8 @@
       <x:c r="H292" t="str">
         <x:v>Paints &gt; Primers</x:v>
       </x:c>
-      <x:c r="I292" t="str">
-        <x:v>benjamin moore, benjamin moore fresh start exterior wood primer, paints, primers</x:v>
+      <x:c r="I292" s="15" t="str">
+        <x:v>wood primer, exterior primer, primer sealer, surface preparation coating, primer, basecoat</x:v>
       </x:c>
       <x:c r="J292" t="str">
         <x:v>Benjamin Moore</x:v>
@@ -15835,8 +15839,8 @@
       <x:c r="H293" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I293" t="str">
-        <x:v>bennett, white taklon short, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I293" s="15" t="str">
+        <x:v>artist brush, fine-detail brush, paint brush, painting tool</x:v>
       </x:c>
       <x:c r="J293" t="str">
         <x:v>Bennett</x:v>
@@ -15882,8 +15886,8 @@
       <x:c r="H294" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I294" t="str">
-        <x:v>bennett, white taklon round, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I294" s="15" t="str">
+        <x:v>artist brush, fine-detail brush, paint brush, painting tool</x:v>
       </x:c>
       <x:c r="J294" t="str">
         <x:v>Bennett</x:v>
@@ -15929,8 +15933,8 @@
       <x:c r="H295" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I295" t="str">
-        <x:v>bennett, tray liner for tray, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I295" s="15" t="str">
+        <x:v>paint tray, paint container, painting accessory, paint tray liner</x:v>
       </x:c>
       <x:c r="J295" t="str">
         <x:v>Bennett</x:v>
@@ -15976,8 +15980,8 @@
       <x:c r="H296" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I296" t="str">
-        <x:v>bennett, rounded, flat artist brushes, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I296" s="15" t="str">
+        <x:v>artist brush, fine-detail brush, paint brush, painting tool</x:v>
       </x:c>
       <x:c r="J296" t="str">
         <x:v>Bennett</x:v>
@@ -16023,8 +16027,8 @@
       <x:c r="H297" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I297" t="str">
-        <x:v>bennett, bennett perfection 2 1/2" soft latex brush, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I297" s="15" t="str">
+        <x:v>paint brush, paint applicator, painting tool, bristle brush</x:v>
       </x:c>
       <x:c r="J297" t="str">
         <x:v>Bennett</x:v>
@@ -16070,8 +16074,8 @@
       <x:c r="H298" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I298" t="str">
-        <x:v>bennett, pad painter replacement, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I298" s="15" t="str">
+        <x:v>paint pad, flat paint applicator, painting tool, coating applicator</x:v>
       </x:c>
       <x:c r="J298" t="str">
         <x:v>Bennett</x:v>
@@ -16117,8 +16121,8 @@
       <x:c r="H299" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I299" t="str">
-        <x:v>bennett, metal sander head, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I299" s="15" t="str">
+        <x:v>sander head, sandpaper holder, hand sander, surface preparation tool</x:v>
       </x:c>
       <x:c r="J299" t="str">
         <x:v>Bennett</x:v>
@@ -16164,8 +16168,8 @@
       <x:c r="H300" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I300" t="str">
-        <x:v>bennett, foam corner roller, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I300" s="15" t="str">
+        <x:v>corner roller, paint roller, paint applicator, painting tool</x:v>
       </x:c>
       <x:c r="J300" t="str">
         <x:v>Bennett</x:v>
@@ -16211,8 +16215,8 @@
       <x:c r="H301" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I301" t="str">
-        <x:v>bennett, flat white taklon, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I301" s="15" t="str">
+        <x:v>artist brush, fine-detail brush, paint brush, painting tool</x:v>
       </x:c>
       <x:c r="J301" t="str">
         <x:v>Bennett</x:v>
@@ -16258,8 +16262,8 @@
       <x:c r="H302" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I302" t="str">
-        <x:v>bennett, dualon german roller, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I302" s="15" t="str">
+        <x:v>paint roller cover, paint roller refill, paint applicator, painting tool</x:v>
       </x:c>
       <x:c r="J302" t="str">
         <x:v>Bennett</x:v>
@@ -16305,8 +16309,8 @@
       <x:c r="H303" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I303" t="str">
-        <x:v>bennett, cheese cloth, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I303" s="15" t="str">
+        <x:v>tack cloth, surface preparation cloth, dust-removal cloth, painting accessory</x:v>
       </x:c>
       <x:c r="J303" t="str">
         <x:v>Bennett</x:v>
@@ -16352,8 +16356,8 @@
       <x:c r="H304" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I304" t="str">
-        <x:v>canpro, canpro cotton drop sheet, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I304" s="15" t="str">
+        <x:v>drop cloth, surface protection, painting cover, painting accessory</x:v>
       </x:c>
       <x:c r="J304" t="str">
         <x:v>CanPro</x:v>
@@ -16407,8 +16411,8 @@
       <x:c r="H305" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I305" t="str">
-        <x:v>bennett, black goat hair artist brush 555, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I305" s="15" t="str">
+        <x:v>artist brush, fine-detail brush, paint brush, painting tool</x:v>
       </x:c>
       <x:c r="J305" t="str">
         <x:v>Bennett</x:v>
@@ -16454,8 +16458,8 @@
       <x:c r="H306" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I306" t="str">
-        <x:v>bennett, bennett small plastic tray liner, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I306" s="15" t="str">
+        <x:v>paint tray, paint container, painting accessory, paint tray liner</x:v>
       </x:c>
       <x:c r="J306" t="str">
         <x:v>Bennett</x:v>
@@ -16501,8 +16505,8 @@
       <x:c r="H307" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I307" t="str">
-        <x:v>bennett, bennett small plastic tray, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I307" s="15" t="str">
+        <x:v>paint tray, paint container, painting accessory, paint roller tray</x:v>
       </x:c>
       <x:c r="J307" t="str">
         <x:v>Bennett</x:v>
@@ -16548,8 +16552,8 @@
       <x:c r="H308" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I308" t="str">
-        <x:v>bennett, bennett plastic xl tray liner, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I308" s="15" t="str">
+        <x:v>paint tray, paint container, painting accessory, paint tray liner</x:v>
       </x:c>
       <x:c r="J308" t="str">
         <x:v>Bennett</x:v>
@@ -16595,8 +16599,8 @@
       <x:c r="H309" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I309" t="str">
-        <x:v>bennett, bennett one stroke taklon, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I309" s="15" t="str">
+        <x:v>artist brush, fine-detail brush, paint brush, painting tool</x:v>
       </x:c>
       <x:c r="J309" t="str">
         <x:v>Bennett</x:v>
@@ -16642,8 +16646,8 @@
       <x:c r="H310" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I310" t="str">
-        <x:v>bennett, bennett micropro refill, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I310" s="15" t="str">
+        <x:v>paint roller cover, paint roller refill, paint applicator, painting tool</x:v>
       </x:c>
       <x:c r="J310" t="str">
         <x:v>Bennett</x:v>
@@ -16697,8 +16701,8 @@
       <x:c r="H311" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I311" t="str">
-        <x:v>bennett, bennett liner for tray, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I311" s="15" t="str">
+        <x:v>paint tray, paint container, painting accessory, paint tray liner</x:v>
       </x:c>
       <x:c r="J311" t="str">
         <x:v>Bennett</x:v>
@@ -16744,8 +16748,8 @@
       <x:c r="H312" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I312" t="str">
-        <x:v>bennett, bennett large sea sponge, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I312" s="15" t="str">
+        <x:v>natural sea sponge, decorative paint applicator, texture sponge, painting tool</x:v>
       </x:c>
       <x:c r="J312" t="str">
         <x:v>Bennett</x:v>
@@ -16791,8 +16795,8 @@
       <x:c r="H313" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I313" t="str">
-        <x:v>bennett, bennett jumbo xl plastic tray, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I313" s="15" t="str">
+        <x:v>paint tray, paint container, painting accessory, paint roller tray</x:v>
       </x:c>
       <x:c r="J313" t="str">
         <x:v>Bennett</x:v>
@@ -16838,8 +16842,8 @@
       <x:c r="H314" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I314" t="str">
-        <x:v>bennett, bennett gallon paint grid, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I314" s="15" t="str">
+        <x:v>paint grid, roller grid, paint bucket accessory, painting tool</x:v>
       </x:c>
       <x:c r="J314" t="str">
         <x:v>Bennett</x:v>
@@ -16885,8 +16889,8 @@
       <x:c r="H315" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Clothing &amp; Safety</x:v>
       </x:c>
-      <x:c r="I315" t="str">
-        <x:v>bennett, bennett disposable coverall large, painting tools &amp; accessories, clothing &amp; safety</x:v>
+      <x:c r="I315" s="15" t="str">
+        <x:v>painter clothing, workwear, protective clothing, coveralls</x:v>
       </x:c>
       <x:c r="J315" t="str">
         <x:v>Bennett</x:v>
@@ -16932,8 +16936,8 @@
       <x:c r="H316" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I316" t="str">
-        <x:v>bennett, bennett brass mini wire brush, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I316" s="15" t="str">
+        <x:v>wire brush, surface preparation brush, rust-removal tool, hand tool</x:v>
       </x:c>
       <x:c r="J316" t="str">
         <x:v>Bennett</x:v>
@@ -16979,8 +16983,8 @@
       <x:c r="H317" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I317" t="str">
-        <x:v>bennett, bennett mini red tray, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I317" s="15" t="str">
+        <x:v>paint tray, paint container, painting accessory, paint roller tray</x:v>
       </x:c>
       <x:c r="J317" t="str">
         <x:v>Bennett</x:v>
@@ -17026,8 +17030,8 @@
       <x:c r="H318" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I318" t="str">
-        <x:v>bennett, bennett fiberglass pole, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I318" s="15" t="str">
+        <x:v>paint roller extension pole, telescoping pole, paint applicator accessory, painting tool</x:v>
       </x:c>
       <x:c r="J318" t="str">
         <x:v>Bennett</x:v>
@@ -17081,8 +17085,8 @@
       <x:c r="H319" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I319" t="str">
-        <x:v>bennett, bennett pad painter, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I319" s="15" t="str">
+        <x:v>paint pad, flat paint applicator, painting tool, coating applicator</x:v>
       </x:c>
       <x:c r="J319" t="str">
         <x:v>Bennett</x:v>
@@ -17128,8 +17132,8 @@
       <x:c r="H320" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I320" t="str">
-        <x:v>bennett, bennett twist fiberglass, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I320" s="15" t="str">
+        <x:v>paint roller extension pole, telescoping pole, paint applicator accessory, painting tool</x:v>
       </x:c>
       <x:c r="J320" t="str">
         <x:v>Bennett</x:v>
@@ -17183,8 +17187,8 @@
       <x:c r="H321" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I321" t="str">
-        <x:v>bennett, bennett red tray, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I321" s="15" t="str">
+        <x:v>paint tray, paint container, painting accessory, paint roller tray</x:v>
       </x:c>
       <x:c r="J321" t="str">
         <x:v>Bennett</x:v>
@@ -17230,8 +17234,8 @@
       <x:c r="H322" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I322" t="str">
-        <x:v>bennett, bennett pure bristle chip brush, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I322" s="15" t="str">
+        <x:v>chip brush, utility paint brush, paint applicator, painting tool</x:v>
       </x:c>
       <x:c r="J322" t="str">
         <x:v>Bennett</x:v>
@@ -17277,8 +17281,8 @@
       <x:c r="H323" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I323" t="str">
-        <x:v>bennett, bennett micropro tray set, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I323" s="15" t="str">
+        <x:v>paint roller kit, paint tray set, paint applicator kit, painting tool</x:v>
       </x:c>
       <x:c r="J323" t="str">
         <x:v>Bennett</x:v>
@@ -17324,8 +17328,8 @@
       <x:c r="H324" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I324" t="str">
-        <x:v>bennett, bennett micropro refills, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I324" s="15" t="str">
+        <x:v>paint roller cover, paint roller refill, paint applicator, painting tool</x:v>
       </x:c>
       <x:c r="J324" t="str">
         <x:v>Bennett</x:v>
@@ -17371,8 +17375,8 @@
       <x:c r="H325" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I325" t="str">
-        <x:v>bennett, bennett foam refills, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I325" s="15" t="str">
+        <x:v>paint roller cover, paint roller refill, paint applicator, painting tool, foam roller cover</x:v>
       </x:c>
       <x:c r="J325" t="str">
         <x:v>Bennett</x:v>
@@ -17418,8 +17422,8 @@
       <x:c r="H326" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I326" t="str">
-        <x:v>bennett, bennett foam brush, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I326" s="15" t="str">
+        <x:v>foam brush, disposable paint brush, paint applicator, painting tool</x:v>
       </x:c>
       <x:c r="J326" t="str">
         <x:v>Bennett</x:v>
@@ -17465,8 +17469,8 @@
       <x:c r="H327" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I327" t="str">
-        <x:v>bennett, bennett 4x12 cotton drop sheet, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I327" s="15" t="str">
+        <x:v>drop cloth, surface protection, painting cover, painting accessory</x:v>
       </x:c>
       <x:c r="J327" t="str">
         <x:v>Bennett</x:v>
@@ -17512,8 +17516,8 @@
       <x:c r="H328" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I328" t="str">
-        <x:v>bennett, bennett drill mixer, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I328" s="15" t="str">
+        <x:v>paint mixer, drill mixing attachment, coating mixing tool, painting tool</x:v>
       </x:c>
       <x:c r="J328" t="str">
         <x:v>Bennett</x:v>
@@ -17567,8 +17571,8 @@
       <x:c r="H329" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I329" t="str">
-        <x:v>bennett, bennett mini roller handle, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I329" s="15" t="str">
+        <x:v>paint roller frame, roller handle, paint applicator, painting tool</x:v>
       </x:c>
       <x:c r="J329" t="str">
         <x:v>Bennett</x:v>
@@ -17614,8 +17618,8 @@
       <x:c r="H330" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I330" t="str">
-        <x:v>bennett, bennett putty knife, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I330" s="15" t="str">
+        <x:v>putty knife, filling knife, surface repair tool, hand tool</x:v>
       </x:c>
       <x:c r="J330" t="str">
         <x:v>Bennett</x:v>
@@ -17661,8 +17665,8 @@
       <x:c r="H331" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I331" t="str">
-        <x:v>bennett, bennett 5-wire cage, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I331" s="15" t="str">
+        <x:v>paint roller frame, roller handle, paint applicator, painting tool</x:v>
       </x:c>
       <x:c r="J331" t="str">
         <x:v>Bennett</x:v>
@@ -17708,8 +17712,8 @@
       <x:c r="H332" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I332" t="str">
-        <x:v>bennett, 8 x 12 plastic drop sheet, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I332" s="15" t="str">
+        <x:v>drop cloth, surface protection, painting cover, painting accessory</x:v>
       </x:c>
       <x:c r="J332" t="str">
         <x:v>Bennett</x:v>
@@ -17755,8 +17759,8 @@
       <x:c r="H333" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I333" t="str">
-        <x:v>bennett, chip brush chip, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I333" s="15" t="str">
+        <x:v>chip brush, utility paint brush, paint applicator, painting tool</x:v>
       </x:c>
       <x:c r="J333" t="str">
         <x:v>Bennett</x:v>
@@ -17802,8 +17806,8 @@
       <x:c r="H334" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I334" t="str">
-        <x:v>bennett, plastic putty knife, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I334" s="15" t="str">
+        <x:v>putty knife, filling knife, surface repair tool, hand tool</x:v>
       </x:c>
       <x:c r="J334" t="str">
         <x:v>Bennett</x:v>
@@ -17849,8 +17853,8 @@
       <x:c r="H335" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I335" t="str">
-        <x:v>bennett, bennett red bee chip brush, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I335" s="15" t="str">
+        <x:v>chip brush, utility paint brush, paint applicator, painting tool</x:v>
       </x:c>
       <x:c r="J335" t="str">
         <x:v>Bennett</x:v>
@@ -17896,8 +17900,8 @@
       <x:c r="H336" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I336" t="str">
-        <x:v>bennett, high density foam, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I336" s="15" t="str">
+        <x:v>foam roller cover, paint roller refill, high-density foam applicator, paint applicator</x:v>
       </x:c>
       <x:c r="J336" t="str">
         <x:v>Bennett</x:v>
@@ -17943,8 +17947,8 @@
       <x:c r="H337" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I337" t="str">
-        <x:v>bennett, lint-free tray set, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I337" s="15" t="str">
+        <x:v>paint roller kit, paint tray set, paint applicator kit, painting tool</x:v>
       </x:c>
       <x:c r="J337" t="str">
         <x:v>Bennett</x:v>
@@ -17990,8 +17994,8 @@
       <x:c r="H338" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I338" t="str">
-        <x:v>bennett, bennett lint free rollers, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I338" s="15" t="str">
+        <x:v>paint roller cover, paint roller refill, paint applicator, painting tool</x:v>
       </x:c>
       <x:c r="J338" t="str">
         <x:v>Bennett</x:v>
@@ -18037,8 +18041,8 @@
       <x:c r="H339" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I339" t="str">
-        <x:v>bennett, angular white taklon, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I339" s="15" t="str">
+        <x:v>artist brush, fine-detail brush, paint brush, painting tool</x:v>
       </x:c>
       <x:c r="J339" t="str">
         <x:v>Bennett</x:v>
@@ -18084,8 +18088,8 @@
       <x:c r="H340" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I340" t="str">
-        <x:v>bennett, high density foam brush, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I340" s="15" t="str">
+        <x:v>foam brush, high-density foam brush, paint applicator, painting tool</x:v>
       </x:c>
       <x:c r="J340" t="str">
         <x:v>Bennett</x:v>
@@ -18131,8 +18135,8 @@
       <x:c r="H341" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I341" t="str">
-        <x:v>canlak, red x pro red blocker, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I341" s="15" t="str">
+        <x:v>stain blocker, colour bleed blocker, wood finishing sealer, wood coating basecoat</x:v>
       </x:c>
       <x:c r="J341" t="str">
         <x:v>Canlak</x:v>
@@ -18178,8 +18182,8 @@
       <x:c r="H342" t="str">
         <x:v>Lacquer And Millwork Coatings &gt; Canlak</x:v>
       </x:c>
-      <x:c r="I342" t="str">
-        <x:v>canlak, canlak white dry glaze, lacquer and millwork coatings</x:v>
+      <x:c r="I342" s="15" t="str">
+        <x:v>decorative glaze, wood finishing glaze, toning finish, decorative coating</x:v>
       </x:c>
       <x:c r="J342" t="str">
         <x:v>Canlak</x:v>
@@ -18225,8 +18229,8 @@
       <x:c r="H343" t="str">
         <x:v>Lacquer And Millwork Coatings &gt; Canlak</x:v>
       </x:c>
-      <x:c r="I343" t="str">
-        <x:v>canlak, canlak wb lacquer 10% sheen, lacquer and millwork coatings</x:v>
+      <x:c r="I343" s="15" t="str">
+        <x:v>water-based lacquer, clear wood finish, millwork coating, low-sheen lacquer</x:v>
       </x:c>
       <x:c r="J343" t="str">
         <x:v>Canlak</x:v>
@@ -18272,8 +18276,8 @@
       <x:c r="H344" t="str">
         <x:v>Lacquer And Millwork Coatings &gt; Canlak</x:v>
       </x:c>
-      <x:c r="I344" t="str">
-        <x:v>canlak, canlak varnish thinner, lacquer and millwork coatings</x:v>
+      <x:c r="I344" s="15" t="str">
+        <x:v>varnish thinner, coating reducer, finishing solvent, paint solvent</x:v>
       </x:c>
       <x:c r="J344" t="str">
         <x:v>Canlak</x:v>
@@ -18319,8 +18323,8 @@
       <x:c r="H345" t="str">
         <x:v>Lacquer And Millwork Coatings &gt; Canlak</x:v>
       </x:c>
-      <x:c r="I345" t="str">
-        <x:v>canlak, canlak thinner, lacquer and millwork coatings</x:v>
+      <x:c r="I345" s="15" t="str">
+        <x:v>coating thinner, wood finishing solvent, coating reducer, equipment cleaning solvent</x:v>
       </x:c>
       <x:c r="J345" t="str">
         <x:v>Canlak</x:v>
@@ -18366,8 +18370,8 @@
       <x:c r="H346" t="str">
         <x:v>Lacquer And Millwork Coatings &gt; Canlak</x:v>
       </x:c>
-      <x:c r="I346" t="str">
-        <x:v>canlak, canlak post-cat clear 10% sheen, lacquer and millwork coatings</x:v>
+      <x:c r="I346" s="15" t="str">
+        <x:v>catalyzed lacquer, wood lacquer, clear wood finish, professional wood coating</x:v>
       </x:c>
       <x:c r="J346" t="str">
         <x:v>Canlak</x:v>
@@ -18413,8 +18417,8 @@
       <x:c r="H347" t="str">
         <x:v>Lacquer And Millwork Coatings &gt; Canlak</x:v>
       </x:c>
-      <x:c r="I347" t="str">
-        <x:v>canlak, canlak high build post-catalyzed white primer, lacquer and millwork coatings</x:v>
+      <x:c r="I347" s="15" t="str">
+        <x:v>post-catalyzed primer, high-build wood primer, white millwork primer, professional wood coating</x:v>
       </x:c>
       <x:c r="J347" t="str">
         <x:v>Canlak</x:v>
@@ -18460,8 +18464,8 @@
       <x:c r="H348" t="str">
         <x:v>Lacquer And Millwork Coatings &gt; Canlak</x:v>
       </x:c>
-      <x:c r="I348" t="str">
-        <x:v>canlak, canlak clear perma-shine50% sheen, lacquer and millwork coatings</x:v>
+      <x:c r="I348" s="15" t="str">
+        <x:v>clear millwork finish, semi-gloss clear coat, protective wood coating, professional wood finish</x:v>
       </x:c>
       <x:c r="J348" t="str">
         <x:v>Canlak</x:v>
@@ -18507,8 +18511,8 @@
       <x:c r="H349" t="str">
         <x:v>Lacquer And Millwork Coatings &gt; Canlak</x:v>
       </x:c>
-      <x:c r="I349" t="str">
-        <x:v>canlak, canlak black wet glaze, lacquer and millwork coatings</x:v>
+      <x:c r="I349" s="15" t="str">
+        <x:v>decorative glaze, wood finishing glaze, toning finish, decorative coating</x:v>
       </x:c>
       <x:c r="J349" t="str">
         <x:v>Canlak</x:v>
@@ -18554,8 +18558,8 @@
       <x:c r="H350" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I350" t="str">
-        <x:v>chapin, chapin xtreme concrete sprayer, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I350" s="15" t="str">
+        <x:v>concrete sprayer, chemical sprayer, pump sprayer, coating application equipment</x:v>
       </x:c>
       <x:c r="J350" t="str">
         <x:v>Chapin</x:v>
@@ -18601,8 +18605,8 @@
       <x:c r="H351" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I351" t="str">
-        <x:v>allpro, allpro mini wallpaper sprayer, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I351" s="15" t="str">
+        <x:v>wallpaper sprayer, pump sprayer, wallcovering removal tool, chemical application equipment</x:v>
       </x:c>
       <x:c r="J351" t="str">
         <x:v>AllPro</x:v>
@@ -18648,8 +18652,8 @@
       <x:c r="H352" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I352" t="str">
-        <x:v>corona, corona ultraweave roller, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I352" s="15" t="str">
+        <x:v>paint roller cover, paint roller refill, paint applicator, painting tool</x:v>
       </x:c>
       <x:c r="J352" t="str">
         <x:v>Corona</x:v>
@@ -18703,8 +18707,8 @@
       <x:c r="H353" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I353" t="str">
-        <x:v>corona, corona ultrafast, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I353" s="15" t="str">
+        <x:v>paint roller cover, paint roller refill, fabric roller cover, paint applicator</x:v>
       </x:c>
       <x:c r="J353" t="str">
         <x:v>Corona</x:v>
@@ -18750,8 +18754,8 @@
       <x:c r="H354" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I354" t="str">
-        <x:v>corona, corona glasskoter mohair, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I354" s="15" t="str">
+        <x:v>paint roller cover, paint roller refill, paint applicator, painting tool, mohair roller cover</x:v>
       </x:c>
       <x:c r="J354" t="str">
         <x:v>Corona</x:v>
@@ -18797,8 +18801,8 @@
       <x:c r="H355" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I355" t="str">
-        <x:v>corona, cortez latex brush corona, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I355" s="15" t="str">
+        <x:v>paint brush, paint applicator, painting tool, bristle brush</x:v>
       </x:c>
       <x:c r="J355" t="str">
         <x:v>Corona</x:v>
@@ -18844,8 +18848,8 @@
       <x:c r="H356" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I356" t="str">
-        <x:v>corona, shelby latex brush, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I356" s="15" t="str">
+        <x:v>paint brush, paint applicator, painting tool, bristle brush</x:v>
       </x:c>
       <x:c r="J356" t="str">
         <x:v>Corona</x:v>
@@ -18891,8 +18895,8 @@
       <x:c r="H357" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I357" t="str">
-        <x:v>corona, excalibur chinex brush corona, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I357" s="15" t="str">
+        <x:v>paint brush, paint applicator, painting tool, bristle brush</x:v>
       </x:c>
       <x:c r="J357" t="str">
         <x:v>Corona</x:v>
@@ -18938,8 +18942,8 @@
       <x:c r="H358" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I358" t="str">
-        <x:v>corona, corona ryan chinex brush, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I358" s="15" t="str">
+        <x:v>paint brush, paint applicator, painting tool, bristle brush</x:v>
       </x:c>
       <x:c r="J358" t="str">
         <x:v>Corona</x:v>
@@ -18985,8 +18989,8 @@
       <x:c r="H359" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I359" t="str">
-        <x:v>corona, vegas latex brush, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I359" s="15" t="str">
+        <x:v>paint brush, paint applicator, painting tool, bristle brush</x:v>
       </x:c>
       <x:c r="J359" t="str">
         <x:v>Corona</x:v>
@@ -19032,8 +19036,8 @@
       <x:c r="H360" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I360" t="str">
-        <x:v>corona, sabre brush corona, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I360" s="15" t="str">
+        <x:v>paint brush, paint applicator, painting tool, bristle brush</x:v>
       </x:c>
       <x:c r="J360" t="str">
         <x:v>Corona</x:v>
@@ -19079,8 +19083,8 @@
       <x:c r="H361" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I361" t="str">
-        <x:v>corona, corona classic smoother, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I361" s="15" t="str">
+        <x:v>wallpaper smoother, wallcovering tool, smoothing tool, installation tool</x:v>
       </x:c>
       <x:c r="J361" t="str">
         <x:v>Corona</x:v>
@@ -19126,8 +19130,8 @@
       <x:c r="H362" t="str">
         <x:v>Paints &gt; Exterior</x:v>
       </x:c>
-      <x:c r="I362" t="str">
-        <x:v>cutek, cutek extreme, paints, exterior</x:v>
+      <x:c r="I362" s="15" t="str">
+        <x:v>penetrating wood oil, exterior wood finish, wood preservative, oil-based wood finish</x:v>
       </x:c>
       <x:c r="J362" t="str">
         <x:v>Cutek</x:v>
@@ -19179,8 +19183,8 @@
       <x:c r="H363" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I363" t="str">
-        <x:v>dap, dynaflex 50yr caulking white, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I363" s="15" t="str">
+        <x:v>sealant, caulk, joint sealant, gap-filling compound, elastomeric sealant, paintable caulk</x:v>
       </x:c>
       <x:c r="J363" t="str">
         <x:v>DAP</x:v>
@@ -19226,8 +19230,8 @@
       <x:c r="H364" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I364" t="str">
-        <x:v>dap, drydex spackling, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I364" s="15" t="str">
+        <x:v>spackling compound, wall repair filler, patching compound, surface repair product</x:v>
       </x:c>
       <x:c r="J364" t="str">
         <x:v>DAP</x:v>
@@ -19273,8 +19277,8 @@
       <x:c r="H365" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I365" t="str">
-        <x:v>dap, dap silicone caulk white, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I365" s="15" t="str">
+        <x:v>sealant, caulk, joint sealant, gap-filling compound, silicone sealant, waterproof caulk</x:v>
       </x:c>
       <x:c r="J365" t="str">
         <x:v>DAP</x:v>
@@ -19320,8 +19324,8 @@
       <x:c r="H366" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I366" t="str">
-        <x:v>dap, dap premium wood filler, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I366" s="15" t="str">
+        <x:v>wood filler, wood repair compound, grain filler, surface repair product</x:v>
       </x:c>
       <x:c r="J366" t="str">
         <x:v>DAP</x:v>
@@ -19367,8 +19371,8 @@
       <x:c r="H367" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I367" t="str">
-        <x:v>dap, dap platinum patch, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I367" s="15" t="str">
+        <x:v>spackling compound, wall repair filler, patching compound, surface repair product</x:v>
       </x:c>
       <x:c r="J367" t="str">
         <x:v>DAP</x:v>
@@ -19422,8 +19426,8 @@
       <x:c r="H368" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I368" t="str">
-        <x:v>dap, dap natural woodpro wood filler - squeeze tube, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I368" s="15" t="str">
+        <x:v>wood filler, wood repair compound, grain filler, surface repair product</x:v>
       </x:c>
       <x:c r="J368" t="str">
         <x:v>DAP</x:v>
@@ -19469,8 +19473,8 @@
       <x:c r="H369" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I369" t="str">
-        <x:v>dap, dap kwik seal ultra white, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I369" s="15" t="str">
+        <x:v>sealant, caulk, joint sealant, gap-filling compound, kitchen and bath sealant, acrylic latex caulk</x:v>
       </x:c>
       <x:c r="J369" t="str">
         <x:v>DAP</x:v>
@@ -19516,8 +19520,8 @@
       <x:c r="H370" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I370" t="str">
-        <x:v>dap, dap kwik seal, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I370" s="15" t="str">
+        <x:v>sealant, caulk, joint sealant, gap-filling compound, kitchen and bath sealant, acrylic latex caulk</x:v>
       </x:c>
       <x:c r="J370" t="str">
         <x:v>DAP</x:v>
@@ -19563,8 +19567,8 @@
       <x:c r="H371" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I371" t="str">
-        <x:v>dap, dap fast'n final filler, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I371" s="15" t="str">
+        <x:v>spackling compound, wall repair filler, patching compound, surface repair product</x:v>
       </x:c>
       <x:c r="J371" t="str">
         <x:v>DAP</x:v>
@@ -19610,8 +19614,8 @@
       <x:c r="H372" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I372" t="str">
-        <x:v>dap, dap fast dry premium spackling, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I372" s="15" t="str">
+        <x:v>spackling compound, wall repair filler, patching compound, surface repair product</x:v>
       </x:c>
       <x:c r="J372" t="str">
         <x:v>DAP</x:v>
@@ -19657,8 +19661,8 @@
       <x:c r="H373" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I373" t="str">
-        <x:v>dap, dap alex flex spackling, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I373" s="15" t="str">
+        <x:v>spackling compound, wall repair filler, patching compound, surface repair product</x:v>
       </x:c>
       <x:c r="J373" t="str">
         <x:v>DAP</x:v>
@@ -19704,8 +19708,8 @@
       <x:c r="H374" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I374" t="str">
-        <x:v>dap, dap alex fast dry contractor, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I374" s="15" t="str">
+        <x:v>sealant, caulk, joint sealant, gap-filling compound</x:v>
       </x:c>
       <x:c r="J374" t="str">
         <x:v>DAP</x:v>
@@ -19751,8 +19755,8 @@
       <x:c r="H375" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I375" t="str">
-        <x:v>dap, dap alex fast dry caulk squeeze tube, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I375" s="15" t="str">
+        <x:v>sealant, caulk, joint sealant, gap-filling compound</x:v>
       </x:c>
       <x:c r="J375" t="str">
         <x:v>DAP</x:v>
@@ -19798,8 +19802,8 @@
       <x:c r="H376" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I376" t="str">
-        <x:v>dap, dap alex fast dry caulk squeeze, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I376" s="15" t="str">
+        <x:v>sealant, caulk, joint sealant, gap-filling compound</x:v>
       </x:c>
       <x:c r="J376" t="str">
         <x:v>DAP</x:v>
@@ -19845,8 +19849,8 @@
       <x:c r="H377" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I377" t="str">
-        <x:v>dap, dap alex fast dry, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I377" s="15" t="str">
+        <x:v>sealant, caulk, joint sealant, gap-filling compound</x:v>
       </x:c>
       <x:c r="J377" t="str">
         <x:v>DAP</x:v>
@@ -19892,8 +19896,8 @@
       <x:c r="H378" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I378" t="str">
-        <x:v>dap, dap 33 glazing, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I378" s="15" t="str">
+        <x:v>window glazing putty, glazing compound, window repair material, oil-based putty</x:v>
       </x:c>
       <x:c r="J378" t="str">
         <x:v>DAP</x:v>
@@ -19947,8 +19951,8 @@
       <x:c r="H379" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I379" t="str">
-        <x:v>dap, plaster of paris, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I379" s="15" t="str">
+        <x:v>plaster of paris, patching plaster, repair compound, gypsum plaster</x:v>
       </x:c>
       <x:c r="J379" t="str">
         <x:v>DAP</x:v>
@@ -19994,8 +19998,8 @@
       <x:c r="H380" t="str">
         <x:v>Specialty &amp; Decorative Products &gt; Window Films</x:v>
       </x:c>
-      <x:c r="I380" t="str">
-        <x:v>decozi, decozi window film, specialty &amp; decorative products, window films</x:v>
+      <x:c r="I380" s="15" t="str">
+        <x:v>decorative window film, self-adhesive film, privacy film, window covering</x:v>
       </x:c>
       <x:c r="J380" t="str">
         <x:v>Decozi</x:v>
@@ -20049,8 +20053,8 @@
       <x:c r="H381" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Clothing &amp; Safety</x:v>
       </x:c>
-      <x:c r="I381" t="str">
-        <x:v>degil, full body harness with lanyard, painting tools &amp; accessories, clothing &amp; safety</x:v>
+      <x:c r="I381" s="15" t="str">
+        <x:v>fall-arrest harness, safety lanyard, fall protection, jobsite safety gear</x:v>
       </x:c>
       <x:c r="J381" t="str">
         <x:v>Degil</x:v>
@@ -20096,8 +20100,8 @@
       <x:c r="H382" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Clothing &amp; Safety</x:v>
       </x:c>
-      <x:c r="I382" t="str">
-        <x:v>degil, hard hat, painting tools &amp; accessories, clothing &amp; safety</x:v>
+      <x:c r="I382" s="15" t="str">
+        <x:v>hard hat, head protection, jobsite safety gear, personal protective equipment</x:v>
       </x:c>
       <x:c r="J382" t="str">
         <x:v>Degil</x:v>
@@ -20143,8 +20147,8 @@
       <x:c r="H383" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Clothing &amp; Safety</x:v>
       </x:c>
-      <x:c r="I383" t="str">
-        <x:v>dentec, citation 932 safety glasses gray, painting tools &amp; accessories, clothing &amp; safety</x:v>
+      <x:c r="I383" s="15" t="str">
+        <x:v>safety glasses, eye protection, protective eyewear, jobsite safety gear</x:v>
       </x:c>
       <x:c r="J383" t="str">
         <x:v>Dentec</x:v>
@@ -20190,8 +20194,8 @@
       <x:c r="H384" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Clothing &amp; Safety</x:v>
       </x:c>
-      <x:c r="I384" t="str">
-        <x:v>dickies, dickies painters overalls 34x30, painting tools &amp; accessories, clothing &amp; safety</x:v>
+      <x:c r="I384" s="15" t="str">
+        <x:v>painter clothing, workwear, protective clothing, coveralls</x:v>
       </x:c>
       <x:c r="J384" t="str">
         <x:v>Dickies</x:v>
@@ -20237,8 +20241,8 @@
       <x:c r="H385" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Clothing &amp; Safety</x:v>
       </x:c>
-      <x:c r="I385" t="str">
-        <x:v>dickies, dickies painter shorts size 34, painting tools &amp; accessories, clothing &amp; safety</x:v>
+      <x:c r="I385" s="15" t="str">
+        <x:v>painter clothing, workwear, protective clothing, painter workwear</x:v>
       </x:c>
       <x:c r="J385" t="str">
         <x:v>Dickies</x:v>
@@ -20284,8 +20288,8 @@
       <x:c r="H386" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Clothing &amp; Safety</x:v>
       </x:c>
-      <x:c r="I386" t="str">
-        <x:v>dickies, dickies painter pants 32x30, painting tools &amp; accessories, clothing &amp; safety</x:v>
+      <x:c r="I386" s="15" t="str">
+        <x:v>painter clothing, workwear, protective clothing, painter workwear</x:v>
       </x:c>
       <x:c r="J386" t="str">
         <x:v>Dickies</x:v>
@@ -20331,8 +20335,8 @@
       <x:c r="H387" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I387" t="str">
-        <x:v>trade secret, trade secret furniture polish&amp;cleaner 4, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I387" s="15" t="str">
+        <x:v>furniture polish, furniture cleaner, wood care product, polishing cleaner</x:v>
       </x:c>
       <x:c r="J387" t="str">
         <x:v>Trade Secret</x:v>
@@ -20378,8 +20382,8 @@
       <x:c r="H388" t="str">
         <x:v>Paints &gt; Specialty Paints</x:v>
       </x:c>
-      <x:c r="I388" t="str">
-        <x:v>tracsafe, trac safe anti slip sealer, paints, specialty paints</x:v>
+      <x:c r="I388" s="15" t="str">
+        <x:v>anti-slip coating, floor coating, protective sealer, specialty coating</x:v>
       </x:c>
       <x:c r="J388" t="str">
         <x:v>TracSafe</x:v>
@@ -20431,8 +20435,8 @@
       <x:c r="H389" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I389" t="str">
-        <x:v>dover, dover touch-up marker 24-piece set, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I389" s="15" t="str">
+        <x:v>touch-up marker, wood repair marker, colour repair pen, finishing tool</x:v>
       </x:c>
       <x:c r="J389" t="str">
         <x:v>Dover</x:v>
@@ -20478,8 +20482,8 @@
       <x:c r="H390" t="str">
         <x:v>Paints &gt; Specialty Paints</x:v>
       </x:c>
-      <x:c r="I390" t="str">
-        <x:v>terrazzo, terrazzo decorative silverado, paints, specialty paints</x:v>
+      <x:c r="I390" s="15" t="str">
+        <x:v>granite resurfacer, decorative floor resurfacer, anti-slip floor coating, acrylic floor coating</x:v>
       </x:c>
       <x:c r="J390" t="str">
         <x:v>Terrazzo</x:v>
@@ -20531,8 +20535,8 @@
       <x:c r="H391" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I391" t="str">
-        <x:v>trade secret, trade secret scratch remover, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I391" s="15" t="str">
+        <x:v>scratch remover, furniture repair product, wood finish restorer, surface polishing compound</x:v>
       </x:c>
       <x:c r="J391" t="str">
         <x:v>Trade Secret</x:v>
@@ -20586,8 +20590,8 @@
       <x:c r="H392" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I392" t="str">
-        <x:v>howard, howard wax it all, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I392" s="15" t="str">
+        <x:v>protective wax, paste wax, furniture wax, surface polish</x:v>
       </x:c>
       <x:c r="J392" t="str">
         <x:v>Howard</x:v>
@@ -20633,8 +20637,8 @@
       <x:c r="H393" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I393" t="str">
-        <x:v>pc products, dover classic fill sticks, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I393" s="15" t="str">
+        <x:v>fill stick, wax repair stick, wood repair filler, furniture touch-up product</x:v>
       </x:c>
       <x:c r="J393" t="str">
         <x:v>PC Products</x:v>
@@ -20680,8 +20684,8 @@
       <x:c r="H394" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I394" t="str">
-        <x:v>dover, caulking smoothing finger, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I394" s="15" t="str">
+        <x:v>caulk finishing tool, sealant smoothing tool, hand tool, caulking accessory</x:v>
       </x:c>
       <x:c r="J394" t="str">
         <x:v>Dover</x:v>
@@ -20727,8 +20731,8 @@
       <x:c r="H395" t="str">
         <x:v>Lacquer And Millwork Coatings &gt; Dover</x:v>
       </x:c>
-      <x:c r="I395" t="str">
-        <x:v>dover, dover pump touch-up marker - white, lacquer and millwork coatings</x:v>
+      <x:c r="I395" s="15" t="str">
+        <x:v>touch-up marker, wood repair marker, colour repair pen, finishing tool</x:v>
       </x:c>
       <x:c r="J395" t="str">
         <x:v>Dover</x:v>
@@ -20774,8 +20778,8 @@
       <x:c r="H396" t="str">
         <x:v>Lacquer And Millwork Coatings &gt; Dover</x:v>
       </x:c>
-      <x:c r="I396" t="str">
-        <x:v>dover, dover empty stain marker pen refill, lacquer and millwork coatings</x:v>
+      <x:c r="I396" s="15" t="str">
+        <x:v>touch-up marker, wood repair marker, colour repair pen, finishing tool</x:v>
       </x:c>
       <x:c r="J396" t="str">
         <x:v>Dover</x:v>
@@ -20821,8 +20825,8 @@
       <x:c r="H397" t="str">
         <x:v>Lacquer And Millwork Coatings &gt; Dover</x:v>
       </x:c>
-      <x:c r="I397" t="str">
-        <x:v>dover, dover spray universal walnut, lacquer and millwork coatings</x:v>
+      <x:c r="I397" s="15" t="str">
+        <x:v>touch-up spray, aerosol wood coating, furniture repair finish, spray lacquer</x:v>
       </x:c>
       <x:c r="J397" t="str">
         <x:v>Dover</x:v>
@@ -20868,8 +20872,8 @@
       <x:c r="H398" t="str">
         <x:v>Lacquer And Millwork Coatings &gt; Dover</x:v>
       </x:c>
-      <x:c r="I398" t="str">
-        <x:v>dover, dover spray gloss white, lacquer and millwork coatings</x:v>
+      <x:c r="I398" s="15" t="str">
+        <x:v>touch-up spray, aerosol wood coating, furniture repair finish, spray lacquer</x:v>
       </x:c>
       <x:c r="J398" t="str">
         <x:v>Dover</x:v>
@@ -20915,8 +20919,8 @@
       <x:c r="H399" t="str">
         <x:v>Lacquer And Millwork Coatings &gt; Dover</x:v>
       </x:c>
-      <x:c r="I399" t="str">
-        <x:v>dover, dover clear satin lacquer, lacquer and millwork coatings</x:v>
+      <x:c r="I399" s="15" t="str">
+        <x:v>clear finish, protective coating, clear coat, wood finish, lacquer, wood coating, fast-drying finish, solvent-based finish</x:v>
       </x:c>
       <x:c r="J399" t="str">
         <x:v>Dover</x:v>
@@ -20962,8 +20966,8 @@
       <x:c r="H400" t="str">
         <x:v>Lacquer And Millwork Coatings &gt; Dover</x:v>
       </x:c>
-      <x:c r="I400" t="str">
-        <x:v>dover, dover blush stopper/leveler, lacquer and millwork coatings</x:v>
+      <x:c r="I400" s="15" t="str">
+        <x:v>lacquer retarder, blush eliminator, finish additive, lacquer additive</x:v>
       </x:c>
       <x:c r="J400" t="str">
         <x:v>Dover</x:v>
@@ -21009,8 +21013,8 @@
       <x:c r="H401" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I401" t="str">
-        <x:v>skrapr, skrapr + skrapr jr, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I401" s="15" t="str">
+        <x:v>scraper, surface preparation tool, hand tool, painting tool</x:v>
       </x:c>
       <x:c r="J401" t="str">
         <x:v>Skrapr</x:v>
@@ -21056,8 +21060,8 @@
       <x:c r="H402" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I402" t="str">
-        <x:v>allpro, allpro dripless caulking gun 3000, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I402" s="15" t="str">
+        <x:v>caulking gun, sealant applicator, cartridge applicator, hand tool</x:v>
       </x:c>
       <x:c r="J402" t="str">
         <x:v>AllPro</x:v>
@@ -21103,8 +21107,8 @@
       <x:c r="H403" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I403" t="str">
-        <x:v>allpro, allpro dripless caulking gun 2000, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I403" s="15" t="str">
+        <x:v>caulking gun, sealant applicator, cartridge applicator, hand tool</x:v>
       </x:c>
       <x:c r="J403" t="str">
         <x:v>AllPro</x:v>
@@ -21150,8 +21154,8 @@
       <x:c r="H404" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I404" t="str">
-        <x:v>allpro, allpro consumer dripless gun, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I404" s="15" t="str">
+        <x:v>caulking gun, sealant applicator, cartridge applicator, hand tool</x:v>
       </x:c>
       <x:c r="J404" t="str">
         <x:v>AllPro</x:v>
@@ -21197,8 +21201,8 @@
       <x:c r="H405" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I405" t="str">
-        <x:v>dumond, watchdog wipe out graffiti remover 1, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I405" s="15" t="str">
+        <x:v>graffiti remover, coating remover, surface cleaner, solvent cleaner</x:v>
       </x:c>
       <x:c r="J405" t="str">
         <x:v>Dumond</x:v>
@@ -21244,8 +21248,8 @@
       <x:c r="H406" t="str">
         <x:v>Paints &gt; Interior</x:v>
       </x:c>
-      <x:c r="I406" t="str">
-        <x:v>duraseal, dura seal quick coat rosewood, paints, interior</x:v>
+      <x:c r="I406" s="15" t="str">
+        <x:v>wood floor stain, oil-based wood stain, quick-dry wood stain, interior wood finish</x:v>
       </x:c>
       <x:c r="J406" t="str">
         <x:v>DuraSeal</x:v>
@@ -21297,8 +21301,8 @@
       <x:c r="H407" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I407" t="str">
-        <x:v>famowood, famowood water-based wood filler, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I407" s="15" t="str">
+        <x:v>wood filler, wood repair compound, grain filler, surface repair product</x:v>
       </x:c>
       <x:c r="J407" t="str">
         <x:v>Famowood</x:v>
@@ -21352,8 +21356,8 @@
       <x:c r="H408" t="str">
         <x:v>Commercial &amp; Industrial &gt; Traffic Paints</x:v>
       </x:c>
-      <x:c r="I408" t="str">
-        <x:v>ennis-flint, ennis traffic paint fed. yellow, commercial &amp; industrial, traffic paints</x:v>
+      <x:c r="I408" s="15" t="str">
+        <x:v>traffic marking paint, line marking paint, industrial coating, pavement marking paint</x:v>
       </x:c>
       <x:c r="J408" t="str">
         <x:v>Ennis-Flint</x:v>
@@ -21405,8 +21409,8 @@
       <x:c r="H409" t="str">
         <x:v>Commercial &amp; Industrial &gt; Traffic Paints</x:v>
       </x:c>
-      <x:c r="I409" t="str">
-        <x:v>ennis-flint, ennis traffic paint fed. white - p, commercial &amp; industrial, traffic paints</x:v>
+      <x:c r="I409" s="15" t="str">
+        <x:v>traffic marking paint, line marking paint, industrial coating, pavement marking paint</x:v>
       </x:c>
       <x:c r="J409" t="str">
         <x:v>Ennis-Flint</x:v>
@@ -21458,8 +21462,8 @@
       <x:c r="H410" t="str">
         <x:v>Commercial &amp; Industrial &gt; Traffic Paints</x:v>
       </x:c>
-      <x:c r="I410" t="str">
-        <x:v>ennis-flint, ennis low voc red traffic paint, commercial &amp; industrial, traffic paints</x:v>
+      <x:c r="I410" s="15" t="str">
+        <x:v>traffic marking paint, line marking paint, industrial coating, pavement marking paint</x:v>
       </x:c>
       <x:c r="J410" t="str">
         <x:v>Ennis-Flint</x:v>
@@ -21505,8 +21509,8 @@
       <x:c r="H411" t="str">
         <x:v>Commercial &amp; Industrial &gt; Traffic Paints</x:v>
       </x:c>
-      <x:c r="I411" t="str">
-        <x:v>ennis-flint, ennis low voc green traffic paint, commercial &amp; industrial, traffic paints</x:v>
+      <x:c r="I411" s="15" t="str">
+        <x:v>traffic marking paint, line marking paint, industrial coating, pavement marking paint</x:v>
       </x:c>
       <x:c r="J411" t="str">
         <x:v>Ennis-Flint</x:v>
@@ -21552,8 +21556,8 @@
       <x:c r="H412" t="str">
         <x:v>Commercial &amp; Industrial &gt; Traffic Paints</x:v>
       </x:c>
-      <x:c r="I412" t="str">
-        <x:v>ennis-flint, ennis handicap blue safety paint, commercial &amp; industrial, traffic paints</x:v>
+      <x:c r="I412" s="15" t="str">
+        <x:v>traffic marking paint, line marking paint, industrial coating, pavement marking paint</x:v>
       </x:c>
       <x:c r="J412" t="str">
         <x:v>Ennis-Flint</x:v>
@@ -21605,8 +21609,8 @@
       <x:c r="H413" t="str">
         <x:v>Commercial &amp; Industrial &gt; Traffic Paints</x:v>
       </x:c>
-      <x:c r="I413" t="str">
-        <x:v>ennis-flint, blackout ennis traffic paint, commercial &amp; industrial, traffic paints</x:v>
+      <x:c r="I413" s="15" t="str">
+        <x:v>traffic marking paint, line marking paint, industrial coating, pavement marking paint</x:v>
       </x:c>
       <x:c r="J413" t="str">
         <x:v>Ennis-Flint</x:v>
@@ -21652,8 +21656,8 @@
       <x:c r="H414" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I414" t="str">
-        <x:v>featherlite, featherlite fiberglass ladder grade 1, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I414" s="15" t="str">
+        <x:v>step ladder, portable ladder, access equipment, jobsite equipment</x:v>
       </x:c>
       <x:c r="J414" t="str">
         <x:v>Featherlite</x:v>
@@ -21699,8 +21703,8 @@
       <x:c r="H415" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I415" t="str">
-        <x:v>featherlite, step ladder lite, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I415" s="15" t="str">
+        <x:v>step ladder, portable ladder, access equipment, jobsite equipment</x:v>
       </x:c>
       <x:c r="J415" t="str">
         <x:v>Featherlite</x:v>
@@ -21746,8 +21750,8 @@
       <x:c r="H416" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Festool</x:v>
       </x:c>
-      <x:c r="I416" t="str">
-        <x:v>festool, filter bag sc-fis-ct mini/midi -2/5, painting tools &amp; accessories</x:v>
+      <x:c r="I416" s="15" t="str">
+        <x:v>dust extractor bag, vacuum filter bag, dust collection accessory, replacement filter bag</x:v>
       </x:c>
       <x:c r="J416" t="str">
         <x:v>Festool</x:v>
@@ -21793,8 +21797,8 @@
       <x:c r="H417" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Festool</x:v>
       </x:c>
-      <x:c r="I417" t="str">
-        <x:v>festool, stickfix sandpa stf d225/8 p40 gr/25, painting tools &amp; accessories</x:v>
+      <x:c r="I417" s="15" t="str">
+        <x:v>sandpaper, coated abrasive, surface preparation abrasive, sanding material</x:v>
       </x:c>
       <x:c r="J417" t="str">
         <x:v>Festool</x:v>
@@ -21840,8 +21844,8 @@
       <x:c r="H418" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Festool</x:v>
       </x:c>
-      <x:c r="I418" t="str">
-        <x:v>festool, stickfix qty. stf 80x133 p 40 gr 50x, painting tools &amp; accessories</x:v>
+      <x:c r="I418" s="15" t="str">
+        <x:v>sandpaper, coated abrasive, surface preparation abrasive, sanding material</x:v>
       </x:c>
       <x:c r="J418" t="str">
         <x:v>Festool</x:v>
@@ -21887,8 +21891,8 @@
       <x:c r="H419" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Festool</x:v>
       </x:c>
-      <x:c r="I419" t="str">
-        <x:v>festool, sandpaper stf d125/8 p 40 gr 50x, painting tools &amp; accessories</x:v>
+      <x:c r="I419" s="15" t="str">
+        <x:v>sandpaper, coated abrasive, surface preparation abrasive, sanding material</x:v>
       </x:c>
       <x:c r="J419" t="str">
         <x:v>Festool</x:v>
@@ -21934,8 +21938,8 @@
       <x:c r="H420" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Festool</x:v>
       </x:c>
-      <x:c r="I420" t="str">
-        <x:v>festool, stickfix sandpa stf d90/6 p 40 gr / 50, painting tools &amp; accessories</x:v>
+      <x:c r="I420" s="15" t="str">
+        <x:v>sandpaper, coated abrasive, surface preparation abrasive, sanding material</x:v>
       </x:c>
       <x:c r="J420" t="str">
         <x:v>Festool</x:v>
@@ -21981,8 +21985,8 @@
       <x:c r="H421" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Festool</x:v>
       </x:c>
-      <x:c r="I421" t="str">
-        <x:v>festool, sandpaper stf v93/6 p 40 gr / 50, painting tools &amp; accessories</x:v>
+      <x:c r="I421" s="15" t="str">
+        <x:v>sandpaper, coated abrasive, surface preparation abrasive, sanding material</x:v>
       </x:c>
       <x:c r="J421" t="str">
         <x:v>Festool</x:v>
@@ -22028,8 +22032,8 @@
       <x:c r="H422" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Festool</x:v>
       </x:c>
-      <x:c r="I422" t="str">
-        <x:v>festool, sanding discs stf d150/48 p40 gr/50, painting tools &amp; accessories</x:v>
+      <x:c r="I422" s="15" t="str">
+        <x:v>sandpaper, coated abrasive, surface preparation abrasive, sanding material</x:v>
       </x:c>
       <x:c r="J422" t="str">
         <x:v>Festool</x:v>
@@ -22075,8 +22079,8 @@
       <x:c r="H423" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Festool</x:v>
       </x:c>
-      <x:c r="I423" t="str">
-        <x:v>festool, long-reach sand planex lhs 225 eq-plus, painting tools &amp; accessories</x:v>
+      <x:c r="I423" s="15" t="str">
+        <x:v>long-reach drywall sander, power sander, surface preparation tool, dust-extraction sander</x:v>
       </x:c>
       <x:c r="J423" t="str">
         <x:v>Festool</x:v>
@@ -22122,8 +22126,8 @@
       <x:c r="H424" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Festool</x:v>
       </x:c>
-      <x:c r="I424" t="str">
-        <x:v>festool, rotex ro 150 feq-plus usa 120v, painting tools &amp; accessories</x:v>
+      <x:c r="I424" s="15" t="str">
+        <x:v>power sander, orbital sander, surface preparation tool, power tool</x:v>
       </x:c>
       <x:c r="J424" t="str">
         <x:v>Festool</x:v>
@@ -22169,8 +22173,8 @@
       <x:c r="H425" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Festool</x:v>
       </x:c>
-      <x:c r="I425" t="str">
-        <x:v>festool, rotex ro 125 feq plus usa 120v, painting tools &amp; accessories</x:v>
+      <x:c r="I425" s="15" t="str">
+        <x:v>power sander, orbital sander, surface preparation tool, power tool</x:v>
       </x:c>
       <x:c r="J425" t="str">
         <x:v>Festool</x:v>
@@ -22216,8 +22220,8 @@
       <x:c r="H426" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Festool</x:v>
       </x:c>
-      <x:c r="I426" t="str">
-        <x:v>festool, orbital sander rts 400 req-plus usa, painting tools &amp; accessories</x:v>
+      <x:c r="I426" s="15" t="str">
+        <x:v>power sander, orbital sander, surface preparation tool, power tool</x:v>
       </x:c>
       <x:c r="J426" t="str">
         <x:v>Festool</x:v>
@@ -22263,8 +22267,8 @@
       <x:c r="H427" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Festool</x:v>
       </x:c>
-      <x:c r="I427" t="str">
-        <x:v>festool, festool ets 125 req-plus orbital sander, painting tools &amp; accessories</x:v>
+      <x:c r="I427" s="15" t="str">
+        <x:v>power sander, orbital sander, surface preparation tool, power tool</x:v>
       </x:c>
       <x:c r="J427" t="str">
         <x:v>Festool</x:v>
@@ -22310,8 +22314,8 @@
       <x:c r="H428" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Festool</x:v>
       </x:c>
-      <x:c r="I428" t="str">
-        <x:v>festool, rotex ro 90 dx feq-plus usa120, painting tools &amp; accessories</x:v>
+      <x:c r="I428" s="15" t="str">
+        <x:v>power sander, orbital sander, surface preparation tool, power tool</x:v>
       </x:c>
       <x:c r="J428" t="str">
         <x:v>Festool</x:v>
@@ -22357,8 +22361,8 @@
       <x:c r="H429" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Festool</x:v>
       </x:c>
-      <x:c r="I429" t="str">
-        <x:v>festool, orbital sander ets ec150/3 eq-plus, painting tools &amp; accessories</x:v>
+      <x:c r="I429" s="15" t="str">
+        <x:v>power sander, orbital sander, surface preparation tool, power tool</x:v>
       </x:c>
       <x:c r="J429" t="str">
         <x:v>Festool</x:v>
@@ -22404,8 +22408,8 @@
       <x:c r="H430" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Festool</x:v>
       </x:c>
-      <x:c r="I430" t="str">
-        <x:v>festool, ecc. grinder ets ec125/3 eq-plus usa, painting tools &amp; accessories</x:v>
+      <x:c r="I430" s="15" t="str">
+        <x:v>power sander, orbital sander, surface preparation tool, power tool</x:v>
       </x:c>
       <x:c r="J430" t="str">
         <x:v>Festool</x:v>
@@ -22451,8 +22455,8 @@
       <x:c r="H431" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Festool</x:v>
       </x:c>
-      <x:c r="I431" t="str">
-        <x:v>festool, diamond grinder rg 130 eci-plus renofix, painting tools &amp; accessories</x:v>
+      <x:c r="I431" s="15" t="str">
+        <x:v>concrete grinder, diamond grinder, surface preparation machine, power tool</x:v>
       </x:c>
       <x:c r="J431" t="str">
         <x:v>Festool</x:v>
@@ -22498,8 +22502,8 @@
       <x:c r="H432" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Festool</x:v>
       </x:c>
-      <x:c r="I432" t="str">
-        <x:v>festool, cordl. d.sander dtsc 400 li 3,1-plus usa, painting tools &amp; accessories</x:v>
+      <x:c r="I432" s="15" t="str">
+        <x:v>power sander, orbital sander, surface preparation tool, power tool</x:v>
       </x:c>
       <x:c r="J432" t="str">
         <x:v>Festool</x:v>
@@ -22545,8 +22549,8 @@
       <x:c r="H433" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Festool</x:v>
       </x:c>
-      <x:c r="I433" t="str">
-        <x:v>festool, delta sander dts 400 req-plus usa, painting tools &amp; accessories</x:v>
+      <x:c r="I433" s="15" t="str">
+        <x:v>power sander, orbital sander, surface preparation tool, power tool</x:v>
       </x:c>
       <x:c r="J433" t="str">
         <x:v>Festool</x:v>
@@ -22592,8 +22596,8 @@
       <x:c r="H434" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Festool</x:v>
       </x:c>
-      <x:c r="I434" t="str">
-        <x:v>festool, sandpaper stf delta/7 p 40 gr 50x, painting tools &amp; accessories</x:v>
+      <x:c r="I434" s="15" t="str">
+        <x:v>sandpaper, coated abrasive, surface preparation abrasive, sanding material</x:v>
       </x:c>
       <x:c r="J434" t="str">
         <x:v>Festool</x:v>
@@ -22639,8 +22643,8 @@
       <x:c r="H435" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Festool</x:v>
       </x:c>
-      <x:c r="I435" t="str">
-        <x:v>pc products, cordless drill t18+3 hpc 4,0 i-set, painting tools &amp; accessories, festool</x:v>
+      <x:c r="I435" s="15" t="str">
+        <x:v>cordless drill, drill driver, power tool, battery tool</x:v>
       </x:c>
       <x:c r="J435" t="str">
         <x:v>PC Products</x:v>
@@ -22686,8 +22690,8 @@
       <x:c r="H436" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Festool</x:v>
       </x:c>
-      <x:c r="I436" t="str">
-        <x:v>festool, festool cordless impact drill tid 18 basic, painting tools &amp; accessories</x:v>
+      <x:c r="I436" s="15" t="str">
+        <x:v>cordless impact driver, impact drill, power tool, battery tool</x:v>
       </x:c>
       <x:c r="J436" t="str">
         <x:v>Festool</x:v>
@@ -22733,8 +22737,8 @@
       <x:c r="H437" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Festool</x:v>
       </x:c>
-      <x:c r="I437" t="str">
-        <x:v>pc products, cordless impact drill tid 18 hpc 4,0 set, painting tools &amp; accessories, festool</x:v>
+      <x:c r="I437" s="15" t="str">
+        <x:v>cordless impact driver, impact drill, power tool, battery tool</x:v>
       </x:c>
       <x:c r="J437" t="str">
         <x:v>PC Products</x:v>
@@ -22780,8 +22784,8 @@
       <x:c r="H438" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Festool</x:v>
       </x:c>
-      <x:c r="I438" t="str">
-        <x:v>festool, dust extractor ct48 e ac hepa, painting tools &amp; accessories</x:v>
+      <x:c r="I438" s="15" t="str">
+        <x:v>dust extractor, hepa vacuum, power tool, dust collection equipment</x:v>
       </x:c>
       <x:c r="J438" t="str">
         <x:v>Festool</x:v>
@@ -22827,8 +22831,8 @@
       <x:c r="H439" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Festool</x:v>
       </x:c>
-      <x:c r="I439" t="str">
-        <x:v>festool, mobil dust extr ct15, painting tools &amp; accessories</x:v>
+      <x:c r="I439" s="15" t="str">
+        <x:v>dust extractor, hepa vacuum, power tool, dust collection equipment</x:v>
       </x:c>
       <x:c r="J439" t="str">
         <x:v>Festool</x:v>
@@ -22874,8 +22878,8 @@
       <x:c r="H440" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Festool</x:v>
       </x:c>
-      <x:c r="I440" t="str">
-        <x:v>festool, mobil dust extr ct midi usa hepa, painting tools &amp; accessories</x:v>
+      <x:c r="I440" s="15" t="str">
+        <x:v>dust extractor, hepa vacuum, power tool, dust collection equipment</x:v>
       </x:c>
       <x:c r="J440" t="str">
         <x:v>Festool</x:v>
@@ -22921,8 +22925,8 @@
       <x:c r="H441" t="str">
         <x:v>Paints &gt; Specialty Paints</x:v>
       </x:c>
-      <x:c r="I441" t="str">
-        <x:v>flame control, flame control finish coat low,semi,high, paints, specialty paints</x:v>
+      <x:c r="I441" s="15" t="str">
+        <x:v>fire-retardant paint, protective coating, interior coating, architectural paint</x:v>
       </x:c>
       <x:c r="J441" t="str">
         <x:v>Flame Control</x:v>
@@ -22982,8 +22986,8 @@
       <x:c r="H442" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I442" t="str">
-        <x:v>radius 360, radius 360 sanding tool, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I442" s="15" t="str">
+        <x:v>drywall sander, round sanding tool, hand sander, surface preparation tool</x:v>
       </x:c>
       <x:c r="J442" t="str">
         <x:v>Radius 360</x:v>
@@ -23029,8 +23033,8 @@
       <x:c r="H443" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I443" t="str">
-        <x:v>radius 360, radius 360 sanding disc 100 grit, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I443" s="15" t="str">
+        <x:v>sandpaper, coated abrasive, surface preparation abrasive, sanding material</x:v>
       </x:c>
       <x:c r="J443" t="str">
         <x:v>Radius 360</x:v>
@@ -23076,8 +23080,8 @@
       <x:c r="H444" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I444" t="str">
-        <x:v>radius 360, full circle flex edge replacement pad, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I444" s="15" t="str">
+        <x:v>sander replacement pad, sanding tool accessory, backing pad, surface preparation accessory</x:v>
       </x:c>
       <x:c r="J444" t="str">
         <x:v>Radius 360</x:v>
@@ -23123,8 +23127,8 @@
       <x:c r="H445" t="str">
         <x:v>Paints &gt; Driveway Coatings</x:v>
       </x:c>
-      <x:c r="I445" t="str">
-        <x:v>gh international, drive kote 10 year driveway sealer, paints, driveway coatings</x:v>
+      <x:c r="I445" s="15" t="str">
+        <x:v>driveway sealer, asphalt sealer, protective pavement coating, exterior coating</x:v>
       </x:c>
       <x:c r="J445" t="str">
         <x:v>GH International</x:v>
@@ -23176,8 +23180,8 @@
       <x:c r="H446" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I446" t="str">
-        <x:v>gorilla, gorilla wood glue, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I446" s="15" t="str">
+        <x:v>wood glue, woodworking adhesive, pva adhesive, interior and exterior adhesive</x:v>
       </x:c>
       <x:c r="J446" t="str">
         <x:v>Gorilla</x:v>
@@ -23223,8 +23227,8 @@
       <x:c r="H447" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I447" t="str">
-        <x:v>gorilla, gorilla tape crystal clear, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I447" s="15" t="str">
+        <x:v>clear repair tape, waterproof tape, pressure-sensitive tape, repair tape</x:v>
       </x:c>
       <x:c r="J447" t="str">
         <x:v>Gorilla</x:v>
@@ -23270,8 +23274,8 @@
       <x:c r="H448" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I448" t="str">
-        <x:v>gorilla, gorilla mounting tape, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I448" s="15" t="str">
+        <x:v>double-sided tape, mounting tape, pressure-sensitive adhesive, repair tape</x:v>
       </x:c>
       <x:c r="J448" t="str">
         <x:v>Gorilla</x:v>
@@ -23317,8 +23321,8 @@
       <x:c r="H449" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I449" t="str">
-        <x:v>gorilla, gorilla glue original, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I449" s="15" t="str">
+        <x:v>polyurethane adhesive, multi-purpose glue, moisture-curing adhesive, repair adhesive</x:v>
       </x:c>
       <x:c r="J449" t="str">
         <x:v>Gorilla</x:v>
@@ -23364,8 +23368,8 @@
       <x:c r="H450" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I450" t="str">
-        <x:v>gorilla, gorilla epoxy, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I450" s="15" t="str">
+        <x:v>epoxy adhesive, two-part epoxy, repair adhesive, structural adhesive</x:v>
       </x:c>
       <x:c r="J450" t="str">
         <x:v>Gorilla</x:v>
@@ -23411,8 +23415,8 @@
       <x:c r="H451" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I451" t="str">
-        <x:v>e-z mix, e-z mix cups, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I451" s="15" t="str">
+        <x:v>mixing cup, paint mixing container, graduated cup, painting accessory</x:v>
       </x:c>
       <x:c r="J451" t="str">
         <x:v>E-Z Mix</x:v>
@@ -23466,8 +23470,8 @@
       <x:c r="H452" t="str">
         <x:v>Lacquer And Millwork Coatings &gt; Goudey</x:v>
       </x:c>
-      <x:c r="I452" t="str">
-        <x:v>goudey, slik bottle fisheye eliminator, lacquer and millwork coatings</x:v>
+      <x:c r="I452" s="15" t="str">
+        <x:v>coating additive, fisheye eliminator, finish additive, paint additive</x:v>
       </x:c>
       <x:c r="J452" t="str">
         <x:v>Goudey</x:v>
@@ -23513,8 +23517,8 @@
       <x:c r="H453" t="str">
         <x:v>Specialty &amp; Decorative Products &gt; Gold Leaf</x:v>
       </x:c>
-      <x:c r="I453" t="str">
-        <x:v>nationale, nationale silver leaf 500 sheet box, specialty &amp; decorative products, gold leaf</x:v>
+      <x:c r="I453" s="15" t="str">
+        <x:v>silver leaf, metal leaf, gilding material, decorative finish</x:v>
       </x:c>
       <x:c r="J453" t="str">
         <x:v>Nationale</x:v>
@@ -23560,8 +23564,8 @@
       <x:c r="H454" t="str">
         <x:v>Specialty &amp; Decorative Products &gt; Gold Leaf</x:v>
       </x:c>
-      <x:c r="I454" t="str">
-        <x:v>nationale, nationale gold leaf 500 sheet box, specialty &amp; decorative products, gold leaf</x:v>
+      <x:c r="I454" s="15" t="str">
+        <x:v>gold leaf, metal leaf, gilding material, decorative finish</x:v>
       </x:c>
       <x:c r="J454" t="str">
         <x:v>Nationale</x:v>
@@ -23607,8 +23611,8 @@
       <x:c r="H455" t="str">
         <x:v>Lacquer And Millwork Coatings &gt; Goudey</x:v>
       </x:c>
-      <x:c r="I455" t="str">
-        <x:v>goudey, goudey ngr stain - red, lacquer and millwork coatings</x:v>
+      <x:c r="I455" s="15" t="str">
+        <x:v>non-grain-raising stain, dye stain, solvent-based wood stain, wood finish</x:v>
       </x:c>
       <x:c r="J455" t="str">
         <x:v>Goudey</x:v>
@@ -23654,8 +23658,8 @@
       <x:c r="H456" t="str">
         <x:v>Lacquer And Millwork Coatings &gt; Goudey</x:v>
       </x:c>
-      <x:c r="I456" t="str">
-        <x:v>goudey, goudey natural paste wood filler, lacquer and millwork coatings</x:v>
+      <x:c r="I456" s="15" t="str">
+        <x:v>wood filler, wood repair compound, grain filler, surface repair product</x:v>
       </x:c>
       <x:c r="J456" t="str">
         <x:v>Goudey</x:v>
@@ -23701,8 +23705,8 @@
       <x:c r="H457" t="str">
         <x:v>Lacquer And Millwork Coatings &gt; Goudey</x:v>
       </x:c>
-      <x:c r="I457" t="str">
-        <x:v>goudey, goudey acetone, lacquer and millwork coatings</x:v>
+      <x:c r="I457" s="15" t="str">
+        <x:v>acetone, finishing solvent, cleaning solvent, surface preparation solvent</x:v>
       </x:c>
       <x:c r="J457" t="str">
         <x:v>Goudey</x:v>
@@ -23748,8 +23752,8 @@
       <x:c r="H458" t="str">
         <x:v>Lacquer And Millwork Coatings &gt; Goudey</x:v>
       </x:c>
-      <x:c r="I458" t="str">
-        <x:v>goudey, dux water-based gilding size, lacquer and millwork coatings</x:v>
+      <x:c r="I458" s="15" t="str">
+        <x:v>gilding size, metal leaf adhesive, water-based adhesive, decorative finishing product</x:v>
       </x:c>
       <x:c r="J458" t="str">
         <x:v>Goudey</x:v>
@@ -23795,8 +23799,8 @@
       <x:c r="H459" t="str">
         <x:v>Spray Equipment Sales &amp; Service &gt; Graco</x:v>
       </x:c>
-      <x:c r="I459" t="str">
-        <x:v>graco, graco tip hd, spray equipment sales &amp; service</x:v>
+      <x:c r="I459" s="15" t="str">
+        <x:v>airless spray tip, sprayer nozzle, paint sprayer accessory, coating application part</x:v>
       </x:c>
       <x:c r="J459" t="str">
         <x:v>Graco</x:v>
@@ -23842,8 +23846,8 @@
       <x:c r="H460" t="str">
         <x:v>Spray Equipment Sales &amp; Service &gt; Graco</x:v>
       </x:c>
-      <x:c r="I460" t="str">
-        <x:v>graco, graco throat seal, spray equipment sales &amp; service</x:v>
+      <x:c r="I460" s="15" t="str">
+        <x:v>sprayer throat seal, pump seal, paint sprayer replacement part, spray equipment part</x:v>
       </x:c>
       <x:c r="J460" t="str">
         <x:v>Graco</x:v>
@@ -23889,8 +23893,8 @@
       <x:c r="H461" t="str">
         <x:v>Spray Equipment Sales &amp; Service &gt; Graco</x:v>
       </x:c>
-      <x:c r="I461" t="str">
-        <x:v>graco, graco rac 10 tip, spray equipment sales &amp; service</x:v>
+      <x:c r="I461" s="15" t="str">
+        <x:v>airless spray tip, sprayer nozzle, paint sprayer accessory, coating application part</x:v>
       </x:c>
       <x:c r="J461" t="str">
         <x:v>Graco</x:v>
@@ -23936,8 +23940,8 @@
       <x:c r="H462" t="str">
         <x:v>Spray Equipment Sales &amp; Service &gt; Graco</x:v>
       </x:c>
-      <x:c r="I462" t="str">
-        <x:v>graco, graco quickshot 3, spray equipment sales &amp; service</x:v>
+      <x:c r="I462" s="15" t="str">
+        <x:v>electric airless spray gun, paint sprayer, coating application equipment, professional spray equipment</x:v>
       </x:c>
       <x:c r="J462" t="str">
         <x:v>Graco</x:v>
@@ -23983,8 +23987,8 @@
       <x:c r="H463" t="str">
         <x:v>Spray Equipment Sales &amp; Service &gt; Graco</x:v>
       </x:c>
-      <x:c r="I463" t="str">
-        <x:v>graco, graco linelazer rac 5 switch tip, spray equipment sales &amp; service</x:v>
+      <x:c r="I463" s="15" t="str">
+        <x:v>airless spray tip, sprayer nozzle, paint sprayer accessory, coating application part</x:v>
       </x:c>
       <x:c r="J463" t="str">
         <x:v>Graco</x:v>
@@ -24030,8 +24034,8 @@
       <x:c r="H464" t="str">
         <x:v>Spray Equipment Sales &amp; Service &gt; Graco</x:v>
       </x:c>
-      <x:c r="I464" t="str">
-        <x:v>graco, graco flat tip, spray equipment sales &amp; service</x:v>
+      <x:c r="I464" s="15" t="str">
+        <x:v>airless spray tip, sprayer nozzle, paint sprayer accessory, coating application part</x:v>
       </x:c>
       <x:c r="J464" t="str">
         <x:v>Graco</x:v>
@@ -24077,8 +24081,8 @@
       <x:c r="H465" t="str">
         <x:v>Spray Equipment Sales &amp; Service &gt; Graco</x:v>
       </x:c>
-      <x:c r="I465" t="str">
-        <x:v>graco, graco finishpro gx19 120v, spray equipment sales &amp; service</x:v>
+      <x:c r="I465" s="15" t="str">
+        <x:v>paint sprayer, airless paint sprayer, coating application equipment, professional spray equipment</x:v>
       </x:c>
       <x:c r="J465" t="str">
         <x:v>Graco</x:v>
@@ -24124,8 +24128,8 @@
       <x:c r="H466" t="str">
         <x:v>Spray Equipment Sales &amp; Service &gt; Graco</x:v>
       </x:c>
-      <x:c r="I466" t="str">
-        <x:v>graco, graco fine finish tip 107, spray equipment sales &amp; service</x:v>
+      <x:c r="I466" s="15" t="str">
+        <x:v>airless spray tip, sprayer nozzle, paint sprayer accessory, coating application part</x:v>
       </x:c>
       <x:c r="J466" t="str">
         <x:v>Graco</x:v>
@@ -24171,8 +24175,8 @@
       <x:c r="H467" t="str">
         <x:v>Spray Equipment Sales &amp; Service &gt; Graco</x:v>
       </x:c>
-      <x:c r="I467" t="str">
-        <x:v>graco, graco filter, spray equipment sales &amp; service</x:v>
+      <x:c r="I467" s="15" t="str">
+        <x:v>spray gun filter, paint sprayer filter, spray equipment accessory, replacement filter</x:v>
       </x:c>
       <x:c r="J467" t="str">
         <x:v>Graco</x:v>
@@ -24218,8 +24222,8 @@
       <x:c r="H468" t="str">
         <x:v>Spray Equipment Sales &amp; Service &gt; Graco</x:v>
       </x:c>
-      <x:c r="I468" t="str">
-        <x:v>graco, graco contractor powershot gun, spray equipment sales &amp; service</x:v>
+      <x:c r="I468" s="15" t="str">
+        <x:v>airless spray gun, paint spray gun, coating application equipment, professional spray equipment</x:v>
       </x:c>
       <x:c r="J468" t="str">
         <x:v>Graco</x:v>
@@ -24265,8 +24269,8 @@
       <x:c r="H469" t="str">
         <x:v>Spray Equipment Sales &amp; Service &gt; Graco</x:v>
       </x:c>
-      <x:c r="I469" t="str">
-        <x:v>graco, graco ext, spray equipment sales &amp; service</x:v>
+      <x:c r="I469" s="15" t="str">
+        <x:v>spray gun extension, paint sprayer accessory, extension wand, coating application part</x:v>
       </x:c>
       <x:c r="J469" t="str">
         <x:v>Graco</x:v>
@@ -24312,8 +24316,8 @@
       <x:c r="H470" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Cleaners &amp; Removers</x:v>
       </x:c>
-      <x:c r="I470" t="str">
-        <x:v>grime eater, purple max cleaner + degreaser concentrate, painting tools &amp; accessories, cleaners &amp; removers</x:v>
+      <x:c r="I470" s="15" t="str">
+        <x:v>degreaser, heavy-duty cleaner, surface preparation cleaner, concentrated cleaner</x:v>
       </x:c>
       <x:c r="J470" t="str">
         <x:v>Grime Eater</x:v>
@@ -24359,8 +24363,8 @@
       <x:c r="H471" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Cleaners &amp; Removers</x:v>
       </x:c>
-      <x:c r="I471" t="str">
-        <x:v>grime eater, power maxx hand cleaner, painting tools &amp; accessories, cleaners &amp; removers</x:v>
+      <x:c r="I471" s="15" t="str">
+        <x:v>hand cleaner, industrial hand cleaner, degreasing soap, personal cleaning product</x:v>
       </x:c>
       <x:c r="J471" t="str">
         <x:v>Grime Eater</x:v>
@@ -24406,8 +24410,8 @@
       <x:c r="H472" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Cleaners &amp; Removers</x:v>
       </x:c>
-      <x:c r="I472" t="str">
-        <x:v>grime eater, power maxx hand cleaner - gal, painting tools &amp; accessories, cleaners &amp; removers</x:v>
+      <x:c r="I472" s="15" t="str">
+        <x:v>hand cleaner, industrial hand cleaner, degreasing soap, personal cleaning product</x:v>
       </x:c>
       <x:c r="J472" t="str">
         <x:v>Grime Eater</x:v>
@@ -24453,8 +24457,8 @@
       <x:c r="H473" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Cleaners &amp; Removers</x:v>
       </x:c>
-      <x:c r="I473" t="str">
-        <x:v>grime eater, grime eater orange hand cleaner, painting tools &amp; accessories, cleaners &amp; removers</x:v>
+      <x:c r="I473" s="15" t="str">
+        <x:v>degreaser, heavy-duty cleaner, surface preparation cleaner, concentrated cleaner, hand cleaner, industrial hand cleaner, degreasing soap, personal cleaning product</x:v>
       </x:c>
       <x:c r="J473" t="str">
         <x:v>Grime Eater</x:v>
@@ -24500,8 +24504,8 @@
       <x:c r="H474" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I474" t="str">
-        <x:v>handy paint pail, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I474" s="15" t="str">
+        <x:v>paint pail, paint container, mixing container, painting accessory</x:v>
       </x:c>
       <x:c r="J474" t="str">
         <x:v>Handy Paint Pail</x:v>
@@ -24547,8 +24551,8 @@
       <x:c r="H475" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I475" t="str">
-        <x:v>handy paint pail, handy pail liners, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I475" s="15" t="str">
+        <x:v>paint container liner, disposable liner, painting accessory, paint pail accessory</x:v>
       </x:c>
       <x:c r="J475" t="str">
         <x:v>Handy Paint Pail</x:v>
@@ -24594,8 +24598,8 @@
       <x:c r="H476" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I476" t="str">
-        <x:v>holland, shoppro cordless led tripod worklight, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I476" s="15" t="str">
+        <x:v>work light, led work light, jobsite lighting, portable light</x:v>
       </x:c>
       <x:c r="J476" t="str">
         <x:v>Holland</x:v>
@@ -24641,8 +24645,8 @@
       <x:c r="H477" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I477" t="str">
-        <x:v>holland, 360 degree cannon work light, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I477" s="15" t="str">
+        <x:v>work light, led work light, jobsite lighting, portable light</x:v>
       </x:c>
       <x:c r="J477" t="str">
         <x:v>Holland</x:v>
@@ -24688,8 +24692,8 @@
       <x:c r="H478" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I478" t="str">
-        <x:v>j-b weld, j-b weld superweld epoxy, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I478" s="15" t="str">
+        <x:v>epoxy adhesive, two-part epoxy, repair adhesive, structural adhesive</x:v>
       </x:c>
       <x:c r="J478" t="str">
         <x:v>J-B Weld</x:v>
@@ -24735,8 +24739,8 @@
       <x:c r="H479" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I479" t="str">
-        <x:v>j-b weld, j-b weld original cold weld, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I479" s="15" t="str">
+        <x:v>epoxy adhesive, two-part epoxy, repair adhesive, structural adhesive</x:v>
       </x:c>
       <x:c r="J479" t="str">
         <x:v>J-B Weld</x:v>
@@ -24782,8 +24786,8 @@
       <x:c r="H480" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I480" t="str">
-        <x:v>j-b weld, j-b weld minuteweld epoxy syringe, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I480" s="15" t="str">
+        <x:v>epoxy adhesive, two-part epoxy, repair adhesive, structural adhesive</x:v>
       </x:c>
       <x:c r="J480" t="str">
         <x:v>J-B Weld</x:v>
@@ -24829,8 +24833,8 @@
       <x:c r="H481" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I481" t="str">
-        <x:v>jen, jen 2" foam brush, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I481" s="15" t="str">
+        <x:v>foam brush, disposable paint brush, paint applicator, painting tool</x:v>
       </x:c>
       <x:c r="J481" t="str">
         <x:v>Jen</x:v>
@@ -24876,8 +24880,8 @@
       <x:c r="H482" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I482" t="str">
-        <x:v>klingspor, wet sanding paper 1500 grit, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I482" s="15" t="str">
+        <x:v>sandpaper, coated abrasive, surface preparation abrasive, sanding material, wet sandpaper</x:v>
       </x:c>
       <x:c r="J482" t="str">
         <x:v>Klingspor</x:v>
@@ -24923,8 +24927,8 @@
       <x:c r="H483" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I483" t="str">
-        <x:v>klingspor, 50 yrd roll 100 grit sandpaper, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I483" s="15" t="str">
+        <x:v>sandpaper, coated abrasive, surface preparation abrasive, sanding material</x:v>
       </x:c>
       <x:c r="J483" t="str">
         <x:v>Klingspor</x:v>
@@ -24970,8 +24974,8 @@
       <x:c r="H484" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I484" t="str">
-        <x:v>klingspor, 25 yard roll red sandpaper 100 grit, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I484" s="15" t="str">
+        <x:v>sandpaper, coated abrasive, surface preparation abrasive, sanding material</x:v>
       </x:c>
       <x:c r="J484" t="str">
         <x:v>Klingspor</x:v>
@@ -25017,8 +25021,8 @@
       <x:c r="H485" t="str">
         <x:v>Paints &gt; Aerosols</x:v>
       </x:c>
-      <x:c r="I485" t="str">
-        <x:v>krylon, krylon metallic silver, paints, aerosols</x:v>
+      <x:c r="I485" s="15" t="str">
+        <x:v>metallic paint, decorative coating, specialty paint, metallic finish, spray paint, aerosol paint, specialty coating</x:v>
       </x:c>
       <x:c r="J485" t="str">
         <x:v>Krylon</x:v>
@@ -25067,8 +25071,8 @@
       <x:c r="H486" t="str">
         <x:v>Paints &gt; Aerosols</x:v>
       </x:c>
-      <x:c r="I486" t="str">
-        <x:v>krylon, krylon fusion satin black, paints, aerosols</x:v>
+      <x:c r="I486" s="15" t="str">
+        <x:v>spray paint, aerosol paint, specialty coating, decorative coating</x:v>
       </x:c>
       <x:c r="J486" t="str">
         <x:v>Krylon</x:v>
@@ -25120,8 +25124,8 @@
       <x:c r="H487" t="str">
         <x:v>Paints &gt; Aerosols</x:v>
       </x:c>
-      <x:c r="I487" t="str">
-        <x:v>krylon, krylon fusion metallic gold, paints, aerosols</x:v>
+      <x:c r="I487" s="15" t="str">
+        <x:v>metallic paint, decorative coating, specialty paint, metallic finish, spray paint, aerosol paint, specialty coating</x:v>
       </x:c>
       <x:c r="J487" t="str">
         <x:v>Krylon</x:v>
@@ -25170,8 +25174,8 @@
       <x:c r="H488" t="str">
         <x:v>Paints &gt; Aerosols</x:v>
       </x:c>
-      <x:c r="I488" t="str">
-        <x:v>krylon, krylon fusion gloss black, paints, aerosols</x:v>
+      <x:c r="I488" s="15" t="str">
+        <x:v>spray paint, aerosol paint, specialty coating, decorative coating</x:v>
       </x:c>
       <x:c r="J488" t="str">
         <x:v>Krylon</x:v>
@@ -25223,8 +25227,8 @@
       <x:c r="H489" t="str">
         <x:v>Paints &gt; Aerosols</x:v>
       </x:c>
-      <x:c r="I489" t="str">
-        <x:v>krylon, krylon fusion flat black, paints, aerosols</x:v>
+      <x:c r="I489" s="15" t="str">
+        <x:v>spray paint, aerosol paint, specialty coating, decorative coating</x:v>
       </x:c>
       <x:c r="J489" t="str">
         <x:v>Krylon</x:v>
@@ -25276,8 +25280,8 @@
       <x:c r="H490" t="str">
         <x:v>Paints &gt; Exterior</x:v>
       </x:c>
-      <x:c r="I490" t="str">
-        <x:v>last n last, last n last satin spar varnish, paints, exterior</x:v>
+      <x:c r="I490" s="15" t="str">
+        <x:v>spar varnish, exterior varnish, clear wood finish, oil-based wood finish</x:v>
       </x:c>
       <x:c r="J490" t="str">
         <x:v>Last n Last</x:v>
@@ -25329,8 +25333,8 @@
       <x:c r="H491" t="str">
         <x:v>Paints &gt; Exterior</x:v>
       </x:c>
-      <x:c r="I491" t="str">
-        <x:v>last n last, last n last oil gloss urethane 350 voc, paints, exterior</x:v>
+      <x:c r="I491" s="15" t="str">
+        <x:v>oil-based polyurethane, clear wood finish, floor finish, gloss varnish</x:v>
       </x:c>
       <x:c r="J491" t="str">
         <x:v>Last n Last</x:v>
@@ -25379,8 +25383,8 @@
       <x:c r="H492" t="str">
         <x:v>Paints &gt; Stains &amp; Varnishes</x:v>
       </x:c>
-      <x:c r="I492" t="str">
-        <x:v>last n last, absco polyurethane wood floor finish sat, paints, stains &amp; varnishes</x:v>
+      <x:c r="I492" s="15" t="str">
+        <x:v>floor varnish, wood floor finish, clear wood finish, protective coating</x:v>
       </x:c>
       <x:c r="J492" t="str">
         <x:v>Last n Last</x:v>
@@ -25429,8 +25433,8 @@
       <x:c r="H493" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I493" t="str">
-        <x:v>leaktite, leaktite multi-purpose mixing pail, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I493" s="15" t="str">
+        <x:v>paint pail, paint container, mixing container, painting accessory</x:v>
       </x:c>
       <x:c r="J493" t="str">
         <x:v>Leaktite</x:v>
@@ -25484,8 +25488,8 @@
       <x:c r="H494" t="str">
         <x:v>Spray Equipment Sales &amp; Service &gt; Lemmer</x:v>
       </x:c>
-      <x:c r="I494" t="str">
-        <x:v>lemmer, lemmer pot liners, spray equipment sales &amp; service</x:v>
+      <x:c r="I494" s="15" t="str">
+        <x:v>paint container liner, disposable liner, painting accessory, paint pail accessory</x:v>
       </x:c>
       <x:c r="J494" t="str">
         <x:v>Lemmer</x:v>
@@ -25531,8 +25535,8 @@
       <x:c r="H495" t="str">
         <x:v>Spray Equipment Sales &amp; Service &gt; Lemmer</x:v>
       </x:c>
-      <x:c r="I495" t="str">
-        <x:v>lemmer, lemmer gravity gun conv, spray equipment sales &amp; service</x:v>
+      <x:c r="I495" s="15" t="str">
+        <x:v>gravity-feed spray gun, paint spray gun, coating application equipment, pneumatic spray equipment</x:v>
       </x:c>
       <x:c r="J495" t="str">
         <x:v>Lemmer</x:v>
@@ -25578,8 +25582,8 @@
       <x:c r="H496" t="str">
         <x:v>Spray Equipment Sales &amp; Service &gt; Lemmer</x:v>
       </x:c>
-      <x:c r="I496" t="str">
-        <x:v>lemmer, lemmer pot, gun, hose complete, spray equipment sales &amp; service</x:v>
+      <x:c r="I496" s="15" t="str">
+        <x:v>pressure-feed spray system, paint spray gun, paint pressure pot, spray hose kit</x:v>
       </x:c>
       <x:c r="J496" t="str">
         <x:v>Lemmer</x:v>
@@ -25625,8 +25629,8 @@
       <x:c r="H497" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I497" t="str">
-        <x:v>pc products, pc-woody wood epoxy paste, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I497" s="15" t="str">
+        <x:v>wood repair epoxy, wood filler, two-part epoxy, repair compound, epoxy paste, repair adhesive</x:v>
       </x:c>
       <x:c r="J497" t="str">
         <x:v>PC Products</x:v>
@@ -25672,8 +25676,8 @@
       <x:c r="H498" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I498" t="str">
-        <x:v>pc products, pc-clear liquid epoxy, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I498" s="15" t="str">
+        <x:v>epoxy adhesive, two-part epoxy, repair adhesive, structural adhesive</x:v>
       </x:c>
       <x:c r="J498" t="str">
         <x:v>PC Products</x:v>
@@ -25719,8 +25723,8 @@
       <x:c r="H499" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I499" t="str">
-        <x:v>pc products, pc petrifier wood hardener, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I499" s="15" t="str">
+        <x:v>wood hardener, wood consolidant, wood repair treatment, penetrating resin</x:v>
       </x:c>
       <x:c r="J499" t="str">
         <x:v>PC Products</x:v>
@@ -25766,8 +25770,8 @@
       <x:c r="H500" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I500" t="str">
-        <x:v>pc products, pc lumber, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I500" s="15" t="str">
+        <x:v>wood repair epoxy, epoxy putty, wood filler, moldable repair compound</x:v>
       </x:c>
       <x:c r="J500" t="str">
         <x:v>PC Products</x:v>
@@ -25813,8 +25817,8 @@
       <x:c r="H501" t="str">
         <x:v>Paints &gt; Aerosols</x:v>
       </x:c>
-      <x:c r="I501" t="str">
-        <x:v>kilz, kilz low voc spray can, paints, aerosols</x:v>
+      <x:c r="I501" s="15" t="str">
+        <x:v>spray primer, aerosol primer, low-voc primer, stain-blocking primer</x:v>
       </x:c>
       <x:c r="J501" t="str">
         <x:v>KILZ</x:v>
@@ -25863,8 +25867,8 @@
       <x:c r="H502" t="str">
         <x:v>Specialty &amp; Decorative Products &gt; Meoded Plasters</x:v>
       </x:c>
-      <x:c r="I502" t="str">
-        <x:v>meoded, tonachino firenze white, specialty &amp; decorative products, meoded plasters</x:v>
+      <x:c r="I502" s="15" t="str">
+        <x:v>lime plaster, venetian plaster, decorative plaster, interior wall finish</x:v>
       </x:c>
       <x:c r="J502" t="str">
         <x:v>Meoded</x:v>
@@ -25916,8 +25920,8 @@
       <x:c r="H503" t="str">
         <x:v>Specialty &amp; Decorative Products &gt; Meoded Plasters</x:v>
       </x:c>
-      <x:c r="I503" t="str">
-        <x:v>meoded, stucco lamundo, specialty &amp; decorative products, meoded plasters</x:v>
+      <x:c r="I503" s="15" t="str">
+        <x:v>lime plaster, venetian plaster, decorative plaster, polished wall finish</x:v>
       </x:c>
       <x:c r="J503" t="str">
         <x:v>Meoded</x:v>
@@ -25969,8 +25973,8 @@
       <x:c r="H504" t="str">
         <x:v>Specialty &amp; Decorative Products &gt; Meoded Plasters</x:v>
       </x:c>
-      <x:c r="I504" t="str">
-        <x:v>meoded, meoded stain shield sealer, specialty &amp; decorative products, meoded plasters</x:v>
+      <x:c r="I504" s="15" t="str">
+        <x:v>plaster sealer, protective clear coat, decorative finish sealer, interior wall coating</x:v>
       </x:c>
       <x:c r="J504" t="str">
         <x:v>Meoded</x:v>
@@ -26022,8 +26026,8 @@
       <x:c r="H505" t="str">
         <x:v>Specialty &amp; Decorative Products &gt; Meoded Plasters</x:v>
       </x:c>
-      <x:c r="I505" t="str">
-        <x:v>meoded, plaster seal plus 3 part quart, specialty &amp; decorative products, meoded plasters</x:v>
+      <x:c r="I505" s="15" t="str">
+        <x:v>plaster sealer, three-part sealer, decorative plaster finish, protective clear coat</x:v>
       </x:c>
       <x:c r="J505" t="str">
         <x:v>Meoded</x:v>
@@ -26075,8 +26079,8 @@
       <x:c r="H506" t="str">
         <x:v>Specialty &amp; Decorative Products &gt; Meoded Plasters</x:v>
       </x:c>
-      <x:c r="I506" t="str">
-        <x:v>meoded, meoded plaster guard sealer, specialty &amp; decorative products, meoded plasters</x:v>
+      <x:c r="I506" s="15" t="str">
+        <x:v>plaster sealer, protective clear coat, decorative finish sealer, interior wall coating, decorative plaster, textured wall finish, specialty finish</x:v>
       </x:c>
       <x:c r="J506" t="str">
         <x:v>Meoded</x:v>
@@ -26136,8 +26140,8 @@
       <x:c r="H507" t="str">
         <x:v>Specialty &amp; Decorative Products &gt; Meoded Plasters</x:v>
       </x:c>
-      <x:c r="I507" t="str">
-        <x:v>meoded, pearlas velvet white, specialty &amp; decorative products, meoded plasters</x:v>
+      <x:c r="I507" s="15" t="str">
+        <x:v>suede paint, metallic suede paint, water-based decorative paint, interior wall coating</x:v>
       </x:c>
       <x:c r="J507" t="str">
         <x:v>Meoded</x:v>
@@ -26189,8 +26193,8 @@
       <x:c r="H508" t="str">
         <x:v>Specialty &amp; Decorative Products &gt; Meoded Plasters</x:v>
       </x:c>
-      <x:c r="I508" t="str">
-        <x:v>meoded, meoded quartz primer, specialty &amp; decorative products, meoded plasters</x:v>
+      <x:c r="I508" s="15" t="str">
+        <x:v>primer, primer sealer, surface preparation coating, basecoat, quartz primer, plaster bonding primer, textured primer, decorative finish basecoat</x:v>
       </x:c>
       <x:c r="J508" t="str">
         <x:v>Meoded</x:v>
@@ -26242,8 +26246,8 @@
       <x:c r="H509" t="str">
         <x:v>Specialty &amp; Decorative Products &gt; Meoded Plasters</x:v>
       </x:c>
-      <x:c r="I509" t="str">
-        <x:v>meoded, meoded moroccan clay, specialty &amp; decorative products, meoded plasters</x:v>
+      <x:c r="I509" s="15" t="str">
+        <x:v>clay plaster, natural wall plaster, decorative plaster, interior wall finish</x:v>
       </x:c>
       <x:c r="J509" t="str">
         <x:v>Meoded</x:v>
@@ -26295,8 +26299,8 @@
       <x:c r="H510" t="str">
         <x:v>Specialty &amp; Decorative Products &gt; Meoded Plasters</x:v>
       </x:c>
-      <x:c r="I510" t="str">
-        <x:v>meoded, meoded lime wash, specialty &amp; decorative products, meoded plasters</x:v>
+      <x:c r="I510" s="15" t="str">
+        <x:v>limewash paint, mineral paint, decorative wall finish, matte wall coating</x:v>
       </x:c>
       <x:c r="J510" t="str">
         <x:v>Meoded</x:v>
@@ -26348,8 +26352,8 @@
       <x:c r="H511" t="str">
         <x:v>Specialty &amp; Decorative Products &gt; Meoded Plasters</x:v>
       </x:c>
-      <x:c r="I511" t="str">
-        <x:v>meoded, marmorino palladino, specialty &amp; decorative products, meoded plasters</x:v>
+      <x:c r="I511" s="15" t="str">
+        <x:v>lime plaster, venetian plaster, decorative plaster, interior wall finish</x:v>
       </x:c>
       <x:c r="J511" t="str">
         <x:v>Meoded</x:v>
@@ -26401,8 +26405,8 @@
       <x:c r="H512" t="str">
         <x:v>Specialty &amp; Decorative Products &gt; Meoded Plasters</x:v>
       </x:c>
-      <x:c r="I512" t="str">
-        <x:v>meoded, lime wash brush 50x150, specialty &amp; decorative products, meoded plasters</x:v>
+      <x:c r="I512" s="15" t="str">
+        <x:v>limewash brush, masonry brush, paint applicator, painting tool</x:v>
       </x:c>
       <x:c r="J512" t="str">
         <x:v>Meoded</x:v>
@@ -26448,8 +26452,8 @@
       <x:c r="H513" t="str">
         <x:v>Specialty &amp; Decorative Products &gt; Meoded Plasters</x:v>
       </x:c>
-      <x:c r="I513" t="str">
-        <x:v>meoded, hydrowax gallon water soluble wax, specialty &amp; decorative products, meoded plasters</x:v>
+      <x:c r="I513" s="15" t="str">
+        <x:v>decorative plaster wax, protective wax finish, wall finish sealer, decorative finishing product</x:v>
       </x:c>
       <x:c r="J513" t="str">
         <x:v>Meoded</x:v>
@@ -26501,8 +26505,8 @@
       <x:c r="H514" t="str">
         <x:v>Specialty &amp; Decorative Products &gt; Meoded Plasters</x:v>
       </x:c>
-      <x:c r="I514" t="str">
-        <x:v>meoded, golmex concrete look, specialty &amp; decorative products, meoded plasters</x:v>
+      <x:c r="I514" s="15" t="str">
+        <x:v>concrete-look plaster, decorative plaster, cement-look wall finish, interior wall coating</x:v>
       </x:c>
       <x:c r="J514" t="str">
         <x:v>Meoded</x:v>
@@ -26554,8 +26558,8 @@
       <x:c r="H515" t="str">
         <x:v>Specialty &amp; Decorative Products &gt; Meoded Plasters</x:v>
       </x:c>
-      <x:c r="I515" t="str">
-        <x:v>meoded, crystal brush white base, specialty &amp; decorative products, meoded plasters</x:v>
+      <x:c r="I515" s="15" t="str">
+        <x:v>decorative paint brush, specialty finish brush, paint applicator, painting tool</x:v>
       </x:c>
       <x:c r="J515" t="str">
         <x:v>Meoded</x:v>
@@ -26607,8 +26611,8 @@
       <x:c r="H516" t="str">
         <x:v>Specialty &amp; Decorative Products &gt; Meoded Plasters</x:v>
       </x:c>
-      <x:c r="I516" t="str">
-        <x:v>meoded, cristallo clear coat matte, specialty &amp; decorative products, meoded plasters</x:v>
+      <x:c r="I516" s="15" t="str">
+        <x:v>decorative plaster clear coat, matte clear finish, protective coating, interior wall finish</x:v>
       </x:c>
       <x:c r="J516" t="str">
         <x:v>Meoded</x:v>
@@ -26660,8 +26664,8 @@
       <x:c r="H517" t="str">
         <x:v>Specialty &amp; Decorative Products &gt; Meoded Plasters</x:v>
       </x:c>
-      <x:c r="I517" t="str">
-        <x:v>meoded, concretta fs white, specialty &amp; decorative products, meoded plasters</x:v>
+      <x:c r="I517" s="15" t="str">
+        <x:v>concrete-look plaster, decorative plaster, cement-look wall finish, interior wall coating</x:v>
       </x:c>
       <x:c r="J517" t="str">
         <x:v>Meoded</x:v>
@@ -26713,8 +26717,8 @@
       <x:c r="H518" t="str">
         <x:v>Paints &gt; Exterior</x:v>
       </x:c>
-      <x:c r="I518" t="str">
-        <x:v>messmer's, messmers uv plus natural, paints, exterior</x:v>
+      <x:c r="I518" s="15" t="str">
+        <x:v>exterior wood stain, penetrating wood finish, wood stain, exterior wood finish</x:v>
       </x:c>
       <x:c r="J518" t="str">
         <x:v>Messmer's</x:v>
@@ -26766,8 +26770,8 @@
       <x:c r="H519" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I519" t="str">
-        <x:v>metaltech, metaltech scaffold aluminum, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I519" s="15" t="str">
+        <x:v>scaffold, mobile scaffold, access equipment, jobsite equipment</x:v>
       </x:c>
       <x:c r="J519" t="str">
         <x:v>Metaltech</x:v>
@@ -26813,8 +26817,8 @@
       <x:c r="H520" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I520" t="str">
-        <x:v>metaltech, metaltech yellow baker scaffold, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I520" s="15" t="str">
+        <x:v>scaffold, mobile scaffold, access equipment, jobsite equipment</x:v>
       </x:c>
       <x:c r="J520" t="str">
         <x:v>Metaltech</x:v>
@@ -26860,8 +26864,8 @@
       <x:c r="H521" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I521" t="str">
-        <x:v>metaltech, metaltech portable work platform, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I521" s="15" t="str">
+        <x:v>work platform, portable platform, access equipment, jobsite equipment</x:v>
       </x:c>
       <x:c r="J521" t="str">
         <x:v>Metaltech</x:v>
@@ -26907,8 +26911,8 @@
       <x:c r="H522" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I522" t="str">
-        <x:v>metaltech, metaltech aluminum step ladder, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I522" s="15" t="str">
+        <x:v>step ladder, portable ladder, access equipment, jobsite equipment</x:v>
       </x:c>
       <x:c r="J522" t="str">
         <x:v>Metaltech</x:v>
@@ -26954,8 +26958,8 @@
       <x:c r="H523" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I523" t="str">
-        <x:v>minwax, minwax wood putty 910 golden oak, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I523" s="15" t="str">
+        <x:v>wood filler, wood repair compound, grain filler, surface repair product</x:v>
       </x:c>
       <x:c r="J523" t="str">
         <x:v>Minwax</x:v>
@@ -27001,8 +27005,8 @@
       <x:c r="H524" t="str">
         <x:v>Paints &gt; Stains &amp; Varnishes</x:v>
       </x:c>
-      <x:c r="I524" t="str">
-        <x:v>minwax, minwax wood filler, paints, stains &amp; varnishes</x:v>
+      <x:c r="I524" s="15" t="str">
+        <x:v>wood filler, wood repair compound, grain filler, surface repair product</x:v>
       </x:c>
       <x:c r="J524" t="str">
         <x:v>Minwax</x:v>
@@ -27048,8 +27052,8 @@
       <x:c r="H525" t="str">
         <x:v>Paints &gt; Stains &amp; Varnishes</x:v>
       </x:c>
-      <x:c r="I525" t="str">
-        <x:v>minwax, minwax wipe-on poly, paints, stains &amp; varnishes</x:v>
+      <x:c r="I525" s="15" t="str">
+        <x:v>wipe-on polyurethane, polyurethane finish, clear wood finish, oil-based wood finish</x:v>
       </x:c>
       <x:c r="J525" t="str">
         <x:v>Minwax</x:v>
@@ -27109,8 +27113,8 @@
       <x:c r="H526" t="str">
         <x:v>Paints &gt; Stains &amp; Varnishes</x:v>
       </x:c>
-      <x:c r="I526" t="str">
-        <x:v>minwax, minwax tung oil, paints, stains &amp; varnishes</x:v>
+      <x:c r="I526" s="15" t="str">
+        <x:v>tung oil finish, drying oil, wood finish, oil-based finish</x:v>
       </x:c>
       <x:c r="J526" t="str">
         <x:v>Minwax</x:v>
@@ -27162,8 +27166,8 @@
       <x:c r="H527" t="str">
         <x:v>Paints &gt; Stains &amp; Varnishes</x:v>
       </x:c>
-      <x:c r="I527" t="str">
-        <x:v>minwax, minwax teak oil, paints, stains &amp; varnishes</x:v>
+      <x:c r="I527" s="15" t="str">
+        <x:v>teak oil finish, penetrating oil finish, wood finish, oil-based finish</x:v>
       </x:c>
       <x:c r="J527" t="str">
         <x:v>Minwax</x:v>
@@ -27212,8 +27216,8 @@
       <x:c r="H528" t="str">
         <x:v>Paints &gt; Stains &amp; Varnishes</x:v>
       </x:c>
-      <x:c r="I528" t="str">
-        <x:v>minwax, minwax stainable wood filler, paints, stains &amp; varnishes</x:v>
+      <x:c r="I528" s="15" t="str">
+        <x:v>wood filler, wood repair compound, grain filler, surface repair product</x:v>
       </x:c>
       <x:c r="J528" t="str">
         <x:v>Minwax</x:v>
@@ -27259,8 +27263,8 @@
       <x:c r="H529" t="str">
         <x:v>Paints &gt; Stains &amp; Varnishes</x:v>
       </x:c>
-      <x:c r="I529" t="str">
-        <x:v>minwax, minwax paste wax, paints, stains &amp; varnishes</x:v>
+      <x:c r="I529" s="15" t="str">
+        <x:v>paste wax, wood wax, wood finish, protective wax finish</x:v>
       </x:c>
       <x:c r="J529" t="str">
         <x:v>Minwax</x:v>
@@ -27312,8 +27316,8 @@
       <x:c r="H530" t="str">
         <x:v>Paints &gt; Stains &amp; Varnishes</x:v>
       </x:c>
-      <x:c r="I530" t="str">
-        <x:v>minwax, minwax wood finish stain - golden oak, paints, stains &amp; varnishes</x:v>
+      <x:c r="I530" s="15" t="str">
+        <x:v>oil-based wood stain, wood stain, wood finish, penetrating finish</x:v>
       </x:c>
       <x:c r="J530" t="str">
         <x:v>Minwax</x:v>
@@ -27365,8 +27369,8 @@
       <x:c r="H531" t="str">
         <x:v>Paints &gt; Stains &amp; Varnishes</x:v>
       </x:c>
-      <x:c r="I531" t="str">
-        <x:v>minwax, antique oil finish, paints, stains &amp; varnishes</x:v>
+      <x:c r="I531" s="15" t="str">
+        <x:v>oil-based wood stain, wood stain, wood finish, penetrating finish</x:v>
       </x:c>
       <x:c r="J531" t="str">
         <x:v>Minwax</x:v>
@@ -27418,8 +27422,8 @@
       <x:c r="H532" t="str">
         <x:v>Paints &gt; Stains &amp; Varnishes</x:v>
       </x:c>
-      <x:c r="I532" t="str">
-        <x:v>minwax, minwax pre-stain wood conditioner, paints, stains &amp; varnishes</x:v>
+      <x:c r="I532" s="15" t="str">
+        <x:v>wood conditioner, pre-stain treatment, wood preparation product, wood finishing basecoat</x:v>
       </x:c>
       <x:c r="J532" t="str">
         <x:v>Minwax</x:v>
@@ -27471,8 +27475,8 @@
       <x:c r="H533" t="str">
         <x:v>Specialty &amp; Decorative Products &gt; Modern Masters</x:v>
       </x:c>
-      <x:c r="I533" t="str">
-        <x:v>modern masters, modern masters metallic paint - flash gold, specialty &amp; decorative products</x:v>
+      <x:c r="I533" s="15" t="str">
+        <x:v>metallic paint, decorative coating, specialty paint, metallic finish</x:v>
       </x:c>
       <x:c r="J533" t="str">
         <x:v>Modern Masters</x:v>
@@ -27532,8 +27536,8 @@
       <x:c r="H534" t="str">
         <x:v>Specialty &amp; Decorative Products &gt; Modern Masters</x:v>
       </x:c>
-      <x:c r="I534" t="str">
-        <x:v>modern masters, master clear supreme satin acrylic, specialty &amp; decorative products</x:v>
+      <x:c r="I534" s="15" t="str">
+        <x:v>clear acrylic coating, satin clear coat, decorative finish topcoat, protective coating</x:v>
       </x:c>
       <x:c r="J534" t="str">
         <x:v>Modern Masters</x:v>
@@ -27585,8 +27589,8 @@
       <x:c r="H535" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I535" t="str">
-        <x:v>dynamic, ptc pro tint medium yellow, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I535" s="15" t="str">
+        <x:v>paint colourant, tinting colour, coating pigment, colour-matching additive</x:v>
       </x:c>
       <x:c r="J535" t="str">
         <x:v>Dynamic</x:v>
@@ -27632,8 +27636,8 @@
       <x:c r="H536" t="str">
         <x:v>Paints &gt; Epoxy</x:v>
       </x:c>
-      <x:c r="I536" t="str">
-        <x:v>klenk's, klenks epoxy white, paints, epoxy</x:v>
+      <x:c r="I536" s="15" t="str">
+        <x:v>tub and tile epoxy, epoxy enamel, two-part refinishing coating, bathroom fixture coating</x:v>
       </x:c>
       <x:c r="J536" t="str">
         <x:v>Klenk's</x:v>
@@ -27685,8 +27689,8 @@
       <x:c r="H537" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I537" t="str">
-        <x:v>homax, homax spray texture, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I537" s="15" t="str">
+        <x:v>spray texture, aerosol wall texture, wall repair coating, textured finish</x:v>
       </x:c>
       <x:c r="J537" t="str">
         <x:v>Homax</x:v>
@@ -27732,8 +27736,8 @@
       <x:c r="H538" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I538" t="str">
-        <x:v>homax, homax 4175 pro popcorn ceiling texture, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I538" s="15" t="str">
+        <x:v>popcorn ceiling texture, spray texture, ceiling repair coating, acoustical ceiling finish</x:v>
       </x:c>
       <x:c r="J538" t="str">
         <x:v>Homax</x:v>
@@ -27779,8 +27783,8 @@
       <x:c r="H539" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Cleaners &amp; Removers</x:v>
       </x:c>
-      <x:c r="I539" t="str">
-        <x:v>goof off, goof off ultimate remover, painting tools &amp; accessories, cleaners &amp; removers</x:v>
+      <x:c r="I539" s="15" t="str">
+        <x:v>spot remover, adhesive remover, solvent cleaner, surface cleaning product</x:v>
       </x:c>
       <x:c r="J539" t="str">
         <x:v>Goof Off</x:v>
@@ -27826,8 +27830,8 @@
       <x:c r="H540" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Cleaners &amp; Removers</x:v>
       </x:c>
-      <x:c r="I540" t="str">
-        <x:v>goof off, goof off 2 cleaner spray, painting tools &amp; accessories, cleaners &amp; removers</x:v>
+      <x:c r="I540" s="15" t="str">
+        <x:v>spot remover, adhesive remover, solvent cleaner, surface cleaning product</x:v>
       </x:c>
       <x:c r="J540" t="str">
         <x:v>Goof Off</x:v>
@@ -27873,8 +27877,8 @@
       <x:c r="H541" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Cleaners &amp; Removers</x:v>
       </x:c>
-      <x:c r="I541" t="str">
-        <x:v>goof off, painting tools &amp; accessories, cleaners &amp; removers</x:v>
+      <x:c r="I541" s="15" t="str">
+        <x:v>spot remover, adhesive remover, solvent cleaner, surface cleaning product</x:v>
       </x:c>
       <x:c r="J541" t="str">
         <x:v>Goof Off</x:v>
@@ -27920,8 +27924,8 @@
       <x:c r="H542" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Cleaners &amp; Removers</x:v>
       </x:c>
-      <x:c r="I542" t="str">
-        <x:v>dynamic, dynamic chomp degreaser spray, painting tools &amp; accessories, cleaners &amp; removers</x:v>
+      <x:c r="I542" s="15" t="str">
+        <x:v>degreaser, heavy-duty cleaner, surface preparation cleaner, concentrated cleaner</x:v>
       </x:c>
       <x:c r="J542" t="str">
         <x:v>Dynamic</x:v>
@@ -27967,8 +27971,8 @@
       <x:c r="H543" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I543" t="str">
-        <x:v>circa 1850, circa wallpaper prep-coat gal, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I543" s="15" t="str">
+        <x:v>wallcovering primer, wall preparation coating, primer sealer, interior primer</x:v>
       </x:c>
       <x:c r="J543" t="str">
         <x:v>Circa 1850</x:v>
@@ -28014,8 +28018,8 @@
       <x:c r="H544" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Cleaners &amp; Removers</x:v>
       </x:c>
-      <x:c r="I544" t="str">
-        <x:v>goo gone, goo gone cleaner, painting tools &amp; accessories, cleaners &amp; removers</x:v>
+      <x:c r="I544" s="15" t="str">
+        <x:v>adhesive remover, residue cleaner, solvent cleaner, surface cleaning product</x:v>
       </x:c>
       <x:c r="J544" t="str">
         <x:v>Goo Gone</x:v>
@@ -28061,8 +28065,8 @@
       <x:c r="H545" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I545" t="str">
-        <x:v>dynamic, super lid with spout dynamic, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I545" s="15" t="str">
+        <x:v>paint can spout, pouring accessory, paint container accessory, painting tool</x:v>
       </x:c>
       <x:c r="J545" t="str">
         <x:v>Dynamic</x:v>
@@ -28108,8 +28112,8 @@
       <x:c r="H546" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I546" t="str">
-        <x:v>dynamic, staining pad, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I546" s="15" t="str">
+        <x:v>paint pad, flat paint applicator, painting tool, coating applicator</x:v>
       </x:c>
       <x:c r="J546" t="str">
         <x:v>Dynamic</x:v>
@@ -28155,8 +28159,8 @@
       <x:c r="H547" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I547" t="str">
-        <x:v>spring tools, spring tools nail set, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I547" s="15" t="str">
+        <x:v>nail set, spring-loaded punch, hand tool, finishing tool</x:v>
       </x:c>
       <x:c r="J547" t="str">
         <x:v>Spring Tools</x:v>
@@ -28202,8 +28206,8 @@
       <x:c r="H548" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I548" t="str">
-        <x:v>siligun, siligun pro compact caulking gun, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I548" s="15" t="str">
+        <x:v>caulking gun, sealant applicator, cartridge applicator, hand tool</x:v>
       </x:c>
       <x:c r="J548" t="str">
         <x:v>SiliGun</x:v>
@@ -28249,8 +28253,8 @@
       <x:c r="H549" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I549" t="str">
-        <x:v>rhodes, rhodes steel wool #1 (12 pads), painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I549" s="15" t="str">
+        <x:v>steel wool, metal abrasive, surface preparation material, finishing pad</x:v>
       </x:c>
       <x:c r="J549" t="str">
         <x:v>Rhodes</x:v>
@@ -28296,8 +28300,8 @@
       <x:c r="H550" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I550" t="str">
-        <x:v>dynamic, qt. dyna patch pro, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I550" s="15" t="str">
+        <x:v>spackling compound, wall repair filler, patching compound, surface repair product</x:v>
       </x:c>
       <x:c r="J550" t="str">
         <x:v>Dynamic</x:v>
@@ -28343,8 +28347,8 @@
       <x:c r="H551" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I551" t="str">
-        <x:v>preval, preval sprayer, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I551" s="15" t="str">
+        <x:v>portable spray system, aerosol spray unit, paint sprayer, coating application equipment</x:v>
       </x:c>
       <x:c r="J551" t="str">
         <x:v>Preval</x:v>
@@ -28390,8 +28394,8 @@
       <x:c r="H552" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I552" t="str">
-        <x:v>preval, preval power unit, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I552" s="15" t="str">
+        <x:v>sprayer power unit, aerosol propellant unit, paint sprayer accessory, replacement spray unit</x:v>
       </x:c>
       <x:c r="J552" t="str">
         <x:v>Preval</x:v>
@@ -28437,8 +28441,8 @@
       <x:c r="H553" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I553" t="str">
-        <x:v>picasso, picasso oval angled brush, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I553" s="15" t="str">
+        <x:v>angled paint brush, sash brush, paint applicator, painting tool</x:v>
       </x:c>
       <x:c r="J553" t="str">
         <x:v>Picasso</x:v>
@@ -28484,8 +28488,8 @@
       <x:c r="H554" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Cleaners &amp; Removers</x:v>
       </x:c>
-      <x:c r="I554" t="str">
-        <x:v>glue buster, glue buster adhesive remover gal, painting tools &amp; accessories, cleaners &amp; removers</x:v>
+      <x:c r="I554" s="15" t="str">
+        <x:v>adhesive remover, residue cleaner, solvent cleaner, surface cleaning product</x:v>
       </x:c>
       <x:c r="J554" t="str">
         <x:v>Glue Buster</x:v>
@@ -28531,8 +28535,8 @@
       <x:c r="H555" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I555" t="str">
-        <x:v>dynamic, dynamic brush&amp;roller spinner cleaner, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I555" s="15" t="str">
+        <x:v>brush and roller cleaner, paint applicator cleaning tool, roller spinner, painting tool</x:v>
       </x:c>
       <x:c r="J555" t="str">
         <x:v>Dynamic</x:v>
@@ -28578,8 +28582,8 @@
       <x:c r="H556" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Cleaners &amp; Removers</x:v>
       </x:c>
-      <x:c r="I556" t="str">
-        <x:v>crocodile cloth, crocodile cloth original, painting tools &amp; accessories, cleaners &amp; removers</x:v>
+      <x:c r="I556" s="15" t="str">
+        <x:v>cleaning wipes, multi-purpose wipes, surface cleaning product, pre-moistened wipes</x:v>
       </x:c>
       <x:c r="J556" t="str">
         <x:v>Crocodile Cloth</x:v>
@@ -28625,8 +28629,8 @@
       <x:c r="H557" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I557" t="str">
-        <x:v>dynamic, measuring bucket, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I557" s="15" t="str">
+        <x:v>paint pail, paint container, mixing container, painting accessory</x:v>
       </x:c>
       <x:c r="J557" t="str">
         <x:v>Dynamic</x:v>
@@ -28672,8 +28676,8 @@
       <x:c r="H558" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Cleaners &amp; Removers</x:v>
       </x:c>
-      <x:c r="I558" t="str">
-        <x:v>dynamic, 1000+ stain remover, painting tools &amp; accessories, cleaners &amp; removers</x:v>
+      <x:c r="I558" s="15" t="str">
+        <x:v>stain remover, spot cleaner, surface cleaning product, specialty cleaner</x:v>
       </x:c>
       <x:c r="J558" t="str">
         <x:v>Dynamic</x:v>
@@ -28719,8 +28723,8 @@
       <x:c r="H559" t="str">
         <x:v>Paints &gt; Stains &amp; Varnishes</x:v>
       </x:c>
-      <x:c r="I559" t="str">
-        <x:v>recochem, recochem boiled linseed oil dynamic, paints, stains &amp; varnishes</x:v>
+      <x:c r="I559" s="15" t="str">
+        <x:v>boiled linseed oil, drying oil, wood finish, oil-based finish</x:v>
       </x:c>
       <x:c r="J559" t="str">
         <x:v>Recochem</x:v>
@@ -28772,8 +28776,8 @@
       <x:c r="H560" t="str">
         <x:v>Paints &gt; Stains &amp; Varnishes</x:v>
       </x:c>
-      <x:c r="I560" t="str">
-        <x:v>penofin, penofin ultra premium red label - sable, paints, stains &amp; varnishes</x:v>
+      <x:c r="I560" s="15" t="str">
+        <x:v>exterior wood stain, penetrating wood finish, wood stain, exterior wood finish</x:v>
       </x:c>
       <x:c r="J560" t="str">
         <x:v>Penofin</x:v>
@@ -28825,8 +28829,8 @@
       <x:c r="H561" t="str">
         <x:v>Paints &gt; Stains &amp; Varnishes</x:v>
       </x:c>
-      <x:c r="I561" t="str">
-        <x:v>penofin, penofin tsf teak satin finish, paints, stains &amp; varnishes</x:v>
+      <x:c r="I561" s="15" t="str">
+        <x:v>teak wood finish, satin wood finish, penetrating oil finish, exterior wood finish</x:v>
       </x:c>
       <x:c r="J561" t="str">
         <x:v>Penofin</x:v>
@@ -28878,8 +28882,8 @@
       <x:c r="H562" t="str">
         <x:v>Paints &gt; Stains &amp; Varnishes</x:v>
       </x:c>
-      <x:c r="I562" t="str">
-        <x:v>penofin, penofin exterior exotic hardwood finish, paints, stains &amp; varnishes</x:v>
+      <x:c r="I562" s="15" t="str">
+        <x:v>exterior wood finish, hardwood finish, penetrating wood finish, wood oil finish</x:v>
       </x:c>
       <x:c r="J562" t="str">
         <x:v>Penofin</x:v>
@@ -28939,8 +28943,8 @@
       <x:c r="H563" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I563" t="str">
-        <x:v>siligun, siligun compact caulking gun, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I563" s="15" t="str">
+        <x:v>caulking gun, sealant applicator, cartridge applicator, hand tool</x:v>
       </x:c>
       <x:c r="J563" t="str">
         <x:v>SiliGun</x:v>
@@ -28986,8 +28990,8 @@
       <x:c r="H564" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I564" t="str">
-        <x:v>dynamic, monkey rung spin pro mini roller cleaner, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I564" s="15" t="str">
+        <x:v>brush and roller cleaner, paint applicator cleaning tool, roller spinner, painting tool</x:v>
       </x:c>
       <x:c r="J564" t="str">
         <x:v>Dynamic</x:v>
@@ -29033,8 +29037,8 @@
       <x:c r="H565" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I565" t="str">
-        <x:v>norton, norton sanding pads 150 grit, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I565" s="15" t="str">
+        <x:v>sandpaper, coated abrasive, surface preparation abrasive, sanding material</x:v>
       </x:c>
       <x:c r="J565" t="str">
         <x:v>Norton</x:v>
@@ -29080,8 +29084,8 @@
       <x:c r="H566" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I566" t="str">
-        <x:v>norton, norton 3x sandpaper 180, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I566" s="15" t="str">
+        <x:v>sandpaper, coated abrasive, surface preparation abrasive, sanding material</x:v>
       </x:c>
       <x:c r="J566" t="str">
         <x:v>Norton</x:v>
@@ -29127,8 +29131,8 @@
       <x:c r="H567" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I567" t="str">
-        <x:v>norton, norton 3x sandpaper 100, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I567" s="15" t="str">
+        <x:v>sandpaper, coated abrasive, surface preparation abrasive, sanding material</x:v>
       </x:c>
       <x:c r="J567" t="str">
         <x:v>Norton</x:v>
@@ -29182,8 +29186,8 @@
       <x:c r="H568" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I568" t="str">
-        <x:v>norton, 12x18 buffing pads thick red, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I568" s="15" t="str">
+        <x:v>buffing pad, floor polishing pad, abrasive pad, surface finishing accessory</x:v>
       </x:c>
       <x:c r="J568" t="str">
         <x:v>Norton</x:v>
@@ -29229,8 +29233,8 @@
       <x:c r="H569" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I569" t="str">
-        <x:v>norton, 12x18 60 grit adhesive back sandpaper, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I569" s="15" t="str">
+        <x:v>sandpaper, coated abrasive, surface preparation abrasive, sanding material</x:v>
       </x:c>
       <x:c r="J569" t="str">
         <x:v>Norton</x:v>
@@ -29276,8 +29280,8 @@
       <x:c r="H570" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I570" t="str">
-        <x:v>nour, nour lime wash brush 100 mm, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I570" s="15" t="str">
+        <x:v>limewash brush, masonry brush, paint applicator, painting tool</x:v>
       </x:c>
       <x:c r="J570" t="str">
         <x:v>Nour</x:v>
@@ -29323,8 +29327,8 @@
       <x:c r="H571" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I571" t="str">
-        <x:v>nour, nour polylamb roller refill 1/2", painting tools &amp; accessories, tools</x:v>
+      <x:c r="I571" s="15" t="str">
+        <x:v>paint roller cover, paint roller refill, paint applicator, painting tool, lambswool roller cover</x:v>
       </x:c>
       <x:c r="J571" t="str">
         <x:v>Nour</x:v>
@@ -29370,8 +29374,8 @@
       <x:c r="H572" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I572" t="str">
-        <x:v>allpro, allpro silver series 2 1/2" polyester brush, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I572" s="15" t="str">
+        <x:v>paint brush, paint applicator, painting tool, bristle brush</x:v>
       </x:c>
       <x:c r="J572" t="str">
         <x:v>AllPro</x:v>
@@ -29417,8 +29421,8 @@
       <x:c r="H573" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I573" t="str">
-        <x:v>allpro, allpro microfiber roller refill 9" x 5/8", painting tools &amp; accessories, tools</x:v>
+      <x:c r="I573" s="15" t="str">
+        <x:v>paint roller cover, paint roller refill, paint applicator, painting tool, microfiber roller cover</x:v>
       </x:c>
       <x:c r="J573" t="str">
         <x:v>AllPro</x:v>
@@ -29464,8 +29468,8 @@
       <x:c r="H574" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I574" t="str">
-        <x:v>olfa, olfa stainless steel auto-lock utility k, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I574" s="15" t="str">
+        <x:v>utility knife, cutting tool, hand tool, snap-off knife</x:v>
       </x:c>
       <x:c r="J574" t="str">
         <x:v>OLFA</x:v>
@@ -29511,8 +29515,8 @@
       <x:c r="H575" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I575" t="str">
-        <x:v>olfa, olfa small snap-off black blade, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I575" s="15" t="str">
+        <x:v>replacement blade, scraper blade, cutting accessory, hand tool accessory</x:v>
       </x:c>
       <x:c r="J575" t="str">
         <x:v>OLFA</x:v>
@@ -29566,8 +29570,8 @@
       <x:c r="H576" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I576" t="str">
-        <x:v>olfa, olfa rubber inset utility knife, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I576" s="15" t="str">
+        <x:v>utility knife, cutting tool, hand tool, snap-off knife</x:v>
       </x:c>
       <x:c r="J576" t="str">
         <x:v>OLFA</x:v>
@@ -29613,8 +29617,8 @@
       <x:c r="H577" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I577" t="str">
-        <x:v>olfa, olfa rubber grip utility knife, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I577" s="15" t="str">
+        <x:v>utility knife, cutting tool, hand tool, snap-off knife</x:v>
       </x:c>
       <x:c r="J577" t="str">
         <x:v>OLFA</x:v>
@@ -29660,8 +29664,8 @@
       <x:c r="H578" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I578" t="str">
-        <x:v>olfa, olfa large snap-off black blade, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I578" s="15" t="str">
+        <x:v>replacement blade, scraper blade, cutting accessory, hand tool accessory</x:v>
       </x:c>
       <x:c r="J578" t="str">
         <x:v>OLFA</x:v>
@@ -29715,8 +29719,8 @@
       <x:c r="H579" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I579" t="str">
-        <x:v>olfa, olfa multi-blade auto-load utility knife, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I579" s="15" t="str">
+        <x:v>utility knife, cutting tool, hand tool, snap-off knife</x:v>
       </x:c>
       <x:c r="J579" t="str">
         <x:v>OLFA</x:v>
@@ -29762,8 +29766,8 @@
       <x:c r="H580" t="str">
         <x:v>Paints &gt; Stains &amp; Varnishes</x:v>
       </x:c>
-      <x:c r="I580" t="str">
-        <x:v>olympic, olympic rescue it! wood &amp; concrete resur, paints, stains &amp; varnishes</x:v>
+      <x:c r="I580" s="15" t="str">
+        <x:v>deck resurfacer, concrete resurfacer, thick-texture coating, exterior repair coating</x:v>
       </x:c>
       <x:c r="J580" t="str">
         <x:v>Olympic</x:v>
@@ -29815,8 +29819,8 @@
       <x:c r="H581" t="str">
         <x:v>Paints &gt; Stains &amp; Varnishes</x:v>
       </x:c>
-      <x:c r="I581" t="str">
-        <x:v>olympic, olympic maximum semi trans hybrid stain neu, paints, stains &amp; varnishes</x:v>
+      <x:c r="I581" s="15" t="str">
+        <x:v>exterior wood stain, penetrating wood finish, wood stain, exterior wood finish</x:v>
       </x:c>
       <x:c r="J581" t="str">
         <x:v>Olympic</x:v>
@@ -29868,8 +29872,8 @@
       <x:c r="H582" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I582" t="str">
-        <x:v>omc, omc painter's plastic, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I582" s="15" t="str">
+        <x:v>drop cloth, surface protection, painting cover, painting accessory</x:v>
       </x:c>
       <x:c r="J582" t="str">
         <x:v>OMC</x:v>
@@ -29915,8 +29919,8 @@
       <x:c r="H583" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I583" t="str">
-        <x:v>omc, omc fiberglass drywall tape, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I583" s="15" t="str">
+        <x:v>drywall tape, joint reinforcement tape, drywall repair material, fiberglass mesh tape</x:v>
       </x:c>
       <x:c r="J583" t="str">
         <x:v>OMC</x:v>
@@ -29962,8 +29966,8 @@
       <x:c r="H584" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I584" t="str">
-        <x:v>omc, omc drywall paper tape, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I584" s="15" t="str">
+        <x:v>drywall paper tape, joint reinforcement tape, drywall repair material, paper joint tape</x:v>
       </x:c>
       <x:c r="J584" t="str">
         <x:v>OMC</x:v>
@@ -30009,8 +30013,8 @@
       <x:c r="H585" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I585" t="str">
-        <x:v>omc, omc drywall corner tape, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I585" s="15" t="str">
+        <x:v>drywall corner tape, corner reinforcement tape, drywall repair material, joint finishing tape</x:v>
       </x:c>
       <x:c r="J585" t="str">
         <x:v>OMC</x:v>
@@ -30056,8 +30060,8 @@
       <x:c r="H586" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I586" t="str">
-        <x:v>omc, omc pre-taped plastic drop cloth, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I586" s="15" t="str">
+        <x:v>drop cloth, surface protection, painting cover, painting accessory</x:v>
       </x:c>
       <x:c r="J586" t="str">
         <x:v>OMC</x:v>
@@ -30111,8 +30115,8 @@
       <x:c r="H587" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I587" t="str">
-        <x:v>pintar, pintar trim roller 3" x 5 mm, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I587" s="15" t="str">
+        <x:v>paint roller cover, paint roller refill, paint applicator, painting tool</x:v>
       </x:c>
       <x:c r="J587" t="str">
         <x:v>Pintar</x:v>
@@ -30158,8 +30162,8 @@
       <x:c r="H588" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I588" t="str">
-        <x:v>pintar, slit foam refill, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I588" s="15" t="str">
+        <x:v>foam roller cover, paint roller refill, slit foam applicator, painting tool</x:v>
       </x:c>
       <x:c r="J588" t="str">
         <x:v>Pintar</x:v>
@@ -30205,8 +30209,8 @@
       <x:c r="H589" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I589" t="str">
-        <x:v>pintar, pre-caulking filler rope, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I589" s="15" t="str">
+        <x:v>caulk backing rod, foam filler rope, joint filler, sealant accessory</x:v>
       </x:c>
       <x:c r="J589" t="str">
         <x:v>Pintar</x:v>
@@ -30252,8 +30256,8 @@
       <x:c r="H590" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I590" t="str">
-        <x:v>pintar, pintar pipe roller, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I590" s="15" t="str">
+        <x:v>pipe paint roller, specialty paint roller, paint applicator, painting tool</x:v>
       </x:c>
       <x:c r="J590" t="str">
         <x:v>Pintar</x:v>
@@ -30299,8 +30303,8 @@
       <x:c r="H591" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I591" t="str">
-        <x:v>pintar, pintar lint-free roller refill, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I591" s="15" t="str">
+        <x:v>paint roller cover, paint roller refill, paint applicator, painting tool</x:v>
       </x:c>
       <x:c r="J591" t="str">
         <x:v>Pintar</x:v>
@@ -30354,8 +30358,8 @@
       <x:c r="H592" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I592" t="str">
-        <x:v>pintar, pintar lambskin block applicator, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I592" s="15" t="str">
+        <x:v>lambskin block applicator, floor finish applicator, wood finish applicator, painting tool</x:v>
       </x:c>
       <x:c r="J592" t="str">
         <x:v>Pintar</x:v>
@@ -30401,8 +30405,8 @@
       <x:c r="H593" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I593" t="str">
-        <x:v>pintar, pintar 10" synthetic water wiz pad with block, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I593" s="15" t="str">
+        <x:v>paint pad, flat paint applicator, painting tool, coating applicator</x:v>
       </x:c>
       <x:c r="J593" t="str">
         <x:v>Pintar</x:v>
@@ -30448,8 +30452,8 @@
       <x:c r="H594" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I594" t="str">
-        <x:v>pintar, pintar microfiber pad w/block, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I594" s="15" t="str">
+        <x:v>paint pad, flat paint applicator, painting tool, coating applicator</x:v>
       </x:c>
       <x:c r="J594" t="str">
         <x:v>Pintar</x:v>
@@ -30495,8 +30499,8 @@
       <x:c r="H595" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I595" t="str">
-        <x:v>olympian, olympian stain brush, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I595" s="15" t="str">
+        <x:v>stain brush, wood finish applicator, paint brush, painting tool</x:v>
       </x:c>
       <x:c r="J595" t="str">
         <x:v>Olympian</x:v>
@@ -30542,8 +30546,8 @@
       <x:c r="H596" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I596" t="str">
-        <x:v>lexel, lexel sealant clear squeeze tube, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I596" s="15" t="str">
+        <x:v>sealant, caulk, joint sealant, gap-filling compound</x:v>
       </x:c>
       <x:c r="J596" t="str">
         <x:v>Lexel</x:v>
@@ -30589,8 +30593,8 @@
       <x:c r="H597" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I597" t="str">
-        <x:v>lexel, lexel sealant clear, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I597" s="15" t="str">
+        <x:v>sealant, caulk, joint sealant, gap-filling compound</x:v>
       </x:c>
       <x:c r="J597" t="str">
         <x:v>Lexel</x:v>
@@ -30636,8 +30640,8 @@
       <x:c r="H598" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I598" t="str">
-        <x:v>pintar, pintar heavy-duty 18" roller frame, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I598" s="15" t="str">
+        <x:v>paint roller frame, roller handle, paint applicator, painting tool</x:v>
       </x:c>
       <x:c r="J598" t="str">
         <x:v>Pintar</x:v>
@@ -30683,8 +30687,8 @@
       <x:c r="H599" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I599" t="str">
-        <x:v>pintar, gallon metal tray, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I599" s="15" t="str">
+        <x:v>paint tray, paint container, painting accessory, paint roller tray</x:v>
       </x:c>
       <x:c r="J599" t="str">
         <x:v>Pintar</x:v>
@@ -30730,8 +30734,8 @@
       <x:c r="H600" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I600" t="str">
-        <x:v>canpro, canpro premium microfibre refill, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I600" s="15" t="str">
+        <x:v>paint roller cover, paint roller refill, paint applicator, painting tool, microfiber roller cover</x:v>
       </x:c>
       <x:c r="J600" t="str">
         <x:v>CanPro</x:v>
@@ -30777,8 +30781,8 @@
       <x:c r="H601" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I601" t="str">
-        <x:v>allway, allway scraper set w/6 blades, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I601" s="15" t="str">
+        <x:v>scraper, surface preparation tool, hand tool, painting tool</x:v>
       </x:c>
       <x:c r="J601" t="str">
         <x:v>Allway</x:v>
@@ -30824,8 +30828,8 @@
       <x:c r="H602" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I602" t="str">
-        <x:v>allway, allway pour spout, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I602" s="15" t="str">
+        <x:v>paint can spout, pouring accessory, paint container accessory, painting tool</x:v>
       </x:c>
       <x:c r="J602" t="str">
         <x:v>Allway</x:v>
@@ -30871,8 +30875,8 @@
       <x:c r="H603" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I603" t="str">
-        <x:v>allpro, allpro washi tape 1 1/2", painting tools &amp; accessories, tools</x:v>
+      <x:c r="I603" s="15" t="str">
+        <x:v>masking tape, painter's tape, pressure-sensitive tape, painting accessory</x:v>
       </x:c>
       <x:c r="J603" t="str">
         <x:v>AllPro</x:v>
@@ -30918,8 +30922,8 @@
       <x:c r="H604" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I604" t="str">
-        <x:v>allpro, allpro microfiber roller refill 15 mm, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I604" s="15" t="str">
+        <x:v>paint roller cover, paint roller refill, paint applicator, painting tool, microfiber roller cover</x:v>
       </x:c>
       <x:c r="J604" t="str">
         <x:v>AllPro</x:v>
@@ -30965,8 +30969,8 @@
       <x:c r="H605" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I605" t="str">
-        <x:v>pintar, pintar foam roller refill 9 1/2", painting tools &amp; accessories, tools</x:v>
+      <x:c r="I605" s="15" t="str">
+        <x:v>paint roller cover, paint roller refill, paint applicator, painting tool, foam roller cover</x:v>
       </x:c>
       <x:c r="J605" t="str">
         <x:v>Pintar</x:v>
@@ -31012,8 +31016,8 @@
       <x:c r="H606" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I606" t="str">
-        <x:v>pintar, pintar mini cage roller frame, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I606" s="15" t="str">
+        <x:v>paint roller frame, roller handle, paint applicator, painting tool</x:v>
       </x:c>
       <x:c r="J606" t="str">
         <x:v>Pintar</x:v>
@@ -31067,8 +31071,8 @@
       <x:c r="H607" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I607" t="str">
-        <x:v>pintar, pintar high-pile roller refill, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I607" s="15" t="str">
+        <x:v>paint roller cover, paint roller refill, paint applicator, painting tool</x:v>
       </x:c>
       <x:c r="J607" t="str">
         <x:v>Pintar</x:v>
@@ -31122,8 +31126,8 @@
       <x:c r="H608" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I608" t="str">
-        <x:v>pintar, pintar stain &amp; paint brush 4", painting tools &amp; accessories, tools</x:v>
+      <x:c r="I608" s="15" t="str">
+        <x:v>paint brush, paint applicator, painting tool, bristle brush</x:v>
       </x:c>
       <x:c r="J608" t="str">
         <x:v>Pintar</x:v>
@@ -31169,8 +31173,8 @@
       <x:c r="H609" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I609" t="str">
-        <x:v>pintar, pintar stain brush 3", painting tools &amp; accessories, tools</x:v>
+      <x:c r="I609" s="15" t="str">
+        <x:v>stain brush, wood finish applicator, paint brush, painting tool</x:v>
       </x:c>
       <x:c r="J609" t="str">
         <x:v>Pintar</x:v>
@@ -31216,8 +31220,8 @@
       <x:c r="H610" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I610" t="str">
-        <x:v>pintar, metal tray, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I610" s="15" t="str">
+        <x:v>paint tray, paint container, painting accessory, paint roller tray</x:v>
       </x:c>
       <x:c r="J610" t="str">
         <x:v>Pintar</x:v>
@@ -31263,8 +31267,8 @@
       <x:c r="H611" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I611" t="str">
-        <x:v>pintar, jumbo refill, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I611" s="15" t="str">
+        <x:v>paint roller cover, paint roller refill, paint applicator, painting tool</x:v>
       </x:c>
       <x:c r="J611" t="str">
         <x:v>Pintar</x:v>
@@ -31310,8 +31314,8 @@
       <x:c r="H612" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I612" t="str">
-        <x:v>polytarp, polytarp lightweight plastic sheeting 20' x 100' (2,000 sq ft), painting tools &amp; accessories, tools</x:v>
+      <x:c r="I612" s="15" t="str">
+        <x:v>drop cloth, surface protection, painting cover, painting accessory</x:v>
       </x:c>
       <x:c r="J612" t="str">
         <x:v>Polytarp</x:v>
@@ -31357,8 +31361,8 @@
       <x:c r="H613" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I613" t="str">
-        <x:v>polytarp, 1500 sq.ft plastic economy, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I613" s="15" t="str">
+        <x:v>drop cloth, surface protection, painting cover, painting accessory</x:v>
       </x:c>
       <x:c r="J613" t="str">
         <x:v>Polytarp</x:v>
@@ -31404,8 +31408,8 @@
       <x:c r="H614" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I614" t="str">
-        <x:v>polytarp, light weight plastic 500 sq ft, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I614" s="15" t="str">
+        <x:v>drop cloth, surface protection, painting cover, painting accessory</x:v>
       </x:c>
       <x:c r="J614" t="str">
         <x:v>Polytarp</x:v>
@@ -31451,8 +31455,8 @@
       <x:c r="H615" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I615" t="str">
-        <x:v>prodec, prodec titan roller frame, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I615" s="15" t="str">
+        <x:v>paint roller frame, roller handle, paint applicator, painting tool</x:v>
       </x:c>
       <x:c r="J615" t="str">
         <x:v>ProDec</x:v>
@@ -31498,8 +31502,8 @@
       <x:c r="H616" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I616" t="str">
-        <x:v>prodec, prodec mini roller frame, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I616" s="15" t="str">
+        <x:v>paint roller frame, roller handle, paint applicator, painting tool</x:v>
       </x:c>
       <x:c r="J616" t="str">
         <x:v>ProDec</x:v>
@@ -31545,8 +31549,8 @@
       <x:c r="H617" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I617" t="str">
-        <x:v>prodec, prodec ice fusion 2 1/2" cutting-in brush, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I617" s="15" t="str">
+        <x:v>angled paint brush, sash brush, paint applicator, painting tool</x:v>
       </x:c>
       <x:c r="J617" t="str">
         <x:v>ProDec</x:v>
@@ -31592,8 +31596,8 @@
       <x:c r="H618" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I618" t="str">
-        <x:v>prodec, prodec ice fusion 2 1/2" angle oval brush, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I618" s="15" t="str">
+        <x:v>oval paint brush, paint applicator, paint brush, painting tool</x:v>
       </x:c>
       <x:c r="J618" t="str">
         <x:v>ProDec</x:v>
@@ -31639,8 +31643,8 @@
       <x:c r="H619" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I619" t="str">
-        <x:v>prodec, prodec ice fusion roller cover, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I619" s="15" t="str">
+        <x:v>paint roller cover, paint roller refill, paint applicator, painting tool</x:v>
       </x:c>
       <x:c r="J619" t="str">
         <x:v>ProDec</x:v>
@@ -31686,8 +31690,8 @@
       <x:c r="H620" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I620" t="str">
-        <x:v>prodec, prodec sabre pole, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I620" s="15" t="str">
+        <x:v>paint roller extension pole, telescoping pole, paint applicator accessory, painting tool</x:v>
       </x:c>
       <x:c r="J620" t="str">
         <x:v>ProDec</x:v>
@@ -31733,8 +31737,8 @@
       <x:c r="H621" t="str">
         <x:v>Specialty &amp; Decorative Products &gt; Textureline</x:v>
       </x:c>
-      <x:c r="I621" t="str">
-        <x:v>protek, waterbased varnish zero gloss texturelin, specialty &amp; decorative products, textureline</x:v>
+      <x:c r="I621" s="15" t="str">
+        <x:v>water-based varnish, matte clear coat, decorative plaster topcoat, protective wall finish</x:v>
       </x:c>
       <x:c r="J621" t="str">
         <x:v>ProTek</x:v>
@@ -31786,8 +31790,8 @@
       <x:c r="H622" t="str">
         <x:v>Specialty &amp; Decorative Products &gt; Textureline</x:v>
       </x:c>
-      <x:c r="I622" t="str">
-        <x:v>textureline, textureline flat wax, specialty &amp; decorative products</x:v>
+      <x:c r="I622" s="15" t="str">
+        <x:v>decorative plaster wax, protective wax finish, wall finish sealer, decorative finishing product</x:v>
       </x:c>
       <x:c r="J622" t="str">
         <x:v>Textureline</x:v>
@@ -31839,8 +31843,8 @@
       <x:c r="H623" t="str">
         <x:v>Specialty &amp; Decorative Products &gt; Textureline</x:v>
       </x:c>
-      <x:c r="I623" t="str">
-        <x:v>textureline, textureline venetian pastel basecoat, specialty &amp; decorative products</x:v>
+      <x:c r="I623" s="15" t="str">
+        <x:v>decorative basecoat, plaster basecoat, tinted basecoat, interior wall coating</x:v>
       </x:c>
       <x:c r="J623" t="str">
         <x:v>Textureline</x:v>
@@ -31892,8 +31896,8 @@
       <x:c r="H624" t="str">
         <x:v>Specialty &amp; Decorative Products &gt; Textureline</x:v>
       </x:c>
-      <x:c r="I624" t="str">
-        <x:v>textureline, textureline metaltech silver base, specialty &amp; decorative products</x:v>
+      <x:c r="I624" s="15" t="str">
+        <x:v>metallic plaster base, decorative wall coating, metallic effect finish, interior wall finish</x:v>
       </x:c>
       <x:c r="J624" t="str">
         <x:v>Textureline</x:v>
@@ -31945,8 +31949,8 @@
       <x:c r="H625" t="str">
         <x:v>Specialty &amp; Decorative Products &gt; Textureline</x:v>
       </x:c>
-      <x:c r="I625" t="str">
-        <x:v>textureline, textureline metaltech pearl base, specialty &amp; decorative products</x:v>
+      <x:c r="I625" s="15" t="str">
+        <x:v>metallic plaster base, decorative wall coating, metallic effect finish, interior wall finish</x:v>
       </x:c>
       <x:c r="J625" t="str">
         <x:v>Textureline</x:v>
@@ -31998,8 +32002,8 @@
       <x:c r="H626" t="str">
         <x:v>Specialty &amp; Decorative Products &gt; Textureline</x:v>
       </x:c>
-      <x:c r="I626" t="str">
-        <x:v>textureline, textureline metaltech gold base, specialty &amp; decorative products</x:v>
+      <x:c r="I626" s="15" t="str">
+        <x:v>metallic plaster base, decorative wall coating, metallic effect finish, interior wall finish</x:v>
       </x:c>
       <x:c r="J626" t="str">
         <x:v>Textureline</x:v>
@@ -32051,8 +32055,8 @@
       <x:c r="H627" t="str">
         <x:v>Specialty &amp; Decorative Products &gt; Textureline</x:v>
       </x:c>
-      <x:c r="I627" t="str">
-        <x:v>textureline, textureline marmorino classic, specialty &amp; decorative products</x:v>
+      <x:c r="I627" s="15" t="str">
+        <x:v>venetian plaster, lime plaster, decorative plaster, interior wall finish, textured wall finish, interior wall coating, specialty finish</x:v>
       </x:c>
       <x:c r="J627" t="str">
         <x:v>Textureline</x:v>
@@ -32104,8 +32108,8 @@
       <x:c r="H628" t="str">
         <x:v>Specialty &amp; Decorative Products &gt; Textureline</x:v>
       </x:c>
-      <x:c r="I628" t="str">
-        <x:v>textureline, textureline carolina sandstone, specialty &amp; decorative products</x:v>
+      <x:c r="I628" s="15" t="str">
+        <x:v>textured wall coating, sandstone finish, decorative plaster, interior wall finish</x:v>
       </x:c>
       <x:c r="J628" t="str">
         <x:v>Textureline</x:v>
@@ -32157,8 +32161,8 @@
       <x:c r="H629" t="str">
         <x:v>Specialty &amp; Decorative Products &gt; Textureline</x:v>
       </x:c>
-      <x:c r="I629" t="str">
-        <x:v>textureline, textureline burnishing wax gallon, specialty &amp; decorative products</x:v>
+      <x:c r="I629" s="15" t="str">
+        <x:v>decorative plaster wax, protective wax finish, wall finish sealer, decorative finishing product</x:v>
       </x:c>
       <x:c r="J629" t="str">
         <x:v>Textureline</x:v>
@@ -32207,8 +32211,8 @@
       <x:c r="H630" t="str">
         <x:v>Specialty &amp; Decorative Products &gt; Textureline</x:v>
       </x:c>
-      <x:c r="I630" t="str">
-        <x:v>protek, texturebase coat pastel base, specialty &amp; decorative products, textureline</x:v>
+      <x:c r="I630" s="15" t="str">
+        <x:v>decorative basecoat, plaster basecoat, tinted basecoat, interior wall coating</x:v>
       </x:c>
       <x:c r="J630" t="str">
         <x:v>ProTek</x:v>
@@ -32260,8 +32264,8 @@
       <x:c r="H631" t="str">
         <x:v>Paints &gt; Specialty Paints</x:v>
       </x:c>
-      <x:c r="I631" t="str">
-        <x:v>protek, sheffield red hot aluminum gal, paints, specialty paints</x:v>
+      <x:c r="I631" s="15" t="str">
+        <x:v>heat-resistant paint, aluminum paint, metallic coating, high-temperature coating</x:v>
       </x:c>
       <x:c r="J631" t="str">
         <x:v>ProTek</x:v>
@@ -32307,8 +32311,8 @@
       <x:c r="H632" t="str">
         <x:v>Specialty &amp; Decorative Products &gt; Textureline</x:v>
       </x:c>
-      <x:c r="I632" t="str">
-        <x:v>protek, marmorino classic venetian plaster, specialty &amp; decorative products, textureline</x:v>
+      <x:c r="I632" s="15" t="str">
+        <x:v>venetian plaster, lime plaster, decorative plaster, interior wall finish, textured wall finish, interior wall coating, specialty finish</x:v>
       </x:c>
       <x:c r="J632" t="str">
         <x:v>ProTek</x:v>
@@ -32360,8 +32364,8 @@
       <x:c r="H633" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I633" t="str">
-        <x:v>protek, stucco veneziano scraper, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I633" s="15" t="str">
+        <x:v>decorative finish scraper, venetian plaster tool, surface texture tool, finishing hand tool</x:v>
       </x:c>
       <x:c r="J633" t="str">
         <x:v>ProTek</x:v>
@@ -32407,8 +32411,8 @@
       <x:c r="H634" t="str">
         <x:v>Specialty &amp; Decorative Products &gt; Textureline</x:v>
       </x:c>
-      <x:c r="I634" t="str">
-        <x:v>protek, come bianko classic trowel 240x80, specialty &amp; decorative products, textureline</x:v>
+      <x:c r="I634" s="15" t="str">
+        <x:v>venetian plaster trowel, finishing trowel, plastering tool, decorative finishing tool</x:v>
       </x:c>
       <x:c r="J634" t="str">
         <x:v>ProTek</x:v>
@@ -32454,8 +32458,8 @@
       <x:c r="H635" t="str">
         <x:v>Specialty &amp; Decorative Products &gt; Textureline</x:v>
       </x:c>
-      <x:c r="I635" t="str">
-        <x:v>protek, come 310lu trowel 240x100, specialty &amp; decorative products, textureline</x:v>
+      <x:c r="I635" s="15" t="str">
+        <x:v>venetian plaster trowel, finishing trowel, plastering tool, decorative finishing tool</x:v>
       </x:c>
       <x:c r="J635" t="str">
         <x:v>ProTek</x:v>
@@ -32501,8 +32505,8 @@
       <x:c r="H636" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I636" t="str">
-        <x:v>pc products, stucco antico applicators, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I636" s="15" t="str">
+        <x:v>decorative plaster applicator, plastering tool, finishing applicator, decorative finishing tool</x:v>
       </x:c>
       <x:c r="J636" t="str">
         <x:v>PC Products</x:v>
@@ -32548,8 +32552,8 @@
       <x:c r="H637" t="str">
         <x:v>Specialty &amp; Decorative Products &gt; Textureline</x:v>
       </x:c>
-      <x:c r="I637" t="str">
-        <x:v>protek, 310li come wood handle 240x100 mm, specialty &amp; decorative products, textureline</x:v>
+      <x:c r="I637" s="15" t="str">
+        <x:v>venetian plaster trowel, finishing trowel, plastering tool, decorative finishing tool</x:v>
       </x:c>
       <x:c r="J637" t="str">
         <x:v>ProTek</x:v>
@@ -32595,8 +32599,8 @@
       <x:c r="H638" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I638" t="str">
-        <x:v>red devil, create a color standard caulk mixer, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I638" s="15" t="str">
+        <x:v>caulk mixer, colour mixing tool, sealant accessory, painting tool</x:v>
       </x:c>
       <x:c r="J638" t="str">
         <x:v>Red Devil</x:v>
@@ -32642,8 +32646,8 @@
       <x:c r="H639" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I639" t="str">
-        <x:v>red devil, create a color pro caulk mixer, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I639" s="15" t="str">
+        <x:v>caulk mixer, colour mixing tool, sealant accessory, painting tool</x:v>
       </x:c>
       <x:c r="J639" t="str">
         <x:v>Red Devil</x:v>
@@ -32689,8 +32693,8 @@
       <x:c r="H640" t="str">
         <x:v>Specialty &amp; Decorative Products &gt; Wallpaper Adhesives</x:v>
       </x:c>
-      <x:c r="I640" t="str">
-        <x:v>roman, roman ultra premium clear glue gallon, specialty &amp; decorative products, wallpaper adhesives</x:v>
+      <x:c r="I640" s="15" t="str">
+        <x:v>wallpaper adhesive, wallcovering paste, installation adhesive, interior adhesive</x:v>
       </x:c>
       <x:c r="J640" t="str">
         <x:v>Roman</x:v>
@@ -32736,8 +32740,8 @@
       <x:c r="H641" t="str">
         <x:v>Specialty &amp; Decorative Products &gt; Wallpaper Adhesives</x:v>
       </x:c>
-      <x:c r="I641" t="str">
-        <x:v>roman, roman rx-35 drywall repair primer, specialty &amp; decorative products, wallpaper adhesives</x:v>
+      <x:c r="I641" s="15" t="str">
+        <x:v>drywall repair primer, problem-surface sealer, porous-surface primer, wall preparation coating</x:v>
       </x:c>
       <x:c r="J641" t="str">
         <x:v>Roman</x:v>
@@ -32789,8 +32793,8 @@
       <x:c r="H642" t="str">
         <x:v>Specialty &amp; Decorative Products &gt; Wallpaper Adhesives</x:v>
       </x:c>
-      <x:c r="I642" t="str">
-        <x:v>roman, roman pro 977 ultra prime pigmented wall, specialty &amp; decorative products, wallpaper adhesives</x:v>
+      <x:c r="I642" s="15" t="str">
+        <x:v>wallcovering primer, primer sealer, wall preparation coating, interior primer</x:v>
       </x:c>
       <x:c r="J642" t="str">
         <x:v>Roman</x:v>
@@ -32842,8 +32846,8 @@
       <x:c r="H643" t="str">
         <x:v>Specialty &amp; Decorative Products &gt; Wallpaper Adhesives</x:v>
       </x:c>
-      <x:c r="I643" t="str">
-        <x:v>roman, roman h.d. strippable clear, specialty &amp; decorative products, wallpaper adhesives</x:v>
+      <x:c r="I643" s="15" t="str">
+        <x:v>wallpaper adhesive, wallcovering paste, installation adhesive, interior adhesive</x:v>
       </x:c>
       <x:c r="J643" t="str">
         <x:v>Roman</x:v>
@@ -32889,8 +32893,8 @@
       <x:c r="H644" t="str">
         <x:v>Specialty &amp; Decorative Products &gt; Wallpaper Adhesives</x:v>
       </x:c>
-      <x:c r="I644" t="str">
-        <x:v>roman, roman extreme tack adhesive, specialty &amp; decorative products, wallpaper adhesives</x:v>
+      <x:c r="I644" s="15" t="str">
+        <x:v>wallpaper adhesive, wallcovering paste, installation adhesive, interior adhesive</x:v>
       </x:c>
       <x:c r="J644" t="str">
         <x:v>Roman</x:v>
@@ -32936,8 +32940,8 @@
       <x:c r="H645" t="str">
         <x:v>Paints &gt; Specialty Paints</x:v>
       </x:c>
-      <x:c r="I645" t="str">
-        <x:v>rosco, video projection screen paint white qt, paints, specialty paints</x:v>
+      <x:c r="I645" s="15" t="str">
+        <x:v>scenic paint, projection screen paint, studio coating, specialty paint</x:v>
       </x:c>
       <x:c r="J645" t="str">
         <x:v>Rosco</x:v>
@@ -32986,8 +32990,8 @@
       <x:c r="H646" t="str">
         <x:v>Paints &gt; Specialty Paints</x:v>
       </x:c>
-      <x:c r="I646" t="str">
-        <x:v>rosco, rosco video paint chroma key green, paints, specialty paints</x:v>
+      <x:c r="I646" s="15" t="str">
+        <x:v>scenic paint, projection screen paint, studio coating, specialty paint</x:v>
       </x:c>
       <x:c r="J646" t="str">
         <x:v>Rosco</x:v>
@@ -33039,8 +33043,8 @@
       <x:c r="H647" t="str">
         <x:v>Paints &gt; Specialty Paints</x:v>
       </x:c>
-      <x:c r="I647" t="str">
-        <x:v>rosco, rosco video paint chroma key blue, paints, specialty paints</x:v>
+      <x:c r="I647" s="15" t="str">
+        <x:v>scenic paint, projection screen paint, studio coating, specialty paint</x:v>
       </x:c>
       <x:c r="J647" t="str">
         <x:v>Rosco</x:v>
@@ -33092,8 +33096,8 @@
       <x:c r="H648" t="str">
         <x:v>Paints &gt; Specialty Paints</x:v>
       </x:c>
-      <x:c r="I648" t="str">
-        <x:v>rosco, rosco tv white, paints, specialty paints</x:v>
+      <x:c r="I648" s="15" t="str">
+        <x:v>scenic paint, projection screen paint, studio coating, specialty paint</x:v>
       </x:c>
       <x:c r="J648" t="str">
         <x:v>Rosco</x:v>
@@ -33142,8 +33146,8 @@
       <x:c r="H649" t="str">
         <x:v>Paints &gt; Specialty Paints</x:v>
       </x:c>
-      <x:c r="I649" t="str">
-        <x:v>rosco, rosco tv black, paints, specialty paints</x:v>
+      <x:c r="I649" s="15" t="str">
+        <x:v>scenic paint, projection screen paint, studio coating, specialty paint</x:v>
       </x:c>
       <x:c r="J649" t="str">
         <x:v>Rosco</x:v>
@@ -33192,8 +33196,8 @@
       <x:c r="H650" t="str">
         <x:v>Paints &gt; Specialty Paints</x:v>
       </x:c>
-      <x:c r="I650" t="str">
-        <x:v>rosco, fire retardant paint additive, paints, specialty paints</x:v>
+      <x:c r="I650" s="15" t="str">
+        <x:v>paint additive, fire-retardant additive, coating additive, powder additive</x:v>
       </x:c>
       <x:c r="J650" t="str">
         <x:v>Rosco</x:v>
@@ -33245,8 +33249,8 @@
       <x:c r="H651" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I651" t="str">
-        <x:v>cgc sheetrock, sheetrock 90, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I651" s="15" t="str">
+        <x:v>drywall joint compound, wall repair compound, drywall finishing material, patching compound</x:v>
       </x:c>
       <x:c r="J651" t="str">
         <x:v>CGC Sheetrock</x:v>
@@ -33292,8 +33296,8 @@
       <x:c r="H652" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I652" t="str">
-        <x:v>cgc sheetrock, cgc joint compound, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I652" s="15" t="str">
+        <x:v>drywall joint compound, wall repair compound, drywall finishing material, patching compound</x:v>
       </x:c>
       <x:c r="J652" t="str">
         <x:v>CGC Sheetrock</x:v>
@@ -33347,8 +33351,8 @@
       <x:c r="H653" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I653" t="str">
-        <x:v>cgc sheetrock, cgc dust control pail compound 12l, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I653" s="15" t="str">
+        <x:v>drywall joint compound, wall repair compound, drywall finishing material, patching compound</x:v>
       </x:c>
       <x:c r="J653" t="str">
         <x:v>CGC Sheetrock</x:v>
@@ -33394,8 +33398,8 @@
       <x:c r="H654" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I654" t="str">
-        <x:v>cgc sheetrock, cgc dust control box compound 17l, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I654" s="15" t="str">
+        <x:v>drywall joint compound, wall repair compound, drywall finishing material, patching compound</x:v>
       </x:c>
       <x:c r="J654" t="str">
         <x:v>CGC Sheetrock</x:v>
@@ -33441,8 +33445,8 @@
       <x:c r="H655" t="str">
         <x:v>Paints &gt; Specialty Paints</x:v>
       </x:c>
-      <x:c r="I655" t="str">
-        <x:v>seal-krete, seal-krete clear seal satin, paints, specialty paints</x:v>
+      <x:c r="I655" s="15" t="str">
+        <x:v>concrete sealer, masonry sealer, clear protective coating, satin floor finish</x:v>
       </x:c>
       <x:c r="J655" t="str">
         <x:v>Seal-Krete</x:v>
@@ -33494,8 +33498,8 @@
       <x:c r="H656" t="str">
         <x:v>Paints &gt; Specialty Paints</x:v>
       </x:c>
-      <x:c r="I656" t="str">
-        <x:v>rust-oleum, rust-oleum tub &amp; tile refinishing kit, paints, specialty paints</x:v>
+      <x:c r="I656" s="15" t="str">
+        <x:v>tub and tile coating, refinishing kit, epoxy coating, specialty coating</x:v>
       </x:c>
       <x:c r="J656" t="str">
         <x:v>Rust-Oleum</x:v>
@@ -33547,8 +33551,8 @@
       <x:c r="H657" t="str">
         <x:v>Paints &gt; Specialty Paints</x:v>
       </x:c>
-      <x:c r="I657" t="str">
-        <x:v>rust-oleum, rust-oleum self-etching primer spray, paints, specialty paints</x:v>
+      <x:c r="I657" s="15" t="str">
+        <x:v>self-etching primer, spray primer, metal primer, aerosol primer</x:v>
       </x:c>
       <x:c r="J657" t="str">
         <x:v>Rust-Oleum</x:v>
@@ -33600,8 +33604,8 @@
       <x:c r="H658" t="str">
         <x:v>Paints &gt; Aerosols</x:v>
       </x:c>
-      <x:c r="I658" t="str">
-        <x:v>rust-oleum, rust-oleum mirror effect silver, paints, aerosols</x:v>
+      <x:c r="I658" s="15" t="str">
+        <x:v>mirror-effect spray paint, aerosol paint, reflective metallic coating, specialty finish</x:v>
       </x:c>
       <x:c r="J658" t="str">
         <x:v>Rust-Oleum</x:v>
@@ -33653,8 +33657,8 @@
       <x:c r="H659" t="str">
         <x:v>Paints &gt; Specialty Paints</x:v>
       </x:c>
-      <x:c r="I659" t="str">
-        <x:v>rust-oleum, rust-oleum metallic gold, paints, specialty paints</x:v>
+      <x:c r="I659" s="15" t="str">
+        <x:v>metallic spray paint, aerosol paint, decorative metallic coating, specialty finish</x:v>
       </x:c>
       <x:c r="J659" t="str">
         <x:v>Rust-Oleum</x:v>
@@ -33706,8 +33710,8 @@
       <x:c r="H660" t="str">
         <x:v>Paints &gt; Aerosols</x:v>
       </x:c>
-      <x:c r="I660" t="str">
-        <x:v>rust-oleum, rust-oleum leak seal clear aerosol, paints, aerosols</x:v>
+      <x:c r="I660" s="15" t="str">
+        <x:v>rubberized sealant coating, leak repair coating, aerosol sealant, waterproof coating</x:v>
       </x:c>
       <x:c r="J660" t="str">
         <x:v>Rust-Oleum</x:v>
@@ -33759,8 +33763,8 @@
       <x:c r="H661" t="str">
         <x:v>Paints &gt; Aerosols</x:v>
       </x:c>
-      <x:c r="I661" t="str">
-        <x:v>rust-oleum, rust-oleum leak seal black aerosol, paints, aerosols</x:v>
+      <x:c r="I661" s="15" t="str">
+        <x:v>rubberized sealant coating, leak repair coating, aerosol sealant, waterproof coating</x:v>
       </x:c>
       <x:c r="J661" t="str">
         <x:v>Rust-Oleum</x:v>
@@ -33812,8 +33816,8 @@
       <x:c r="H662" t="str">
         <x:v>Paints &gt; Aerosols</x:v>
       </x:c>
-      <x:c r="I662" t="str">
-        <x:v>rust-oleum, rust-oleum appliance epoxy spray - gloss white, paints, aerosols</x:v>
+      <x:c r="I662" s="15" t="str">
+        <x:v>appliance epoxy paint, spray enamel, epoxy coating, specialty coating</x:v>
       </x:c>
       <x:c r="J662" t="str">
         <x:v>Rust-Oleum</x:v>
@@ -33865,8 +33869,8 @@
       <x:c r="H663" t="str">
         <x:v>Paints &gt; Specialty Paints</x:v>
       </x:c>
-      <x:c r="I663" t="str">
-        <x:v>rust-oleum, rust-oleum painter's touch latex - black, paints, specialty paints</x:v>
+      <x:c r="I663" s="15" t="str">
+        <x:v>latex paint, multi-purpose paint, interior and exterior paint, water-based coating</x:v>
       </x:c>
       <x:c r="J663" t="str">
         <x:v>Rust-Oleum</x:v>
@@ -33923,8 +33927,8 @@
       <x:c r="H664" t="str">
         <x:v>Paints &gt; Aerosols</x:v>
       </x:c>
-      <x:c r="I664" t="str">
-        <x:v>tremclad, tremclad rust primer spray - red oxide, paints, aerosols</x:v>
+      <x:c r="I664" s="15" t="str">
+        <x:v>spray primer, aerosol primer, primer, surface preparation coating, primer sealer, basecoat</x:v>
       </x:c>
       <x:c r="J664" t="str">
         <x:v>Tremclad</x:v>
@@ -33973,8 +33977,8 @@
       <x:c r="H665" t="str">
         <x:v>Paints &gt; Aerosols</x:v>
       </x:c>
-      <x:c r="I665" t="str">
-        <x:v>tremclad, tremclad rust paint spray - gloss white, paints, aerosols</x:v>
+      <x:c r="I665" s="15" t="str">
+        <x:v>rust-preventive paint, metal paint, protective enamel, anti-corrosion coating, spray paint, aerosol paint, specialty coating, decorative coating</x:v>
       </x:c>
       <x:c r="J665" t="str">
         <x:v>Tremclad</x:v>
@@ -34026,8 +34030,8 @@
       <x:c r="H666" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Cleaners &amp; Removers</x:v>
       </x:c>
-      <x:c r="I666" t="str">
-        <x:v>krud kutter, krud kutter original, painting tools &amp; accessories, cleaners &amp; removers</x:v>
+      <x:c r="I666" s="15" t="str">
+        <x:v>multi-purpose cleaner, degreaser, surface cleaner, cleaning concentrate</x:v>
       </x:c>
       <x:c r="J666" t="str">
         <x:v>Krud Kutter</x:v>
@@ -34073,8 +34077,8 @@
       <x:c r="H667" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Cleaners &amp; Removers</x:v>
       </x:c>
-      <x:c r="I667" t="str">
-        <x:v>krud kutter, krud kutter oil grabber stain remover, painting tools &amp; accessories, cleaners &amp; removers</x:v>
+      <x:c r="I667" s="15" t="str">
+        <x:v>oil stain remover, concrete stain cleaner, liquid stain remover, surface cleaner</x:v>
       </x:c>
       <x:c r="J667" t="str">
         <x:v>Krud Kutter</x:v>
@@ -34120,8 +34124,8 @@
       <x:c r="H668" t="str">
         <x:v>Paints &gt; Aerosols</x:v>
       </x:c>
-      <x:c r="I668" t="str">
-        <x:v>concrobium, concrobium mold control spray, paints, aerosols</x:v>
+      <x:c r="I668" s="15" t="str">
+        <x:v>cleaning treatment, aerosol cleaner, surface preparation chemical, mould control treatment</x:v>
       </x:c>
       <x:c r="J668" t="str">
         <x:v>Concrobium</x:v>
@@ -34167,8 +34171,8 @@
       <x:c r="H669" t="str">
         <x:v>Paints &gt; Stains &amp; Varnishes</x:v>
       </x:c>
-      <x:c r="I669" t="str">
-        <x:v>ready seal, ready seal exterior stain natural, paints, stains &amp; varnishes</x:v>
+      <x:c r="I669" s="15" t="str">
+        <x:v>exterior wood stain, penetrating wood finish, wood stain, exterior wood finish</x:v>
       </x:c>
       <x:c r="J669" t="str">
         <x:v>Ready Seal</x:v>
@@ -34220,8 +34224,8 @@
       <x:c r="H670" t="str">
         <x:v>Paints &gt; Stains &amp; Varnishes</x:v>
       </x:c>
-      <x:c r="I670" t="str">
-        <x:v>saman, saman water-based clear finish, paints, stains &amp; varnishes</x:v>
+      <x:c r="I670" s="15" t="str">
+        <x:v>clear finish, protective coating, clear coat, wood finish</x:v>
       </x:c>
       <x:c r="J670" t="str">
         <x:v>SamaN</x:v>
@@ -34270,8 +34274,8 @@
       <x:c r="H671" t="str">
         <x:v>Paints &gt; Stains &amp; Varnishes</x:v>
       </x:c>
-      <x:c r="I671" t="str">
-        <x:v>saman, saman water-based wood floor stain, paints, stains &amp; varnishes</x:v>
+      <x:c r="I671" s="15" t="str">
+        <x:v>wood floor stain, interior wood stain, wood finish, floor finish</x:v>
       </x:c>
       <x:c r="J671" t="str">
         <x:v>SamaN</x:v>
@@ -34323,8 +34327,8 @@
       <x:c r="H672" t="str">
         <x:v>Paints &gt; Stains &amp; Varnishes</x:v>
       </x:c>
-      <x:c r="I672" t="str">
-        <x:v>saman, saman water-based clear glaze, paints, stains &amp; varnishes</x:v>
+      <x:c r="I672" s="15" t="str">
+        <x:v>decorative glaze, wood finishing glaze, toning finish, decorative coating</x:v>
       </x:c>
       <x:c r="J672" t="str">
         <x:v>SamaN</x:v>
@@ -34373,8 +34377,8 @@
       <x:c r="H673" t="str">
         <x:v>Paints &gt; Stains &amp; Varnishes</x:v>
       </x:c>
-      <x:c r="I673" t="str">
-        <x:v>saman, saman tung oil natural, paints, stains &amp; varnishes</x:v>
+      <x:c r="I673" s="15" t="str">
+        <x:v>tung oil finish, drying oil, wood finish, oil-based finish</x:v>
       </x:c>
       <x:c r="J673" t="str">
         <x:v>SamaN</x:v>
@@ -34426,8 +34430,8 @@
       <x:c r="H674" t="str">
         <x:v>Paints &gt; Epoxy</x:v>
       </x:c>
-      <x:c r="I674" t="str">
-        <x:v>saman, saman tabletop epoxy, paints, epoxy</x:v>
+      <x:c r="I674" s="15" t="str">
+        <x:v>casting epoxy, clear epoxy resin, two-part epoxy, decorative resin</x:v>
       </x:c>
       <x:c r="J674" t="str">
         <x:v>SamaN</x:v>
@@ -34476,8 +34480,8 @@
       <x:c r="H675" t="str">
         <x:v>Paints &gt; Stains &amp; Varnishes</x:v>
       </x:c>
-      <x:c r="I675" t="str">
-        <x:v>saman, saman retarder gallon, paints, stains &amp; varnishes</x:v>
+      <x:c r="I675" s="15" t="str">
+        <x:v>coating retarder, drying-time additive, finish additive, paint additive</x:v>
       </x:c>
       <x:c r="J675" t="str">
         <x:v>SamaN</x:v>
@@ -34523,8 +34527,8 @@
       <x:c r="H676" t="str">
         <x:v>Paints &gt; Epoxy</x:v>
       </x:c>
-      <x:c r="I676" t="str">
-        <x:v>saman, saman casting epoxy 1.5l, paints, epoxy</x:v>
+      <x:c r="I676" s="15" t="str">
+        <x:v>casting epoxy, clear epoxy resin, two-part epoxy, decorative resin</x:v>
       </x:c>
       <x:c r="J676" t="str">
         <x:v>SamaN</x:v>
@@ -34570,8 +34574,8 @@
       <x:c r="H677" t="str">
         <x:v>Paints &gt; Stains &amp; Varnishes</x:v>
       </x:c>
-      <x:c r="I677" t="str">
-        <x:v>saman, saman beeswax wood finish, paints, stains &amp; varnishes</x:v>
+      <x:c r="I677" s="15" t="str">
+        <x:v>beeswax finish, wood wax, wood finish, protective wax finish</x:v>
       </x:c>
       <x:c r="J677" t="str">
         <x:v>SamaN</x:v>
@@ -34620,8 +34624,8 @@
       <x:c r="H678" t="str">
         <x:v>Paints &gt; Aerosols</x:v>
       </x:c>
-      <x:c r="I678" t="str">
-        <x:v>canpro, canpro tsp eco spray, paints, aerosols</x:v>
+      <x:c r="I678" s="15" t="str">
+        <x:v>cleaning treatment, aerosol cleaner, surface preparation chemical, tsp substitute cleaner, tsp cleaner, surface preparation cleaner, degreaser, paint preparation chemical</x:v>
       </x:c>
       <x:c r="J678" t="str">
         <x:v>CanPro</x:v>
@@ -34667,8 +34671,8 @@
       <x:c r="H679" t="str">
         <x:v>Paints &gt; Driveway Coatings</x:v>
       </x:c>
-      <x:c r="I679" t="str">
-        <x:v>seal king, sealking strip-all, paints, driveway coatings</x:v>
+      <x:c r="I679" s="15" t="str">
+        <x:v>coating remover, paint remover, finish stripper, surface preparation chemical</x:v>
       </x:c>
       <x:c r="J679" t="str">
         <x:v>Seal King</x:v>
@@ -34714,8 +34718,8 @@
       <x:c r="H680" t="str">
         <x:v>Paints &gt; Driveway Coatings</x:v>
       </x:c>
-      <x:c r="I680" t="str">
-        <x:v>seal king, seal king seal-grip, paints, driveway coatings</x:v>
+      <x:c r="I680" s="15" t="str">
+        <x:v>anti-slip additive, coating additive, traction additive, floor coating additive</x:v>
       </x:c>
       <x:c r="J680" t="str">
         <x:v>Seal King</x:v>
@@ -34761,8 +34765,8 @@
       <x:c r="H681" t="str">
         <x:v>Paints &gt; Driveway Coatings</x:v>
       </x:c>
-      <x:c r="I681" t="str">
-        <x:v>seal king, seal king rust remover, paints, driveway coatings</x:v>
+      <x:c r="I681" s="15" t="str">
+        <x:v>rust remover, metal cleaner, surface preparation chemical, corrosion remover</x:v>
       </x:c>
       <x:c r="J681" t="str">
         <x:v>Seal King</x:v>
@@ -34808,8 +34812,8 @@
       <x:c r="H682" t="str">
         <x:v>Paints &gt; Driveway Coatings</x:v>
       </x:c>
-      <x:c r="I682" t="str">
-        <x:v>seal king, seal king paving stone sealer semi, paints, driveway coatings</x:v>
+      <x:c r="I682" s="15" t="str">
+        <x:v>paver sealer, masonry sealer, protective clear coat, exterior coating</x:v>
       </x:c>
       <x:c r="J682" t="str">
         <x:v>Seal King</x:v>
@@ -34861,8 +34865,8 @@
       <x:c r="H683" t="str">
         <x:v>Paints &gt; Driveway Coatings</x:v>
       </x:c>
-      <x:c r="I683" t="str">
-        <x:v>seal king, seal king oil-off degreaser, paints, driveway coatings</x:v>
+      <x:c r="I683" s="15" t="str">
+        <x:v>degreaser, oil stain remover, masonry cleaner, surface preparation chemical, heavy-duty cleaner, surface preparation cleaner, concentrated cleaner</x:v>
       </x:c>
       <x:c r="J683" t="str">
         <x:v>Seal King</x:v>
@@ -34908,8 +34912,8 @@
       <x:c r="H684" t="str">
         <x:v>Paints &gt; Driveway Coatings</x:v>
       </x:c>
-      <x:c r="I684" t="str">
-        <x:v>seal king, seal king natural stone sealer natural l, paints, driveway coatings</x:v>
+      <x:c r="I684" s="15" t="str">
+        <x:v>natural stone sealer, masonry sealer, protective clear coat, exterior coating</x:v>
       </x:c>
       <x:c r="J684" t="str">
         <x:v>Seal King</x:v>
@@ -34961,8 +34965,8 @@
       <x:c r="H685" t="str">
         <x:v>Paints &gt; Driveway Coatings</x:v>
       </x:c>
-      <x:c r="I685" t="str">
-        <x:v>seal king, seal king natural stone sealer colour en, paints, driveway coatings</x:v>
+      <x:c r="I685" s="15" t="str">
+        <x:v>natural stone sealer, masonry sealer, protective clear coat, exterior coating</x:v>
       </x:c>
       <x:c r="J685" t="str">
         <x:v>Seal King</x:v>
@@ -35014,8 +35018,8 @@
       <x:c r="H686" t="str">
         <x:v>Paints &gt; Driveway Coatings</x:v>
       </x:c>
-      <x:c r="I686" t="str">
-        <x:v>seal king, seal king grease release, paints, driveway coatings</x:v>
+      <x:c r="I686" s="15" t="str">
+        <x:v>degreaser, oil stain remover, masonry cleaner, surface preparation chemical</x:v>
       </x:c>
       <x:c r="J686" t="str">
         <x:v>Seal King</x:v>
@@ -35061,8 +35065,8 @@
       <x:c r="H687" t="str">
         <x:v>Paints &gt; Driveway Coatings</x:v>
       </x:c>
-      <x:c r="I687" t="str">
-        <x:v>seal king, seal king efflorescence cleane, paints, driveway coatings</x:v>
+      <x:c r="I687" s="15" t="str">
+        <x:v>efflorescence cleaner, masonry cleaner, acidic surface cleaner, surface preparation chemical</x:v>
       </x:c>
       <x:c r="J687" t="str">
         <x:v>Seal King</x:v>
@@ -35108,8 +35112,8 @@
       <x:c r="H688" t="str">
         <x:v>Paints &gt; Driveway Coatings</x:v>
       </x:c>
-      <x:c r="I688" t="str">
-        <x:v>seal king, seal king easy strip, paints, driveway coatings</x:v>
+      <x:c r="I688" s="15" t="str">
+        <x:v>coating remover, paint remover, finish stripper, surface preparation chemical</x:v>
       </x:c>
       <x:c r="J688" t="str">
         <x:v>Seal King</x:v>
@@ -35155,8 +35159,8 @@
       <x:c r="H689" t="str">
         <x:v>Paints &gt; Driveway Coatings</x:v>
       </x:c>
-      <x:c r="I689" t="str">
-        <x:v>seal king, seal king basement floor seale clear, paints, driveway coatings</x:v>
+      <x:c r="I689" s="15" t="str">
+        <x:v>basement floor sealer, concrete sealer, clear floor coating, protective coating</x:v>
       </x:c>
       <x:c r="J689" t="str">
         <x:v>Seal King</x:v>
@@ -35208,8 +35212,8 @@
       <x:c r="H690" t="str">
         <x:v>Paints &gt; Aerosols</x:v>
       </x:c>
-      <x:c r="I690" t="str">
-        <x:v>allpro, allpro spray can fire engine red, paints, aerosols</x:v>
+      <x:c r="I690" s="15" t="str">
+        <x:v>spray paint, aerosol paint, specialty coating, decorative coating</x:v>
       </x:c>
       <x:c r="J690" t="str">
         <x:v>AllPro</x:v>
@@ -35261,8 +35265,8 @@
       <x:c r="H691" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I691" t="str">
-        <x:v>frogtape, frog tape pro grade blue, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I691" s="15" t="str">
+        <x:v>masking tape, painter's tape, pressure-sensitive tape, painting accessory</x:v>
       </x:c>
       <x:c r="J691" t="str">
         <x:v>FrogTape</x:v>
@@ -35308,8 +35312,8 @@
       <x:c r="H692" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I692" t="str">
-        <x:v>frogtape, frogtape delicate surface painter's tape 1 1/2", painting tools &amp; accessories, tools</x:v>
+      <x:c r="I692" s="15" t="str">
+        <x:v>masking tape, painter's tape, pressure-sensitive tape, painting accessory, delicate-surface masking tape</x:v>
       </x:c>
       <x:c r="J692" t="str">
         <x:v>FrogTape</x:v>
@@ -35355,8 +35359,8 @@
       <x:c r="H693" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I693" t="str">
-        <x:v>frogtape, frogtape advanced painter's tape 1 1/2", painting tools &amp; accessories, tools</x:v>
+      <x:c r="I693" s="15" t="str">
+        <x:v>masking tape, painter's tape, pressure-sensitive tape, painting accessory</x:v>
       </x:c>
       <x:c r="J693" t="str">
         <x:v>FrogTape</x:v>
@@ -35402,8 +35406,8 @@
       <x:c r="H694" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I694" t="str">
-        <x:v>frogtape, frog tape, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I694" s="15" t="str">
+        <x:v>masking tape, painter's tape, pressure-sensitive tape, painting accessory</x:v>
       </x:c>
       <x:c r="J694" t="str">
         <x:v>FrogTape</x:v>
@@ -35449,8 +35453,8 @@
       <x:c r="H695" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I695" t="str">
-        <x:v>frogtape, shurtape green masking tape 1 1/2", painting tools &amp; accessories, tools</x:v>
+      <x:c r="I695" s="15" t="str">
+        <x:v>masking tape, painter's tape, pressure-sensitive tape, painting accessory</x:v>
       </x:c>
       <x:c r="J695" t="str">
         <x:v>FrogTape</x:v>
@@ -35496,8 +35500,8 @@
       <x:c r="H696" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I696" t="str">
-        <x:v>sia, siafast disc 8 hole 100 grit, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I696" s="15" t="str">
+        <x:v>sandpaper, coated abrasive, surface preparation abrasive, sanding material</x:v>
       </x:c>
       <x:c r="J696" t="str">
         <x:v>Sia</x:v>
@@ -35543,8 +35547,8 @@
       <x:c r="H697" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I697" t="str">
-        <x:v>sia, sia soft roll 3 1/2" x 11 yd - 100 grit, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I697" s="15" t="str">
+        <x:v>sandpaper, coated abrasive, surface preparation abrasive, sanding material</x:v>
       </x:c>
       <x:c r="J697" t="str">
         <x:v>Sia</x:v>
@@ -35590,8 +35594,8 @@
       <x:c r="H698" t="str">
         <x:v>Paints &gt; Stains &amp; Varnishes</x:v>
       </x:c>
-      <x:c r="I698" t="str">
-        <x:v>sikkens, sikkens srd 005 natural oak, paints, stains &amp; varnishes</x:v>
+      <x:c r="I698" s="15" t="str">
+        <x:v>exterior wood stain, penetrating wood finish, wood stain, exterior wood finish</x:v>
       </x:c>
       <x:c r="J698" t="str">
         <x:v>Sikkens</x:v>
@@ -35643,8 +35647,8 @@
       <x:c r="H699" t="str">
         <x:v>Paints &gt; Stains &amp; Varnishes</x:v>
       </x:c>
-      <x:c r="I699" t="str">
-        <x:v>sikkens, sikkens cetol dek finish cedar 077, paints, stains &amp; varnishes</x:v>
+      <x:c r="I699" s="15" t="str">
+        <x:v>exterior wood stain, penetrating wood finish, wood stain, exterior wood finish</x:v>
       </x:c>
       <x:c r="J699" t="str">
         <x:v>Sikkens</x:v>
@@ -35696,8 +35700,8 @@
       <x:c r="H700" t="str">
         <x:v>Paints &gt; Stains &amp; Varnishes</x:v>
       </x:c>
-      <x:c r="I700" t="str">
-        <x:v>sikkens, cetol door+window satin colorless, paints, stains &amp; varnishes</x:v>
+      <x:c r="I700" s="15" t="str">
+        <x:v>exterior wood stain, penetrating wood finish, wood stain, exterior wood finish</x:v>
       </x:c>
       <x:c r="J700" t="str">
         <x:v>Sikkens</x:v>
@@ -35749,8 +35753,8 @@
       <x:c r="H701" t="str">
         <x:v>Paints &gt; Stains &amp; Varnishes</x:v>
       </x:c>
-      <x:c r="I701" t="str">
-        <x:v>sikkens, cetol 23 005 natural oak, paints, stains &amp; varnishes</x:v>
+      <x:c r="I701" s="15" t="str">
+        <x:v>exterior wood stain, penetrating wood finish, wood stain, exterior wood finish</x:v>
       </x:c>
       <x:c r="J701" t="str">
         <x:v>Sikkens</x:v>
@@ -35802,8 +35806,8 @@
       <x:c r="H702" t="str">
         <x:v>Paints &gt; Stains &amp; Varnishes</x:v>
       </x:c>
-      <x:c r="I702" t="str">
-        <x:v>sikkens, cetol 1 005 natural oak, paints, stains &amp; varnishes</x:v>
+      <x:c r="I702" s="15" t="str">
+        <x:v>exterior wood stain, penetrating wood finish, wood stain, exterior wood finish</x:v>
       </x:c>
       <x:c r="J702" t="str">
         <x:v>Sikkens</x:v>
@@ -35855,8 +35859,8 @@
       <x:c r="H703" t="str">
         <x:v>Paints &gt; Specialty Paints</x:v>
       </x:c>
-      <x:c r="I703" t="str">
-        <x:v>simiron, smark dry erase paint clear 200 sq ft, paints, specialty paints</x:v>
+      <x:c r="I703" s="15" t="str">
+        <x:v>dry erase coating, whiteboard paint, clear specialty coating, two-part coating</x:v>
       </x:c>
       <x:c r="J703" t="str">
         <x:v>Simiron</x:v>
@@ -35908,8 +35912,8 @@
       <x:c r="H704" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I704" t="str">
-        <x:v>sioux, sioux orbital sander velcro, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I704" s="15" t="str">
+        <x:v>power sander, orbital sander, surface preparation tool, power tool</x:v>
       </x:c>
       <x:c r="J704" t="str">
         <x:v>Sioux</x:v>
@@ -35955,8 +35959,8 @@
       <x:c r="H705" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I705" t="str">
-        <x:v>sioux, sioux orbital sander, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I705" s="15" t="str">
+        <x:v>power sander, orbital sander, surface preparation tool, power tool</x:v>
       </x:c>
       <x:c r="J705" t="str">
         <x:v>Sioux</x:v>
@@ -36002,8 +36006,8 @@
       <x:c r="H706" t="str">
         <x:v>Paints &gt; Stains &amp; Varnishes</x:v>
       </x:c>
-      <x:c r="I706" t="str">
-        <x:v>sunshield, sunshield c-tone, paints, stains &amp; varnishes</x:v>
+      <x:c r="I706" s="15" t="str">
+        <x:v>exterior wood stain, penetrating wood finish, tinted wood finish, wood preservative</x:v>
       </x:c>
       <x:c r="J706" t="str">
         <x:v>SunShield</x:v>
@@ -36049,8 +36053,8 @@
       <x:c r="H707" t="str">
         <x:v>Paints &gt; Stains &amp; Varnishes</x:v>
       </x:c>
-      <x:c r="I707" t="str">
-        <x:v>sunshield, sunshield clear, paints, stains &amp; varnishes</x:v>
+      <x:c r="I707" s="15" t="str">
+        <x:v>clear wood finish, exterior wood finish, penetrating wood finish, wood preservative</x:v>
       </x:c>
       <x:c r="J707" t="str">
         <x:v>SunShield</x:v>
@@ -36096,8 +36100,8 @@
       <x:c r="H708" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I708" t="str">
-        <x:v>simms, simms tray arm, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I708" s="15" t="str">
+        <x:v>paint tray arm, roller tray support, paint tray accessory, painting tool</x:v>
       </x:c>
       <x:c r="J708" t="str">
         <x:v>Simms</x:v>
@@ -36143,8 +36147,8 @@
       <x:c r="H709" t="str">
         <x:v>Specialty &amp; Decorative Products &gt; Gold Leaf</x:v>
       </x:c>
-      <x:c r="I709" t="str">
-        <x:v>the gold leaf company, gold leaf 6.5" x 6.5" box of 10,000, specialty &amp; decorative products, gold leaf</x:v>
+      <x:c r="I709" s="15" t="str">
+        <x:v>gold leaf, metal leaf, gilding material, decorative finish</x:v>
       </x:c>
       <x:c r="J709" t="str">
         <x:v>The Gold Leaf Company</x:v>
@@ -36190,8 +36194,8 @@
       <x:c r="H710" t="str">
         <x:v>Spray Equipment Sales &amp; Service &gt; Titan</x:v>
       </x:c>
-      <x:c r="I710" t="str">
-        <x:v>titan, wagner furno heat gun, spray equipment sales &amp; service</x:v>
+      <x:c r="I710" s="15" t="str">
+        <x:v>heat gun, paint stripping tool, power tool, hot-air tool</x:v>
       </x:c>
       <x:c r="J710" t="str">
         <x:v>Titan</x:v>
@@ -36237,8 +36241,8 @@
       <x:c r="H711" t="str">
         <x:v>Spray Equipment Sales &amp; Service &gt; Titan</x:v>
       </x:c>
-      <x:c r="I711" t="str">
-        <x:v>titan, titan synergy fine finish tip, spray equipment sales &amp; service</x:v>
+      <x:c r="I711" s="15" t="str">
+        <x:v>airless spray tip, sprayer nozzle, paint sprayer accessory, coating application part</x:v>
       </x:c>
       <x:c r="J711" t="str">
         <x:v>Titan</x:v>
@@ -36284,8 +36288,8 @@
       <x:c r="H712" t="str">
         <x:v>Spray Equipment Sales &amp; Service &gt; Titan</x:v>
       </x:c>
-      <x:c r="I712" t="str">
-        <x:v>titan, titan sc-6 plus red tip, spray equipment sales &amp; service</x:v>
+      <x:c r="I712" s="15" t="str">
+        <x:v>airless spray tip, sprayer nozzle, paint sprayer accessory, coating application part</x:v>
       </x:c>
       <x:c r="J712" t="str">
         <x:v>Titan</x:v>
@@ -36331,8 +36335,8 @@
       <x:c r="H713" t="str">
         <x:v>Spray Equipment Sales &amp; Service &gt; Titan</x:v>
       </x:c>
-      <x:c r="I713" t="str">
-        <x:v>titan, titan rx-80 2 finger w/tr2, spray equipment sales &amp; service</x:v>
+      <x:c r="I713" s="15" t="str">
+        <x:v>airless spray gun, paint spray gun, coating application equipment, professional spray equipment</x:v>
       </x:c>
       <x:c r="J713" t="str">
         <x:v>Titan</x:v>
@@ -36378,8 +36382,8 @@
       <x:c r="H714" t="str">
         <x:v>Spray Equipment Sales &amp; Service &gt; Titan</x:v>
       </x:c>
-      <x:c r="I714" t="str">
-        <x:v>titan, titan piston lube qt, spray equipment sales &amp; service</x:v>
+      <x:c r="I714" s="15" t="str">
+        <x:v>sprayer lubricant, pump lubricant, paint sprayer maintenance product, equipment lubricant</x:v>
       </x:c>
       <x:c r="J714" t="str">
         <x:v>Titan</x:v>
@@ -36425,8 +36429,8 @@
       <x:c r="H715" t="str">
         <x:v>Spray Equipment Sales &amp; Service &gt; Titan</x:v>
       </x:c>
-      <x:c r="I715" t="str">
-        <x:v>titan, titan piston lube, spray equipment sales &amp; service</x:v>
+      <x:c r="I715" s="15" t="str">
+        <x:v>sprayer lubricant, pump lubricant, paint sprayer maintenance product, equipment lubricant</x:v>
       </x:c>
       <x:c r="J715" t="str">
         <x:v>Titan</x:v>
@@ -36472,8 +36476,8 @@
       <x:c r="H716" t="str">
         <x:v>Spray Equipment Sales &amp; Service &gt; Titan</x:v>
       </x:c>
-      <x:c r="I716" t="str">
-        <x:v>titan, titan impact x440 airless, spray equipment sales &amp; service</x:v>
+      <x:c r="I716" s="15" t="str">
+        <x:v>paint sprayer, airless paint sprayer, coating application equipment, professional spray equipment</x:v>
       </x:c>
       <x:c r="J716" t="str">
         <x:v>Titan</x:v>
@@ -36519,8 +36523,8 @@
       <x:c r="H717" t="str">
         <x:v>Spray Equipment Sales &amp; Service &gt; Titan</x:v>
       </x:c>
-      <x:c r="I717" t="str">
-        <x:v>titan, titan impact x 120 backpack, spray equipment sales &amp; service</x:v>
+      <x:c r="I717" s="15" t="str">
+        <x:v>backpack paint sprayer, airless paint sprayer, portable spray system, coating application equipment</x:v>
       </x:c>
       <x:c r="J717" t="str">
         <x:v>Titan</x:v>
@@ -36566,8 +36570,8 @@
       <x:c r="H718" t="str">
         <x:v>Spray Equipment Sales &amp; Service &gt; Titan</x:v>
       </x:c>
-      <x:c r="I718" t="str">
-        <x:v>titan, titan hea tips, spray equipment sales &amp; service</x:v>
+      <x:c r="I718" s="15" t="str">
+        <x:v>airless spray tip, sprayer nozzle, paint sprayer accessory, coating application part</x:v>
       </x:c>
       <x:c r="J718" t="str">
         <x:v>Titan</x:v>
@@ -36613,8 +36617,8 @@
       <x:c r="H719" t="str">
         <x:v>Spray Equipment Sales &amp; Service &gt; Titan</x:v>
       </x:c>
-      <x:c r="I719" t="str">
-        <x:v>titan, titan gun extension, spray equipment sales &amp; service</x:v>
+      <x:c r="I719" s="15" t="str">
+        <x:v>spray gun extension, paint sprayer accessory, extension wand, coating application part</x:v>
       </x:c>
       <x:c r="J719" t="str">
         <x:v>Titan</x:v>
@@ -36660,8 +36664,8 @@
       <x:c r="H720" t="str">
         <x:v>Spray Equipment Sales &amp; Service &gt; Titan</x:v>
       </x:c>
-      <x:c r="I720" t="str">
-        <x:v>titan, titan 640i impact skid, spray equipment sales &amp; service</x:v>
+      <x:c r="I720" s="15" t="str">
+        <x:v>skid-mounted paint sprayer, airless paint sprayer, professional spray system, coating application equipment</x:v>
       </x:c>
       <x:c r="J720" t="str">
         <x:v>Titan</x:v>
@@ -36707,8 +36711,8 @@
       <x:c r="H721" t="str">
         <x:v>Spray Equipment Sales &amp; Service &gt; Titan</x:v>
       </x:c>
-      <x:c r="I721" t="str">
-        <x:v>titan, titan airless hose, spray equipment sales &amp; service</x:v>
+      <x:c r="I721" s="15" t="str">
+        <x:v>airless spray hose, paint sprayer hose, high-pressure hose, spray equipment accessory</x:v>
       </x:c>
       <x:c r="J721" t="str">
         <x:v>Titan</x:v>
@@ -36754,8 +36758,8 @@
       <x:c r="H722" t="str">
         <x:v>Spray Equipment Sales &amp; Service &gt; Titan</x:v>
       </x:c>
-      <x:c r="I722" t="str">
-        <x:v>titan, titan hose, spray equipment sales &amp; service</x:v>
+      <x:c r="I722" s="15" t="str">
+        <x:v>airless spray hose, paint sprayer hose, spray equipment accessory, high-pressure hose</x:v>
       </x:c>
       <x:c r="J722" t="str">
         <x:v>Titan</x:v>
@@ -36801,8 +36805,8 @@
       <x:c r="H723" t="str">
         <x:v>Spray Equipment Sales &amp; Service &gt; Titan</x:v>
       </x:c>
-      <x:c r="I723" t="str">
-        <x:v>titan, gun filter 60 mesh, spray equipment sales &amp; service</x:v>
+      <x:c r="I723" s="15" t="str">
+        <x:v>spray gun filter, paint sprayer filter, spray equipment accessory, replacement filter</x:v>
       </x:c>
       <x:c r="J723" t="str">
         <x:v>Titan</x:v>
@@ -36848,8 +36852,8 @@
       <x:c r="H724" t="str">
         <x:v>Spray Equipment Sales &amp; Service &gt; Titan</x:v>
       </x:c>
-      <x:c r="I724" t="str">
-        <x:v>titan, capspray 106, spray equipment sales &amp; service</x:v>
+      <x:c r="I724" s="15" t="str">
+        <x:v>hvlp turbine sprayer, paint spray system, coating application equipment, professional spray equipment</x:v>
       </x:c>
       <x:c r="J724" t="str">
         <x:v>Titan</x:v>
@@ -36895,8 +36899,8 @@
       <x:c r="H725" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I725" t="str">
-        <x:v>toolway, durapro premium contact cement, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I725" s="15" t="str">
+        <x:v>contact cement, solvent-based adhesive, construction adhesive, laminate adhesive</x:v>
       </x:c>
       <x:c r="J725" t="str">
         <x:v>Toolway</x:v>
@@ -36942,8 +36946,8 @@
       <x:c r="H726" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I726" t="str">
-        <x:v>pc products, wire brush set, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I726" s="15" t="str">
+        <x:v>wire brush, surface preparation brush, rust-removal tool, hand tool</x:v>
       </x:c>
       <x:c r="J726" t="str">
         <x:v>PC Products</x:v>
@@ -36997,8 +37001,8 @@
       <x:c r="H727" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Clothing &amp; Safety</x:v>
       </x:c>
-      <x:c r="I727" t="str">
-        <x:v>toolway, twx neoprene knee pads, painting tools &amp; accessories, clothing &amp; safety</x:v>
+      <x:c r="I727" s="15" t="str">
+        <x:v>knee pads, knee protection, jobsite safety gear, personal protective equipment</x:v>
       </x:c>
       <x:c r="J727" t="str">
         <x:v>Toolway</x:v>
@@ -37044,8 +37048,8 @@
       <x:c r="H728" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Clothing &amp; Safety</x:v>
       </x:c>
-      <x:c r="I728" t="str">
-        <x:v>toolway, toolway foam knee pads, painting tools &amp; accessories, clothing &amp; safety</x:v>
+      <x:c r="I728" s="15" t="str">
+        <x:v>knee pads, knee protection, jobsite safety gear, personal protective equipment</x:v>
       </x:c>
       <x:c r="J728" t="str">
         <x:v>Toolway</x:v>
@@ -37091,8 +37095,8 @@
       <x:c r="H729" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I729" t="str">
-        <x:v>toolway, polyfilla prep, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I729" s="15" t="str">
+        <x:v>spackling compound, wall repair filler, patching compound, surface repair product</x:v>
       </x:c>
       <x:c r="J729" t="str">
         <x:v>Toolway</x:v>
@@ -37138,8 +37142,8 @@
       <x:c r="H730" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I730" t="str">
-        <x:v>toolway, plastic mud pan, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I730" s="15" t="str">
+        <x:v>drywall mud pan, joint compound tray, drywall finishing tool, hand tool</x:v>
       </x:c>
       <x:c r="J730" t="str">
         <x:v>Toolway</x:v>
@@ -37185,8 +37189,8 @@
       <x:c r="H731" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I731" t="str">
-        <x:v>toolway, pl premium construction adhesive, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I731" s="15" t="str">
+        <x:v>construction adhesive, polyurethane adhesive, heavy-duty adhesive, cartridge adhesive</x:v>
       </x:c>
       <x:c r="J731" t="str">
         <x:v>Toolway</x:v>
@@ -37232,8 +37236,8 @@
       <x:c r="H732" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I732" t="str">
-        <x:v>toolway, muriatic acid, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I732" s="15" t="str">
+        <x:v>muriatic acid, masonry etcher, acid cleaner, surface preparation chemical</x:v>
       </x:c>
       <x:c r="J732" t="str">
         <x:v>Toolway</x:v>
@@ -37279,8 +37283,8 @@
       <x:c r="H733" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I733" t="str">
-        <x:v>toolway, measuring wheel, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I733" s="15" t="str">
+        <x:v>measuring wheel, distance measuring tool, layout tool, hand tool</x:v>
       </x:c>
       <x:c r="J733" t="str">
         <x:v>Toolway</x:v>
@@ -37326,8 +37330,8 @@
       <x:c r="H734" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I734" t="str">
-        <x:v>toolway, instant poly filla tube, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I734" s="15" t="str">
+        <x:v>spackling compound, wall repair filler, patching compound, surface repair product</x:v>
       </x:c>
       <x:c r="J734" t="str">
         <x:v>Toolway</x:v>
@@ -37373,8 +37377,8 @@
       <x:c r="H735" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I735" t="str">
-        <x:v>toolway, toolway heavy-duty angled broom 16" with 48" handle, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I735" s="15" t="str">
+        <x:v>push broom, angled broom, cleaning tool, floor cleaning tool</x:v>
       </x:c>
       <x:c r="J735" t="str">
         <x:v>Toolway</x:v>
@@ -37420,8 +37424,8 @@
       <x:c r="H736" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I736" t="str">
-        <x:v>toolway, ez clean black garbage bags 15pk 3mil, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I736" s="15" t="str">
+        <x:v>contractor garbage bag, heavy-duty waste bag, cleanup supply, jobsite accessory</x:v>
       </x:c>
       <x:c r="J736" t="str">
         <x:v>Toolway</x:v>
@@ -37467,8 +37471,8 @@
       <x:c r="H737" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I737" t="str">
-        <x:v>toolway, extension cord 15m int/ext, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I737" s="15" t="str">
+        <x:v>extension cord, electrical power cord, jobsite power accessory, outdoor extension cord</x:v>
       </x:c>
       <x:c r="J737" t="str">
         <x:v>Toolway</x:v>
@@ -37514,8 +37518,8 @@
       <x:c r="H738" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I738" t="str">
-        <x:v>allpro, allpro pro stretch caulking white, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I738" s="15" t="str">
+        <x:v>sealant, caulk, joint sealant, gap-filling compound, elastomeric sealant, paintable caulk</x:v>
       </x:c>
       <x:c r="J738" t="str">
         <x:v>AllPro</x:v>
@@ -37561,8 +37565,8 @@
       <x:c r="H739" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I739" t="str">
-        <x:v>trimaco, x-board surface protector, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I739" s="15" t="str">
+        <x:v>floor protection, surface protection material, protective paper, painting accessory</x:v>
       </x:c>
       <x:c r="J739" t="str">
         <x:v>Trimaco</x:v>
@@ -37608,8 +37612,8 @@
       <x:c r="H740" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I740" t="str">
-        <x:v>trimaco, trimaco protective film for carpets, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I740" s="15" t="str">
+        <x:v>carpet protection film, self-adhesive protective film, surface protection, painting accessory</x:v>
       </x:c>
       <x:c r="J740" t="str">
         <x:v>Trimaco</x:v>
@@ -37655,8 +37659,8 @@
       <x:c r="H741" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I741" t="str">
-        <x:v>trimaco, trimaco 90 day floorsmart tape, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I741" s="15" t="str">
+        <x:v>masking tape, painter's tape, pressure-sensitive tape, painting accessory</x:v>
       </x:c>
       <x:c r="J741" t="str">
         <x:v>Trimaco</x:v>
@@ -37702,8 +37706,8 @@
       <x:c r="H742" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I742" t="str">
-        <x:v>trimaco, stay put canvas plus runner, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I742" s="15" t="str">
+        <x:v>drop cloth, surface protection, painting cover, painting accessory</x:v>
       </x:c>
       <x:c r="J742" t="str">
         <x:v>Trimaco</x:v>
@@ -37749,8 +37753,8 @@
       <x:c r="H743" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I743" t="str">
-        <x:v>trimaco, protective film for hard surfaces x, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I743" s="15" t="str">
+        <x:v>hard-surface protection film, self-adhesive protective film, surface protection, painting accessory</x:v>
       </x:c>
       <x:c r="J743" t="str">
         <x:v>Trimaco</x:v>
@@ -37796,8 +37800,8 @@
       <x:c r="H744" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I744" t="str">
-        <x:v>trimaco, gallon nylon strainer, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I744" s="15" t="str">
+        <x:v>paint strainer, coating filter, paint preparation accessory, painting tool</x:v>
       </x:c>
       <x:c r="J744" t="str">
         <x:v>Trimaco</x:v>
@@ -37843,8 +37847,8 @@
       <x:c r="H745" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I745" t="str">
-        <x:v>trimaco, floorshell seam tape, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I745" s="15" t="str">
+        <x:v>floor protection seam tape, reinforcement tape, surface protection accessory, heavy-duty tape</x:v>
       </x:c>
       <x:c r="J745" t="str">
         <x:v>Trimaco</x:v>
@@ -37890,8 +37894,8 @@
       <x:c r="H746" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I746" t="str">
-        <x:v>trimaco, easy mask tape n drape, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I746" s="15" t="str">
+        <x:v>pre-taped masking film, masking drop cloth, surface protection, painting accessory</x:v>
       </x:c>
       <x:c r="J746" t="str">
         <x:v>Trimaco</x:v>
@@ -37937,8 +37941,8 @@
       <x:c r="H747" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I747" t="str">
-        <x:v>allpro, cone strainer allpro, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I747" s="15" t="str">
+        <x:v>paint strainer, coating filter, paint preparation accessory, painting tool</x:v>
       </x:c>
       <x:c r="J747" t="str">
         <x:v>AllPro</x:v>
@@ -37984,8 +37988,8 @@
       <x:c r="H748" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I748" t="str">
-        <x:v>trimaco, cone strainer, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I748" s="15" t="str">
+        <x:v>paint strainer, coating filter, paint preparation accessory, painting tool</x:v>
       </x:c>
       <x:c r="J748" t="str">
         <x:v>Trimaco</x:v>
@@ -38031,8 +38035,8 @@
       <x:c r="H749" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I749" t="str">
-        <x:v>trimaco, caution wet paint, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I749" s="15" t="str">
+        <x:v>wet paint sign, caution sign, jobsite safety sign, painting accessory</x:v>
       </x:c>
       <x:c r="J749" t="str">
         <x:v>Trimaco</x:v>
@@ -38078,8 +38082,8 @@
       <x:c r="H750" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I750" t="str">
-        <x:v>allpro, allpro tack cloth, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I750" s="15" t="str">
+        <x:v>tack cloth, surface preparation cloth, dust-removal cloth, painting accessory</x:v>
       </x:c>
       <x:c r="J750" t="str">
         <x:v>AllPro</x:v>
@@ -38125,8 +38129,8 @@
       <x:c r="H751" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I751" t="str">
-        <x:v>allpro, allpro spray sock, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I751" s="15" t="str">
+        <x:v>spray hood, protective headwear, painting safety gear, disposable protective clothing</x:v>
       </x:c>
       <x:c r="J751" t="str">
         <x:v>AllPro</x:v>
@@ -38172,8 +38176,8 @@
       <x:c r="H752" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I752" t="str">
-        <x:v>allpro, allpro gallon nylon strainer, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I752" s="15" t="str">
+        <x:v>paint strainer, coating filter, paint preparation accessory, painting tool</x:v>
       </x:c>
       <x:c r="J752" t="str">
         <x:v>AllPro</x:v>
@@ -38219,8 +38223,8 @@
       <x:c r="H753" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I753" t="str">
-        <x:v>allpro, allpro 5-gallon nylon paint strainer 25pk, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I753" s="15" t="str">
+        <x:v>paint strainer, coating filter, paint preparation accessory, painting tool</x:v>
       </x:c>
       <x:c r="J753" t="str">
         <x:v>AllPro</x:v>
@@ -38266,8 +38270,8 @@
       <x:c r="H754" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I754" t="str">
-        <x:v>trimaco, nylon strainers, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I754" s="15" t="str">
+        <x:v>paint strainer, coating filter, paint preparation accessory, painting tool</x:v>
       </x:c>
       <x:c r="J754" t="str">
         <x:v>Trimaco</x:v>
@@ -38313,8 +38317,8 @@
       <x:c r="H755" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I755" t="str">
-        <x:v>trimaco, trimaco 12" masking paper, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I755" s="15" t="str">
+        <x:v>masking paper, surface protection paper, paint masking material, painting accessory</x:v>
       </x:c>
       <x:c r="J755" t="str">
         <x:v>Trimaco</x:v>
@@ -38360,8 +38364,8 @@
       <x:c r="H756" t="str">
         <x:v>Spray Equipment Sales &amp; Service &gt; Tritech</x:v>
       </x:c>
-      <x:c r="I756" t="str">
-        <x:v>tritech, tritech t93r ultra-finish tip 408, spray equipment sales &amp; service</x:v>
+      <x:c r="I756" s="15" t="str">
+        <x:v>airless spray tip, sprayer nozzle, paint sprayer accessory, coating application part</x:v>
       </x:c>
       <x:c r="J756" t="str">
         <x:v>TriTech</x:v>
@@ -38407,8 +38411,8 @@
       <x:c r="H757" t="str">
         <x:v>Spray Equipment Sales &amp; Service &gt; Tritech</x:v>
       </x:c>
-      <x:c r="I757" t="str">
-        <x:v>tritech, tritech t93r contractor tip 415, spray equipment sales &amp; service</x:v>
+      <x:c r="I757" s="15" t="str">
+        <x:v>airless spray tip, sprayer nozzle, paint sprayer accessory, coating application part</x:v>
       </x:c>
       <x:c r="J757" t="str">
         <x:v>TriTech</x:v>
@@ -38454,8 +38458,8 @@
       <x:c r="H758" t="str">
         <x:v>Spray Equipment Sales &amp; Service &gt; Tritech</x:v>
       </x:c>
-      <x:c r="I758" t="str">
-        <x:v>tritech, tritech t9 hi cart complete 110v, spray equipment sales &amp; service</x:v>
+      <x:c r="I758" s="15" t="str">
+        <x:v>paint sprayer, airless paint sprayer, coating application equipment, professional spray equipment</x:v>
       </x:c>
       <x:c r="J758" t="str">
         <x:v>TriTech</x:v>
@@ -38501,8 +38505,8 @@
       <x:c r="H759" t="str">
         <x:v>Spray Equipment Sales &amp; Service &gt; Tritech</x:v>
       </x:c>
-      <x:c r="I759" t="str">
-        <x:v>tritech, tritech t4 110v stand complete, spray equipment sales &amp; service</x:v>
+      <x:c r="I759" s="15" t="str">
+        <x:v>paint sprayer, airless paint sprayer, coating application equipment, professional spray equipment</x:v>
       </x:c>
       <x:c r="J759" t="str">
         <x:v>TriTech</x:v>
@@ -38548,8 +38552,8 @@
       <x:c r="H760" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Cleaners &amp; Removers</x:v>
       </x:c>
-      <x:c r="I760" t="str">
-        <x:v>value chem, satin finish cleaner for stainless steel, painting tools &amp; accessories, cleaners &amp; removers</x:v>
+      <x:c r="I760" s="15" t="str">
+        <x:v>stainless steel cleaner, metal cleaner, polishing cleaner, surface cleaning product</x:v>
       </x:c>
       <x:c r="J760" t="str">
         <x:v>Value Chem</x:v>
@@ -38595,8 +38599,8 @@
       <x:c r="H761" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Cleaners &amp; Removers</x:v>
       </x:c>
-      <x:c r="I761" t="str">
-        <x:v>value chem, grease buster concentrate cleaner, painting tools &amp; accessories, cleaners &amp; removers</x:v>
+      <x:c r="I761" s="15" t="str">
+        <x:v>degreaser, heavy-duty cleaner, surface preparation cleaner, concentrated cleaner</x:v>
       </x:c>
       <x:c r="J761" t="str">
         <x:v>Value Chem</x:v>
@@ -38642,8 +38646,8 @@
       <x:c r="H762" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Cleaners &amp; Removers</x:v>
       </x:c>
-      <x:c r="I762" t="str">
-        <x:v>value chem, crete &amp; clean concrete etching and clean, painting tools &amp; accessories, cleaners &amp; removers</x:v>
+      <x:c r="I762" s="15" t="str">
+        <x:v>concrete etcher, masonry cleaner, acidic surface cleaner, surface preparation chemical</x:v>
       </x:c>
       <x:c r="J762" t="str">
         <x:v>Value Chem</x:v>
@@ -38689,8 +38693,8 @@
       <x:c r="H763" t="str">
         <x:v>Paints &gt; Aerosols</x:v>
       </x:c>
-      <x:c r="I763" t="str">
-        <x:v>value chem, acoustical tile restorer, paints, aerosols</x:v>
+      <x:c r="I763" s="15" t="str">
+        <x:v>acoustical tile coating, ceiling tile restorer, aerosol coating, specialty restoration coating</x:v>
       </x:c>
       <x:c r="J763" t="str">
         <x:v>Value Chem</x:v>
@@ -38739,8 +38743,8 @@
       <x:c r="H764" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Clothing &amp; Safety</x:v>
       </x:c>
-      <x:c r="I764" t="str">
-        <x:v>vic safety, green rubber gloves sol-vex large, painting tools &amp; accessories, clothing &amp; safety</x:v>
+      <x:c r="I764" s="15" t="str">
+        <x:v>protective gloves, chemical-resistant gloves, hand protection, personal protective equipment</x:v>
       </x:c>
       <x:c r="J764" t="str">
         <x:v>Vic Safety</x:v>
@@ -38786,8 +38790,8 @@
       <x:c r="H765" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Clothing &amp; Safety</x:v>
       </x:c>
-      <x:c r="I765" t="str">
-        <x:v>vic safety, foot slip covers 5 pairs, painting tools &amp; accessories, clothing &amp; safety</x:v>
+      <x:c r="I765" s="15" t="str">
+        <x:v>shoe covers, disposable footwear cover, protective clothing, jobsite cleanliness product</x:v>
       </x:c>
       <x:c r="J765" t="str">
         <x:v>Vic Safety</x:v>
@@ -38833,8 +38837,8 @@
       <x:c r="H766" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Clothing &amp; Safety</x:v>
       </x:c>
-      <x:c r="I766" t="str">
-        <x:v>vic safety, blackshield black nitrile medium, painting tools &amp; accessories, clothing &amp; safety</x:v>
+      <x:c r="I766" s="15" t="str">
+        <x:v>nitrile gloves, protective gloves, hand protection, personal protective equipment</x:v>
       </x:c>
       <x:c r="J766" t="str">
         <x:v>Vic Safety</x:v>
@@ -38880,8 +38884,8 @@
       <x:c r="H767" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Clothing &amp; Safety</x:v>
       </x:c>
-      <x:c r="I767" t="str">
-        <x:v>vic safety, black nitrile 8 mil gloves lg 50bk, painting tools &amp; accessories, clothing &amp; safety</x:v>
+      <x:c r="I767" s="15" t="str">
+        <x:v>protective gloves, nitrile gloves, hand protection, personal protective equipment</x:v>
       </x:c>
       <x:c r="J767" t="str">
         <x:v>Vic Safety</x:v>
@@ -38927,8 +38931,8 @@
       <x:c r="H768" t="str">
         <x:v>Paints &gt; Stains &amp; Varnishes</x:v>
       </x:c>
-      <x:c r="I768" t="str">
-        <x:v>renner, renner exterior uv water-based varnish - matte, paints, stains &amp; varnishes</x:v>
+      <x:c r="I768" s="15" t="str">
+        <x:v>exterior varnish, water-based varnish, clear wood finish, uv-resistant finish, clear finish, protective coating, clear coat, wood finish</x:v>
       </x:c>
       <x:c r="J768" t="str">
         <x:v>Renner</x:v>
@@ -38977,8 +38981,8 @@
       <x:c r="H769" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I769" t="str">
-        <x:v>warner, warner adjustable spray shield, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I769" s="15" t="str">
+        <x:v>spray shield, overspray guard, paint spraying accessory, painting tool</x:v>
       </x:c>
       <x:c r="J769" t="str">
         <x:v>Warner</x:v>
@@ -39024,8 +39028,8 @@
       <x:c r="H770" t="str">
         <x:v>Paints &gt; Stains &amp; Varnishes</x:v>
       </x:c>
-      <x:c r="I770" t="str">
-        <x:v>watco, watco danish oil dark walnut, paints, stains &amp; varnishes</x:v>
+      <x:c r="I770" s="15" t="str">
+        <x:v>danish oil finish, penetrating oil finish, wood finish, oil-based finish</x:v>
       </x:c>
       <x:c r="J770" t="str">
         <x:v>Watco</x:v>
@@ -39077,8 +39081,8 @@
       <x:c r="H771" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Clothing &amp; Safety</x:v>
       </x:c>
-      <x:c r="I771" t="str">
-        <x:v>wipeco, workeze coverall large, painting tools &amp; accessories, clothing &amp; safety</x:v>
+      <x:c r="I771" s="15" t="str">
+        <x:v>painter clothing, workwear, protective clothing, coveralls</x:v>
       </x:c>
       <x:c r="J771" t="str">
         <x:v>Wipeco</x:v>
@@ -39124,8 +39128,8 @@
       <x:c r="H772" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I772" t="str">
-        <x:v>wipeco, wipeco painters glove large, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I772" s="15" t="str">
+        <x:v>painting cloth, surface preparation cloth, lint-free wiping cloth, painting accessory</x:v>
       </x:c>
       <x:c r="J772" t="str">
         <x:v>Wipeco</x:v>
@@ -39171,8 +39175,8 @@
       <x:c r="H773" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I773" t="str">
-        <x:v>wipeco, stainpro stain pad, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I773" s="15" t="str">
+        <x:v>paint pad, flat paint applicator, painting tool, coating applicator</x:v>
       </x:c>
       <x:c r="J773" t="str">
         <x:v>Wipeco</x:v>
@@ -39218,8 +39222,8 @@
       <x:c r="H774" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I774" t="str">
-        <x:v>wipeco, stainpro leak-proof drop cloth, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I774" s="15" t="str">
+        <x:v>drop cloth, surface protection, painting cover, painting accessory</x:v>
       </x:c>
       <x:c r="J774" t="str">
         <x:v>Wipeco</x:v>
@@ -39265,8 +39269,8 @@
       <x:c r="H775" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I775" t="str">
-        <x:v>wooster brush co., wooster super/fab roller cover 4 1/2" x 3/8" 2pk, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I775" s="15" t="str">
+        <x:v>paint roller cover, paint roller refill, paint applicator, painting tool</x:v>
       </x:c>
       <x:c r="J775" t="str">
         <x:v>Wooster Brush Co.</x:v>
@@ -39312,8 +39316,8 @@
       <x:c r="H776" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I776" t="str">
-        <x:v>wooster brush co., wooster super doo-z roller kit, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I776" s="15" t="str">
+        <x:v>paint roller kit, paint tray set, paint applicator kit, painting tool</x:v>
       </x:c>
       <x:c r="J776" t="str">
         <x:v>Wooster Brush Co.</x:v>
@@ -39359,8 +39363,8 @@
       <x:c r="H777" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I777" t="str">
-        <x:v>wooster brush co., wooster silver tip 2 1/2" angle brush, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I777" s="15" t="str">
+        <x:v>angled paint brush, sash brush, paint applicator, painting tool, paint brush, bristle brush</x:v>
       </x:c>
       <x:c r="J777" t="str">
         <x:v>Wooster Brush Co.</x:v>
@@ -39406,8 +39410,8 @@
       <x:c r="H778" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I778" t="str">
-        <x:v>wooster brush co., wooster sherlock roller frame 9 1/2", painting tools &amp; accessories, tools</x:v>
+      <x:c r="I778" s="15" t="str">
+        <x:v>paint roller frame, roller handle, paint applicator, painting tool</x:v>
       </x:c>
       <x:c r="J778" t="str">
         <x:v>Wooster Brush Co.</x:v>
@@ -39453,8 +39457,8 @@
       <x:c r="H779" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I779" t="str">
-        <x:v>wooster brush co., wooster pro/doo-z roller cover 6 1/2" x 3/8" 2pk, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I779" s="15" t="str">
+        <x:v>paint roller cover, paint roller refill, paint applicator, painting tool</x:v>
       </x:c>
       <x:c r="J779" t="str">
         <x:v>Wooster Brush Co.</x:v>
@@ -39500,8 +39504,8 @@
       <x:c r="H780" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I780" t="str">
-        <x:v>wooster brush co., wooster mohair blend roller cover 14" x 1/4", painting tools &amp; accessories, tools</x:v>
+      <x:c r="I780" s="15" t="str">
+        <x:v>paint roller cover, paint roller refill, paint applicator, painting tool, mohair roller cover</x:v>
       </x:c>
       <x:c r="J780" t="str">
         <x:v>Wooster Brush Co.</x:v>
@@ -39547,8 +39551,8 @@
       <x:c r="H781" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I781" t="str">
-        <x:v>wooster brush co., wooster jumbo-koter big green flocked foam roller, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I781" s="15" t="str">
+        <x:v>paint roller cover, paint roller refill, paint applicator, painting tool, foam roller cover</x:v>
       </x:c>
       <x:c r="J781" t="str">
         <x:v>Wooster Brush Co.</x:v>
@@ -39594,8 +39598,8 @@
       <x:c r="H782" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I782" t="str">
-        <x:v>wooster brush co., wooster jumbo-koter 14" roller frame, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I782" s="15" t="str">
+        <x:v>paint roller frame, roller handle, paint applicator, painting tool</x:v>
       </x:c>
       <x:c r="J782" t="str">
         <x:v>Wooster Brush Co.</x:v>
@@ -39641,8 +39645,8 @@
       <x:c r="H783" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I783" t="str">
-        <x:v>wooster brush co., wooster jumbo-koter microfiber roller 4 1/2" x 3/8" 2pk, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I783" s="15" t="str">
+        <x:v>paint roller cover, paint roller refill, paint applicator, painting tool, microfiber roller cover</x:v>
       </x:c>
       <x:c r="J783" t="str">
         <x:v>Wooster Brush Co.</x:v>
@@ -39688,8 +39692,8 @@
       <x:c r="H784" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I784" t="str">
-        <x:v>wooster brush co., wooster dust eater, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I784" s="15" t="str">
+        <x:v>dusting tool, surface preparation brush, sanding dust remover, painting preparation tool</x:v>
       </x:c>
       <x:c r="J784" t="str">
         <x:v>Wooster Brush Co.</x:v>
@@ -39735,8 +39739,8 @@
       <x:c r="H785" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I785" t="str">
-        <x:v>wooster brush co., wooster wide boy 5-gallon bucket, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I785" s="15" t="str">
+        <x:v>paint pail, paint container, mixing container, painting accessory</x:v>
       </x:c>
       <x:c r="J785" t="str">
         <x:v>Wooster Brush Co.</x:v>
@@ -39782,8 +39786,8 @@
       <x:c r="H786" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I786" t="str">
-        <x:v>wooster, wooster sherlock extension pole 4–8 ft, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I786" s="15" t="str">
+        <x:v>paint roller extension pole, telescoping pole, paint applicator accessory, painting tool</x:v>
       </x:c>
       <x:c r="J786" t="str">
         <x:v>Wooster</x:v>
@@ -39829,8 +39833,8 @@
       <x:c r="H787" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I787" t="str">
-        <x:v>wooster brush co., wooster shortcut 2" angle brush, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I787" s="15" t="str">
+        <x:v>angled paint brush, sash brush, paint applicator, painting tool, paint brush, bristle brush</x:v>
       </x:c>
       <x:c r="J787" t="str">
         <x:v>Wooster Brush Co.</x:v>
@@ -39876,8 +39880,8 @@
       <x:c r="H788" t="str">
         <x:v>Paints &gt; Primers</x:v>
       </x:c>
-      <x:c r="I788" t="str">
-        <x:v>xim, xim uma acrylic primer, paints, primers</x:v>
+      <x:c r="I788" s="15" t="str">
+        <x:v>primer, primer sealer, surface preparation coating, basecoat</x:v>
       </x:c>
       <x:c r="J788" t="str">
         <x:v>XIM</x:v>
@@ -39929,8 +39933,8 @@
       <x:c r="H789" t="str">
         <x:v>Paints &gt; Stains &amp; Varnishes</x:v>
       </x:c>
-      <x:c r="I789" t="str">
-        <x:v>howard, restor-a-finish walnut, paints, stains &amp; varnishes</x:v>
+      <x:c r="I789" s="15" t="str">
+        <x:v>wood finish restorer, furniture refinisher, colour-restoring finish, wood care product</x:v>
       </x:c>
       <x:c r="J789" t="str">
         <x:v>Howard</x:v>
@@ -39982,8 +39986,8 @@
       <x:c r="H790" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I790" t="str">
-        <x:v>flood, floetrol gallon - flood, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I790" s="15" t="str">
+        <x:v>paint additive, paint conditioner, latex paint additive, flow and levelling additive</x:v>
       </x:c>
       <x:c r="J790" t="str">
         <x:v>Flood</x:v>
@@ -40029,8 +40033,8 @@
       <x:c r="H791" t="str">
         <x:v>Paints &gt; Primers</x:v>
       </x:c>
-      <x:c r="I791" t="str">
-        <x:v>zinsser, zinsser odor killing primer, paints, primers</x:v>
+      <x:c r="I791" s="15" t="str">
+        <x:v>stain-blocking primer, odour-blocking primer, primer sealer, surface preparation coating, primer, basecoat</x:v>
       </x:c>
       <x:c r="J791" t="str">
         <x:v>Zinsser</x:v>
@@ -40082,8 +40086,8 @@
       <x:c r="H792" t="str">
         <x:v>Paints &gt; Primers</x:v>
       </x:c>
-      <x:c r="I792" t="str">
-        <x:v>zinsser, zinsser covers up ceiling paint &amp; primer spray, paints, primers</x:v>
+      <x:c r="I792" s="15" t="str">
+        <x:v>ceiling paint, interior paint, flat paint, architectural coating, spray primer, aerosol primer, primer, surface preparation coating</x:v>
       </x:c>
       <x:c r="J792" t="str">
         <x:v>Zinsser</x:v>
@@ -40135,8 +40139,8 @@
       <x:c r="H793" t="str">
         <x:v>Paints &gt; Primers</x:v>
       </x:c>
-      <x:c r="I793" t="str">
-        <x:v>zinsser, zinsser bulls eye shellac, paints, primers</x:v>
+      <x:c r="I793" s="15" t="str">
+        <x:v>shellac finish, clear wood finish, natural resin finish, sealing finish</x:v>
       </x:c>
       <x:c r="J793" t="str">
         <x:v>Zinsser</x:v>
@@ -40204,8 +40208,8 @@
       <x:c r="H794" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Paint Prep &amp; Repairs</x:v>
       </x:c>
-      <x:c r="I794" t="str">
-        <x:v>zinsser, zinsser watertite hydraulic cement, painting tools &amp; accessories, paint prep &amp; repairs</x:v>
+      <x:c r="I794" s="15" t="str">
+        <x:v>hydraulic cement, waterproof repair cement, masonry patch, rapid-setting cement</x:v>
       </x:c>
       <x:c r="J794" t="str">
         <x:v>Zinsser</x:v>
@@ -40251,8 +40255,8 @@
       <x:c r="H795" t="str">
         <x:v>Paints &gt; Primers</x:v>
       </x:c>
-      <x:c r="I795" t="str">
-        <x:v>zinsser, zinsser shieldz universal wallcovering primer, paints, primers</x:v>
+      <x:c r="I795" s="15" t="str">
+        <x:v>wallcovering primer, primer sealer, wall preparation coating, interior primer, primer, surface preparation coating, basecoat</x:v>
       </x:c>
       <x:c r="J795" t="str">
         <x:v>Zinsser</x:v>
@@ -40304,8 +40308,8 @@
       <x:c r="H796" t="str">
         <x:v>Paints &gt; Primers</x:v>
       </x:c>
-      <x:c r="I796" t="str">
-        <x:v>zinsser, zinsser peel stop plus high build binding primer, paints, primers</x:v>
+      <x:c r="I796" s="15" t="str">
+        <x:v>binding primer, high-build primer, problem-surface primer, primer sealer, primer, surface preparation coating, basecoat</x:v>
       </x:c>
       <x:c r="J796" t="str">
         <x:v>Zinsser</x:v>
@@ -40357,8 +40361,8 @@
       <x:c r="H797" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Cleaners &amp; Removers</x:v>
       </x:c>
-      <x:c r="I797" t="str">
-        <x:v>zinsser, zinsser dif wallpaper stripper gel, painting tools &amp; accessories, cleaners &amp; removers</x:v>
+      <x:c r="I797" s="15" t="str">
+        <x:v>wallpaper remover, wallpaper stripping gel, wallcovering remover, surface preparation chemical</x:v>
       </x:c>
       <x:c r="J797" t="str">
         <x:v>Zinsser</x:v>
@@ -40404,8 +40408,8 @@
       <x:c r="H798" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I798" t="str">
-        <x:v>zipwall, zipwall zippole10, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I798" s="15" t="str">
+        <x:v>dust barrier pole, telescoping support pole, plastic sheeting support, renovation containment system</x:v>
       </x:c>
       <x:c r="J798" t="str">
         <x:v>ZipWall</x:v>
@@ -40451,8 +40455,8 @@
       <x:c r="H799" t="str">
         <x:v>Painting Tools &amp; Accessories &gt; Tools</x:v>
       </x:c>
-      <x:c r="I799" t="str">
-        <x:v>zipwall, zipwall heavy duty zipper, painting tools &amp; accessories, tools</x:v>
+      <x:c r="I799" s="15" t="str">
+        <x:v>dust barrier zipper, adhesive zipper, plastic sheeting access door, renovation containment accessory</x:v>
       </x:c>
       <x:c r="J799" t="str">
         <x:v>ZipWall</x:v>
